--- a/research/traditional_assets/database/data/lithuania/lithuania_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_furn_home_furnishings.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03425</v>
+        <v>0.0009499999999999925</v>
+      </c>
+      <c r="E2">
+        <v>-0.111</v>
       </c>
       <c r="G2">
-        <v>0.06670588235294117</v>
+        <v>-0.006627906976744187</v>
       </c>
       <c r="H2">
-        <v>0.06437908496732025</v>
+        <v>-0.008813953488372094</v>
       </c>
       <c r="I2">
-        <v>-0.01428104575163399</v>
+        <v>-0.07108527131782946</v>
       </c>
       <c r="J2">
-        <v>-0.01428104575163399</v>
+        <v>-0.06683323821752984</v>
       </c>
       <c r="K2">
-        <v>-4.72</v>
+        <v>-1.86</v>
       </c>
       <c r="L2">
-        <v>-0.03084967320261438</v>
+        <v>-0.01441860465116279</v>
       </c>
       <c r="M2">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.000351493848857645</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.003389830508474577</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.000351493848857645</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.003389830508474577</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>0.171</v>
+        <v>0.5720000000000001</v>
       </c>
       <c r="V2">
-        <v>0.003756590509666081</v>
+        <v>0.01514028586553732</v>
       </c>
       <c r="W2">
-        <v>-0.1190969903102169</v>
+        <v>-0.383583202511774</v>
       </c>
       <c r="X2">
-        <v>0.1335264745341695</v>
+        <v>0.2275507275924808</v>
       </c>
       <c r="Y2">
-        <v>-0.2526234648443865</v>
+        <v>-0.6111339301042548</v>
       </c>
       <c r="Z2">
-        <v>1.572747270820912</v>
+        <v>1.382355147397636</v>
       </c>
       <c r="AA2">
-        <v>-0.01448229072934345</v>
+        <v>-0.1592359928396284</v>
       </c>
       <c r="AB2">
-        <v>0.07201526758673665</v>
+        <v>0.1203129233738948</v>
       </c>
       <c r="AC2">
-        <v>-0.08649755831608009</v>
+        <v>-0.2795489162135232</v>
       </c>
       <c r="AD2">
-        <v>62.1</v>
+        <v>51.46</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>62.1</v>
+        <v>51.46</v>
       </c>
       <c r="AG2">
-        <v>61.929</v>
+        <v>50.888</v>
       </c>
       <c r="AH2">
-        <v>0.5770302917673295</v>
+        <v>0.5766472433886149</v>
       </c>
       <c r="AI2">
-        <v>0.6642421649374264</v>
+        <v>0.6598028028156373</v>
       </c>
       <c r="AJ2">
-        <v>0.5763571554877198</v>
+        <v>0.5739161817115531</v>
       </c>
       <c r="AK2">
-        <v>0.6636269141332419</v>
+        <v>0.6572893659343073</v>
       </c>
       <c r="AL2">
-        <v>2.279</v>
+        <v>2.416</v>
       </c>
       <c r="AM2">
-        <v>2.273</v>
+        <v>2.416</v>
       </c>
       <c r="AN2">
-        <v>13.32618025751073</v>
+        <v>-18.80160759956156</v>
       </c>
       <c r="AO2">
-        <v>-0.9587538394032471</v>
+        <v>-3.795529801324503</v>
       </c>
       <c r="AP2">
-        <v>13.28948497854077</v>
+        <v>-18.59261965655827</v>
       </c>
       <c r="AQ2">
-        <v>-0.9612846458424988</v>
+        <v>-3.795529801324503</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AB Snaige (NSEL:SNG1L)</t>
+          <t>Vilniaus Baldai AB (NSEL:VBL1L)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,25 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0475</v>
+        <v>0.0949</v>
+      </c>
+      <c r="E3">
+        <v>-0.111</v>
       </c>
       <c r="G3">
-        <v>0.08579634464751959</v>
+        <v>-0.01213270142180095</v>
       </c>
       <c r="H3">
-        <v>0.07650130548302873</v>
+        <v>-0.01213270142180095</v>
       </c>
       <c r="I3">
-        <v>-0.0009138381201044388</v>
+        <v>-0.04635071090047393</v>
       </c>
       <c r="J3">
-        <v>-0.0009138381201044388</v>
+        <v>-0.04080568720379146</v>
       </c>
       <c r="K3">
-        <v>-0.68</v>
+        <v>2.87</v>
       </c>
       <c r="L3">
-        <v>-0.01775456919060053</v>
+        <v>0.02720379146919431</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,79 +758,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.09</v>
+        <v>0.379</v>
       </c>
       <c r="V3">
-        <v>0.01056338028169014</v>
+        <v>0.01159021406727829</v>
       </c>
       <c r="W3">
-        <v>-0.1107491856677525</v>
+        <v>0.1103846153846154</v>
       </c>
       <c r="X3">
-        <v>0.1314054165280935</v>
+        <v>0.2070015021994248</v>
       </c>
       <c r="Y3">
-        <v>-0.2421546021958459</v>
+        <v>-0.09661688681480943</v>
       </c>
       <c r="Z3">
-        <v>2.179603915319827</v>
+        <v>1.369791869538685</v>
       </c>
       <c r="AA3">
-        <v>-0.001991805144548145</v>
+        <v>-0.05589529856269233</v>
       </c>
       <c r="AB3">
-        <v>0.07199415271721664</v>
+        <v>0.1182614062510035</v>
       </c>
       <c r="AC3">
-        <v>-0.07398595786176479</v>
+        <v>-0.1741567048136958</v>
       </c>
       <c r="AD3">
-        <v>11</v>
+        <v>41.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>41.9</v>
       </c>
       <c r="AG3">
-        <v>10.91</v>
+        <v>41.521</v>
       </c>
       <c r="AH3">
-        <v>0.5635245901639344</v>
+        <v>0.561662198391421</v>
       </c>
       <c r="AI3">
-        <v>0.6711409395973155</v>
+        <v>0.6107871720116619</v>
       </c>
       <c r="AJ3">
-        <v>0.5615028306742151</v>
+        <v>0.5594238827286078</v>
       </c>
       <c r="AK3">
-        <v>0.6693251533742332</v>
+        <v>0.6086249102182613</v>
       </c>
       <c r="AL3">
-        <v>0.549</v>
+        <v>1.85</v>
       </c>
       <c r="AM3">
-        <v>0.549</v>
+        <v>1.85</v>
       </c>
       <c r="AN3">
-        <v>5.82010582010582</v>
+        <v>-2464.705882352941</v>
       </c>
       <c r="AO3">
-        <v>-0.06375227686703097</v>
+        <v>-2.643243243243243</v>
       </c>
       <c r="AP3">
-        <v>5.772486772486773</v>
+        <v>-2442.411764705882</v>
       </c>
       <c r="AQ3">
-        <v>-0.06375227686703097</v>
+        <v>-2.643243243243243</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vilniaus Baldai AB (NSEL:VBL1L)</t>
+          <t>AB Snaige (NSEL:SNG1L)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,118 +850,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.116</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G4">
-        <v>0.06033129904097646</v>
+        <v>0.01808510638297872</v>
       </c>
       <c r="H4">
-        <v>0.06033129904097646</v>
+        <v>0.006085106382978723</v>
       </c>
       <c r="I4">
-        <v>-0.01874455100261552</v>
+        <v>-0.1821276595744681</v>
       </c>
       <c r="J4">
-        <v>-0.01874455100261552</v>
+        <v>-0.1821276595744681</v>
       </c>
       <c r="K4">
-        <v>-4.04</v>
+        <v>-4.73</v>
       </c>
       <c r="L4">
-        <v>-0.03522231909328683</v>
+        <v>-0.2012765957446809</v>
       </c>
       <c r="M4">
-        <v>0.016</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.0004324324324324324</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.00396039603960396</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0.016</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.0004324324324324324</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0.00396039603960396</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>0.081</v>
+        <v>0.193</v>
       </c>
       <c r="V4">
-        <v>0.002189189189189189</v>
+        <v>0.03799212598425197</v>
       </c>
       <c r="W4">
-        <v>-0.1274447949526814</v>
+        <v>-0.8775510204081634</v>
       </c>
       <c r="X4">
-        <v>0.1356475325402456</v>
+        <v>0.2480999529855367</v>
       </c>
       <c r="Y4">
-        <v>-0.2630923274929269</v>
+        <v>-1.1256509733937</v>
       </c>
       <c r="Z4">
-        <v>1.438966252665914</v>
+        <v>1.441717791411043</v>
       </c>
       <c r="AA4">
-        <v>-0.02697277631413875</v>
+        <v>-0.2625766871165644</v>
       </c>
       <c r="AB4">
-        <v>0.07203638245625665</v>
+        <v>0.1223644404967861</v>
       </c>
       <c r="AC4">
-        <v>-0.0990091587703954</v>
+        <v>-0.3849411276133505</v>
       </c>
       <c r="AD4">
-        <v>51.1</v>
+        <v>9.56</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>51.1</v>
+        <v>9.56</v>
       </c>
       <c r="AG4">
-        <v>51.019</v>
+        <v>9.367000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.580022701475596</v>
+        <v>0.6530054644808744</v>
       </c>
       <c r="AI4">
-        <v>0.6627756160830092</v>
+        <v>1.017779197274566</v>
       </c>
       <c r="AJ4">
-        <v>0.5796362149081448</v>
+        <v>0.6483699037862533</v>
       </c>
       <c r="AK4">
-        <v>0.6624209610615561</v>
+        <v>1.018152173913043</v>
       </c>
       <c r="AL4">
-        <v>1.73</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AM4">
-        <v>1.724</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AN4">
-        <v>18.44765342960289</v>
+        <v>-3.514705882352941</v>
       </c>
       <c r="AO4">
-        <v>-1.242774566473988</v>
+        <v>-7.56183745583039</v>
       </c>
       <c r="AP4">
-        <v>18.41841155234657</v>
+        <v>-3.44375</v>
       </c>
       <c r="AQ4">
-        <v>-1.247099767981438</v>
+        <v>-7.56183745583039</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/lithuania/lithuania_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_furn_home_furnishings.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nsel_vbl1l" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0009499999999999925</v>
+        <v>-0.0258</v>
       </c>
       <c r="E2">
-        <v>-0.111</v>
+        <v>0.387</v>
       </c>
       <c r="G2">
-        <v>-0.006627906976744187</v>
+        <v>0.04825409197194078</v>
       </c>
       <c r="H2">
-        <v>-0.008813953488372094</v>
+        <v>0.04598597038191739</v>
       </c>
       <c r="I2">
-        <v>-0.07108527131782946</v>
+        <v>0.04809041309431022</v>
       </c>
       <c r="J2">
-        <v>-0.06683323821752984</v>
+        <v>0.04737108317934616</v>
       </c>
       <c r="K2">
-        <v>-1.86</v>
+        <v>3.35</v>
       </c>
       <c r="L2">
-        <v>-0.01441860465116279</v>
+        <v>0.02611067809820733</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.001759915944313107</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.001759915944313107</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.5720000000000001</v>
+        <v>3.172</v>
       </c>
       <c r="V2">
-        <v>0.01514028586553732</v>
+        <v>0.08332019963225636</v>
       </c>
       <c r="W2">
-        <v>-0.383583202511774</v>
+        <v>10.78808338379421</v>
       </c>
       <c r="X2">
-        <v>0.2275507275924808</v>
+        <v>0.1667875680931357</v>
       </c>
       <c r="Y2">
-        <v>-0.6111339301042548</v>
+        <v>10.62129581570107</v>
       </c>
       <c r="Z2">
-        <v>1.382355147397636</v>
+        <v>1.657173118404567</v>
       </c>
       <c r="AA2">
-        <v>-0.1592359928396284</v>
+        <v>-0.1370535188315494</v>
       </c>
       <c r="AB2">
-        <v>0.1203129233738948</v>
+        <v>0.09442175222219482</v>
       </c>
       <c r="AC2">
-        <v>-0.2795489162135232</v>
+        <v>-0.2314752710537442</v>
       </c>
       <c r="AD2">
-        <v>51.46</v>
+        <v>54</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>51.46</v>
+        <v>54</v>
       </c>
       <c r="AG2">
-        <v>50.888</v>
+        <v>50.828</v>
       </c>
       <c r="AH2">
-        <v>0.5766472433886149</v>
+        <v>0.5865102639296188</v>
       </c>
       <c r="AI2">
-        <v>0.6598028028156373</v>
+        <v>0.6318745611982214</v>
       </c>
       <c r="AJ2">
-        <v>0.5739161817115531</v>
+        <v>0.5717563949695157</v>
       </c>
       <c r="AK2">
-        <v>0.6572893659343073</v>
+        <v>0.6176842309935835</v>
       </c>
       <c r="AL2">
-        <v>2.416</v>
+        <v>2.914</v>
       </c>
       <c r="AM2">
-        <v>2.416</v>
+        <v>2.914</v>
       </c>
       <c r="AN2">
-        <v>-18.80160759956156</v>
+        <v>4.160246533127889</v>
       </c>
       <c r="AO2">
-        <v>-3.795529801324503</v>
+        <v>2.117364447494853</v>
       </c>
       <c r="AP2">
-        <v>-18.59261965655827</v>
+        <v>3.915870570107858</v>
       </c>
       <c r="AQ2">
-        <v>-3.795529801324503</v>
+        <v>2.117364447494853</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +724,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0949</v>
+        <v>0.0684</v>
       </c>
       <c r="E3">
-        <v>-0.111</v>
+        <v>0.387</v>
       </c>
       <c r="G3">
-        <v>-0.01213270142180095</v>
+        <v>0.08738489871086556</v>
       </c>
       <c r="H3">
-        <v>-0.01213270142180095</v>
+        <v>0.08738489871086556</v>
       </c>
       <c r="I3">
-        <v>-0.04635071090047393</v>
+        <v>0.09208103130755065</v>
       </c>
       <c r="J3">
-        <v>-0.04080568720379146</v>
+        <v>0.08932636000579387</v>
       </c>
       <c r="K3">
-        <v>2.87</v>
+        <v>6.91</v>
       </c>
       <c r="L3">
-        <v>0.02720379146919431</v>
+        <v>0.0636279926335175</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.067</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.002080745341614907</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.009696092619392185</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.067</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.002080745341614907</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.009696092619392185</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.379</v>
+        <v>2.69</v>
       </c>
       <c r="V3">
-        <v>0.01159021406727829</v>
+        <v>0.08354037267080744</v>
       </c>
       <c r="W3">
-        <v>0.1103846153846154</v>
+        <v>0.2588014981273408</v>
       </c>
       <c r="X3">
-        <v>0.2070015021994248</v>
+        <v>0.1557030786618309</v>
       </c>
       <c r="Y3">
-        <v>-0.09661688681480943</v>
+        <v>0.1030984194655099</v>
       </c>
       <c r="Z3">
-        <v>1.369791869538685</v>
+        <v>1.591885196640331</v>
       </c>
       <c r="AA3">
-        <v>-0.05589529856269233</v>
+        <v>0.1421973101629882</v>
       </c>
       <c r="AB3">
-        <v>0.1182614062510035</v>
+        <v>0.0928577484751623</v>
       </c>
       <c r="AC3">
-        <v>-0.1741567048136958</v>
+        <v>0.04933956168782587</v>
       </c>
       <c r="AD3">
-        <v>41.9</v>
+        <v>43.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>41.9</v>
+        <v>43.3</v>
       </c>
       <c r="AG3">
-        <v>41.521</v>
+        <v>40.61</v>
       </c>
       <c r="AH3">
-        <v>0.561662198391421</v>
+        <v>0.5735099337748344</v>
       </c>
       <c r="AI3">
-        <v>0.6107871720116619</v>
+        <v>0.5515923566878981</v>
       </c>
       <c r="AJ3">
-        <v>0.5594238827286078</v>
+        <v>0.557753055898915</v>
       </c>
       <c r="AK3">
-        <v>0.6086249102182613</v>
+        <v>0.5356813085344941</v>
       </c>
       <c r="AL3">
-        <v>1.85</v>
+        <v>2.86</v>
       </c>
       <c r="AM3">
-        <v>1.85</v>
+        <v>2.86</v>
       </c>
       <c r="AN3">
-        <v>-2464.705882352941</v>
+        <v>2.867549668874172</v>
       </c>
       <c r="AO3">
-        <v>-2.643243243243243</v>
+        <v>3.496503496503497</v>
       </c>
       <c r="AP3">
-        <v>-2442.411764705882</v>
+        <v>2.689403973509934</v>
       </c>
       <c r="AQ3">
-        <v>-2.643243243243243</v>
+        <v>3.496503496503497</v>
       </c>
     </row>
     <row r="4">
@@ -850,25 +858,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.09300000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="G4">
-        <v>0.01808510638297872</v>
+        <v>-0.1674619289340102</v>
       </c>
       <c r="H4">
-        <v>0.006085106382978723</v>
+        <v>-0.1822335025380711</v>
       </c>
       <c r="I4">
-        <v>-0.1821276595744681</v>
+        <v>-0.1944162436548224</v>
       </c>
       <c r="J4">
-        <v>-0.1821276595744681</v>
+        <v>-0.1944162436548224</v>
       </c>
       <c r="K4">
-        <v>-4.73</v>
+        <v>-3.56</v>
       </c>
       <c r="L4">
-        <v>-0.2012765957446809</v>
+        <v>-0.1807106598984772</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -892,73 +900,8845 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.193</v>
+        <v>0.482</v>
       </c>
       <c r="V4">
-        <v>0.03799212598425197</v>
+        <v>0.08211243611584326</v>
       </c>
       <c r="W4">
-        <v>-0.8775510204081634</v>
+        <v>21.31736526946108</v>
       </c>
       <c r="X4">
-        <v>0.2480999529855367</v>
+        <v>0.1778720575244404</v>
       </c>
       <c r="Y4">
-        <v>-1.1256509733937</v>
+        <v>21.13949321193664</v>
       </c>
       <c r="Z4">
-        <v>1.441717791411043</v>
+        <v>2.141304347826086</v>
       </c>
       <c r="AA4">
-        <v>-0.2625766871165644</v>
+        <v>-0.4163043478260869</v>
       </c>
       <c r="AB4">
-        <v>0.1223644404967861</v>
+        <v>0.09598575596922733</v>
       </c>
       <c r="AC4">
-        <v>-0.3849411276133505</v>
+        <v>-0.5122901037953143</v>
       </c>
       <c r="AD4">
-        <v>9.56</v>
+        <v>10.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>9.56</v>
+        <v>10.7</v>
       </c>
       <c r="AG4">
-        <v>9.367000000000001</v>
+        <v>10.218</v>
       </c>
       <c r="AH4">
-        <v>0.6530054644808744</v>
+        <v>0.6457453228726614</v>
       </c>
       <c r="AI4">
-        <v>1.017779197274566</v>
+        <v>1.537356321839081</v>
       </c>
       <c r="AJ4">
-        <v>0.6483699037862533</v>
+        <v>0.6351317752362009</v>
       </c>
       <c r="AK4">
-        <v>1.018152173913043</v>
+        <v>1.577338684779253</v>
       </c>
       <c r="AL4">
-        <v>0.5659999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="AM4">
-        <v>0.5659999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="AN4">
-        <v>-3.514705882352941</v>
+        <v>-5.047169811320754</v>
       </c>
       <c r="AO4">
-        <v>-7.56183745583039</v>
+        <v>-70.92592592592592</v>
       </c>
       <c r="AP4">
-        <v>-3.44375</v>
+        <v>-4.819811320754717</v>
       </c>
       <c r="AQ4">
-        <v>-7.56183745583039</v>
+        <v>-70.92592592592592</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Vilniaus Baldai AB (NSEL:VBL1L)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NSEL:VBL1L</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Furn/Home Furnishings</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3.4965034965035</v>
+      </c>
+      <c r="F2">
+        <v>9.9590792099251</v>
+      </c>
+      <c r="G2">
+        <v>2.86754966887417</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>0.5735099337748339</v>
+      </c>
+      <c r="J2">
+        <v>0.4</v>
+      </c>
+      <c r="K2">
+        <v>32.2</v>
+      </c>
+      <c r="L2">
+        <v>47.2814066973329</v>
+      </c>
+      <c r="M2">
+        <v>72.81</v>
+      </c>
+      <c r="N2">
+        <v>74.7914066973329</v>
+      </c>
+      <c r="O2">
+        <v>43.3</v>
+      </c>
+      <c r="P2">
+        <v>30.2</v>
+      </c>
+      <c r="Q2">
+        <v>0.0928577484751623</v>
+      </c>
+      <c r="R2">
+        <v>0.09012976805936231</v>
+      </c>
+      <c r="S2">
+        <v>0.046122883994545</v>
+      </c>
+      <c r="T2">
+        <v>0.03893</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.155703078661831</v>
+      </c>
+      <c r="X2">
+        <v>0.124262946765604</v>
+      </c>
+      <c r="Y2">
+        <v>2.0025797546304</v>
+      </c>
+      <c r="Z2">
+        <v>1.46400222237888</v>
+      </c>
+      <c r="AA2">
+        <v>43.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.05426221646417059</v>
+      </c>
+      <c r="AC2">
+        <v>3.496503496503497</v>
+      </c>
+      <c r="AD2">
+        <v>43.3</v>
+      </c>
+      <c r="AE2">
+        <v>2.86</v>
+      </c>
+      <c r="AF2">
+        <v>5.1</v>
+      </c>
+      <c r="AG2">
+        <v>15.1</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>32.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.0583762411417202</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.15</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>6.026</v>
+      </c>
+      <c r="AR2">
+        <v>2.86</v>
+      </c>
+      <c r="AS2">
+        <v>43.3</v>
+      </c>
+      <c r="AT2">
+        <v>2.69</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09335081708442801</v>
+      </c>
+      <c r="C2">
+        <v>75.1530199852906</v>
+      </c>
+      <c r="D2">
+        <v>72.4630199852906</v>
+      </c>
+      <c r="E2">
+        <v>-43.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.69</v>
+      </c>
+      <c r="H2">
+        <v>32.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>18.875</v>
+      </c>
+      <c r="K2">
+        <v>5.1</v>
+      </c>
+      <c r="L2">
+        <v>13.775</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>13.775</v>
+      </c>
+      <c r="O2">
+        <v>2.06625</v>
+      </c>
+      <c r="P2">
+        <v>11.70875</v>
+      </c>
+      <c r="Q2">
+        <v>16.80875</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09335081708442801</v>
+      </c>
+      <c r="T2">
+        <v>0.9344695036460947</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.037995</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09326094085880138</v>
+      </c>
+      <c r="C3">
+        <v>74.4610205946895</v>
+      </c>
+      <c r="D3">
+        <v>72.5260205946895</v>
+      </c>
+      <c r="E3">
+        <v>-42.54499999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.755</v>
+      </c>
+      <c r="G3">
+        <v>2.69</v>
+      </c>
+      <c r="H3">
+        <v>32.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>18.875</v>
+      </c>
+      <c r="K3">
+        <v>5.1</v>
+      </c>
+      <c r="L3">
+        <v>13.775</v>
+      </c>
+      <c r="M3">
+        <v>0.0337485</v>
+      </c>
+      <c r="N3">
+        <v>13.7412515</v>
+      </c>
+      <c r="O3">
+        <v>2.061187725</v>
+      </c>
+      <c r="P3">
+        <v>11.680063775</v>
+      </c>
+      <c r="Q3">
+        <v>16.780063775</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09381918268565795</v>
+      </c>
+      <c r="T3">
+        <v>0.9424927266571974</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.037995</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>408.1662888720981</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09317106463317472</v>
+      </c>
+      <c r="C4">
+        <v>73.76913084706416</v>
+      </c>
+      <c r="D4">
+        <v>72.58913084706417</v>
+      </c>
+      <c r="E4">
+        <v>-41.79</v>
+      </c>
+      <c r="F4">
+        <v>1.51</v>
+      </c>
+      <c r="G4">
+        <v>2.69</v>
+      </c>
+      <c r="H4">
+        <v>32.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>18.875</v>
+      </c>
+      <c r="K4">
+        <v>5.1</v>
+      </c>
+      <c r="L4">
+        <v>13.775</v>
+      </c>
+      <c r="M4">
+        <v>0.067497</v>
+      </c>
+      <c r="N4">
+        <v>13.707503</v>
+      </c>
+      <c r="O4">
+        <v>2.05612545</v>
+      </c>
+      <c r="P4">
+        <v>11.65137755</v>
+      </c>
+      <c r="Q4">
+        <v>16.75137755</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09429710676854564</v>
+      </c>
+      <c r="T4">
+        <v>0.950679688913425</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.037995</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>204.083144436049</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09308118840754807</v>
+      </c>
+      <c r="C5">
+        <v>73.07735102888924</v>
+      </c>
+      <c r="D5">
+        <v>72.65235102888924</v>
+      </c>
+      <c r="E5">
+        <v>-41.035</v>
+      </c>
+      <c r="F5">
+        <v>2.265</v>
+      </c>
+      <c r="G5">
+        <v>2.69</v>
+      </c>
+      <c r="H5">
+        <v>32.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>18.875</v>
+      </c>
+      <c r="K5">
+        <v>5.1</v>
+      </c>
+      <c r="L5">
+        <v>13.775</v>
+      </c>
+      <c r="M5">
+        <v>0.1012455</v>
+      </c>
+      <c r="N5">
+        <v>13.6737545</v>
+      </c>
+      <c r="O5">
+        <v>2.051063175</v>
+      </c>
+      <c r="P5">
+        <v>11.622691325</v>
+      </c>
+      <c r="Q5">
+        <v>16.722691325</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09478488495623513</v>
+      </c>
+      <c r="T5">
+        <v>0.9590354545151415</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.037995</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>136.0554296240327</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09299131218192144</v>
+      </c>
+      <c r="C6">
+        <v>72.38568142763826</v>
+      </c>
+      <c r="D6">
+        <v>72.71568142763826</v>
+      </c>
+      <c r="E6">
+        <v>-40.27999999999999</v>
+      </c>
+      <c r="F6">
+        <v>3.02</v>
+      </c>
+      <c r="G6">
+        <v>2.69</v>
+      </c>
+      <c r="H6">
+        <v>32.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>18.875</v>
+      </c>
+      <c r="K6">
+        <v>5.1</v>
+      </c>
+      <c r="L6">
+        <v>13.775</v>
+      </c>
+      <c r="M6">
+        <v>0.134994</v>
+      </c>
+      <c r="N6">
+        <v>13.640006</v>
+      </c>
+      <c r="O6">
+        <v>2.0460009</v>
+      </c>
+      <c r="P6">
+        <v>11.5940051</v>
+      </c>
+      <c r="Q6">
+        <v>16.6940051</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0952828251895015</v>
+      </c>
+      <c r="T6">
+        <v>0.9675652985668939</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.037995</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>102.0415722180245</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.0929014359562948</v>
+      </c>
+      <c r="C7">
+        <v>71.69412233178798</v>
+      </c>
+      <c r="D7">
+        <v>72.77912233178799</v>
+      </c>
+      <c r="E7">
+        <v>-39.525</v>
+      </c>
+      <c r="F7">
+        <v>3.775</v>
+      </c>
+      <c r="G7">
+        <v>2.69</v>
+      </c>
+      <c r="H7">
+        <v>32.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>18.875</v>
+      </c>
+      <c r="K7">
+        <v>5.1</v>
+      </c>
+      <c r="L7">
+        <v>13.775</v>
+      </c>
+      <c r="M7">
+        <v>0.1687425</v>
+      </c>
+      <c r="N7">
+        <v>13.6062575</v>
+      </c>
+      <c r="O7">
+        <v>2.040938625</v>
+      </c>
+      <c r="P7">
+        <v>11.565318875</v>
+      </c>
+      <c r="Q7">
+        <v>16.665318875</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09579124837504716</v>
+      </c>
+      <c r="T7">
+        <v>0.9762747182828937</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.037995</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>81.63325777441959</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09281155973066815</v>
+      </c>
+      <c r="C8">
+        <v>71.00267403082277</v>
+      </c>
+      <c r="D8">
+        <v>72.84267403082278</v>
+      </c>
+      <c r="E8">
+        <v>-38.77</v>
+      </c>
+      <c r="F8">
+        <v>4.53</v>
+      </c>
+      <c r="G8">
+        <v>2.69</v>
+      </c>
+      <c r="H8">
+        <v>32.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>18.875</v>
+      </c>
+      <c r="K8">
+        <v>5.1</v>
+      </c>
+      <c r="L8">
+        <v>13.775</v>
+      </c>
+      <c r="M8">
+        <v>0.202491</v>
+      </c>
+      <c r="N8">
+        <v>13.572509</v>
+      </c>
+      <c r="O8">
+        <v>2.03587635</v>
+      </c>
+      <c r="P8">
+        <v>11.53663265</v>
+      </c>
+      <c r="Q8">
+        <v>16.63663265</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09631048907517889</v>
+      </c>
+      <c r="T8">
+        <v>0.9851694448013615</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.037995</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>68.02771481201633</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09272168350504151</v>
+      </c>
+      <c r="C9">
+        <v>70.31133681523902</v>
+      </c>
+      <c r="D9">
+        <v>72.90633681523902</v>
+      </c>
+      <c r="E9">
+        <v>-38.015</v>
+      </c>
+      <c r="F9">
+        <v>5.285</v>
+      </c>
+      <c r="G9">
+        <v>2.69</v>
+      </c>
+      <c r="H9">
+        <v>32.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>18.875</v>
+      </c>
+      <c r="K9">
+        <v>5.1</v>
+      </c>
+      <c r="L9">
+        <v>13.775</v>
+      </c>
+      <c r="M9">
+        <v>0.2362395</v>
+      </c>
+      <c r="N9">
+        <v>13.5387605</v>
+      </c>
+      <c r="O9">
+        <v>2.030814075</v>
+      </c>
+      <c r="P9">
+        <v>11.507946425</v>
+      </c>
+      <c r="Q9">
+        <v>16.607946425</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09684089624198013</v>
+      </c>
+      <c r="T9">
+        <v>0.9942554557610868</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.037995</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>58.30946983887114</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09263180727941488</v>
+      </c>
+      <c r="C10">
+        <v>69.62011097654947</v>
+      </c>
+      <c r="D10">
+        <v>72.97011097654948</v>
+      </c>
+      <c r="E10">
+        <v>-37.26</v>
+      </c>
+      <c r="F10">
+        <v>6.04</v>
+      </c>
+      <c r="G10">
+        <v>2.69</v>
+      </c>
+      <c r="H10">
+        <v>32.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>18.875</v>
+      </c>
+      <c r="K10">
+        <v>5.1</v>
+      </c>
+      <c r="L10">
+        <v>13.775</v>
+      </c>
+      <c r="M10">
+        <v>0.269988</v>
+      </c>
+      <c r="N10">
+        <v>13.505012</v>
+      </c>
+      <c r="O10">
+        <v>2.0257518</v>
+      </c>
+      <c r="P10">
+        <v>11.4792602</v>
+      </c>
+      <c r="Q10">
+        <v>16.5792602</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09738283399936398</v>
+      </c>
+      <c r="T10">
+        <v>1.003538988698197</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.037995</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>51.02078610901226</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09254193105378823</v>
+      </c>
+      <c r="C11">
+        <v>68.92899680728792</v>
+      </c>
+      <c r="D11">
+        <v>73.03399680728792</v>
+      </c>
+      <c r="E11">
+        <v>-36.505</v>
+      </c>
+      <c r="F11">
+        <v>6.795</v>
+      </c>
+      <c r="G11">
+        <v>2.69</v>
+      </c>
+      <c r="H11">
+        <v>32.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>18.875</v>
+      </c>
+      <c r="K11">
+        <v>5.1</v>
+      </c>
+      <c r="L11">
+        <v>13.775</v>
+      </c>
+      <c r="M11">
+        <v>0.3037365</v>
+      </c>
+      <c r="N11">
+        <v>13.4712635</v>
+      </c>
+      <c r="O11">
+        <v>2.020689525</v>
+      </c>
+      <c r="P11">
+        <v>11.450573975</v>
+      </c>
+      <c r="Q11">
+        <v>16.550573975</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09793668247669036</v>
+      </c>
+      <c r="T11">
+        <v>1.013026555326233</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.037995</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>45.35180987467756</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09245205482816159</v>
+      </c>
+      <c r="C12">
+        <v>68.23799460101334</v>
+      </c>
+      <c r="D12">
+        <v>73.09799460101334</v>
+      </c>
+      <c r="E12">
+        <v>-35.75</v>
+      </c>
+      <c r="F12">
+        <v>7.550000000000001</v>
+      </c>
+      <c r="G12">
+        <v>2.69</v>
+      </c>
+      <c r="H12">
+        <v>32.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>18.875</v>
+      </c>
+      <c r="K12">
+        <v>5.1</v>
+      </c>
+      <c r="L12">
+        <v>13.775</v>
+      </c>
+      <c r="M12">
+        <v>0.337485</v>
+      </c>
+      <c r="N12">
+        <v>13.437515</v>
+      </c>
+      <c r="O12">
+        <v>2.01562725</v>
+      </c>
+      <c r="P12">
+        <v>11.42188775</v>
+      </c>
+      <c r="Q12">
+        <v>16.52188775</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09850283869795733</v>
+      </c>
+      <c r="T12">
+        <v>1.022724956768226</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.037995</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>40.8166288872098</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09236217860253494</v>
+      </c>
+      <c r="C13">
+        <v>67.54710465231469</v>
+      </c>
+      <c r="D13">
+        <v>73.16210465231468</v>
+      </c>
+      <c r="E13">
+        <v>-34.995</v>
+      </c>
+      <c r="F13">
+        <v>8.305</v>
+      </c>
+      <c r="G13">
+        <v>2.69</v>
+      </c>
+      <c r="H13">
+        <v>32.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>18.875</v>
+      </c>
+      <c r="K13">
+        <v>5.1</v>
+      </c>
+      <c r="L13">
+        <v>13.775</v>
+      </c>
+      <c r="M13">
+        <v>0.3712335</v>
+      </c>
+      <c r="N13">
+        <v>13.4037665</v>
+      </c>
+      <c r="O13">
+        <v>2.010564975</v>
+      </c>
+      <c r="P13">
+        <v>11.393201525</v>
+      </c>
+      <c r="Q13">
+        <v>16.493201525</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09908171753093814</v>
+      </c>
+      <c r="T13">
+        <v>1.032641299815656</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.037995</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>37.10602626109982</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09227230237690832</v>
+      </c>
+      <c r="C14">
+        <v>66.85632725681519</v>
+      </c>
+      <c r="D14">
+        <v>73.2263272568152</v>
+      </c>
+      <c r="E14">
+        <v>-34.23999999999999</v>
+      </c>
+      <c r="F14">
+        <v>9.06</v>
+      </c>
+      <c r="G14">
+        <v>2.69</v>
+      </c>
+      <c r="H14">
+        <v>32.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>18.875</v>
+      </c>
+      <c r="K14">
+        <v>5.1</v>
+      </c>
+      <c r="L14">
+        <v>13.775</v>
+      </c>
+      <c r="M14">
+        <v>0.4049820000000001</v>
+      </c>
+      <c r="N14">
+        <v>13.370018</v>
+      </c>
+      <c r="O14">
+        <v>2.0055027</v>
+      </c>
+      <c r="P14">
+        <v>11.3645153</v>
+      </c>
+      <c r="Q14">
+        <v>16.4645153</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09967375270103218</v>
+      </c>
+      <c r="T14">
+        <v>1.042783014295983</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.037995</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>34.01385740600816</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09218242615128167</v>
+      </c>
+      <c r="C15">
+        <v>66.16566271117716</v>
+      </c>
+      <c r="D15">
+        <v>73.29066271117716</v>
+      </c>
+      <c r="E15">
+        <v>-33.485</v>
+      </c>
+      <c r="F15">
+        <v>9.815</v>
+      </c>
+      <c r="G15">
+        <v>2.69</v>
+      </c>
+      <c r="H15">
+        <v>32.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>18.875</v>
+      </c>
+      <c r="K15">
+        <v>5.1</v>
+      </c>
+      <c r="L15">
+        <v>13.775</v>
+      </c>
+      <c r="M15">
+        <v>0.4387305</v>
+      </c>
+      <c r="N15">
+        <v>13.3362695</v>
+      </c>
+      <c r="O15">
+        <v>2.000440425</v>
+      </c>
+      <c r="P15">
+        <v>11.335829075</v>
+      </c>
+      <c r="Q15">
+        <v>16.435829075</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1002793978750364</v>
+      </c>
+      <c r="T15">
+        <v>1.053157871637926</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.037995</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>31.39740683631523</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09209254992565502</v>
+      </c>
+      <c r="C16">
+        <v>65.4751113131062</v>
+      </c>
+      <c r="D16">
+        <v>73.35511131310619</v>
+      </c>
+      <c r="E16">
+        <v>-32.73</v>
+      </c>
+      <c r="F16">
+        <v>10.57</v>
+      </c>
+      <c r="G16">
+        <v>2.69</v>
+      </c>
+      <c r="H16">
+        <v>32.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>18.875</v>
+      </c>
+      <c r="K16">
+        <v>5.1</v>
+      </c>
+      <c r="L16">
+        <v>13.775</v>
+      </c>
+      <c r="M16">
+        <v>0.472479</v>
+      </c>
+      <c r="N16">
+        <v>13.302521</v>
+      </c>
+      <c r="O16">
+        <v>1.99537815</v>
+      </c>
+      <c r="P16">
+        <v>11.30714285</v>
+      </c>
+      <c r="Q16">
+        <v>16.40714285</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1008991278205291</v>
+      </c>
+      <c r="T16">
+        <v>1.063774004732008</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.037995</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>29.15473491943557</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09200267370002838</v>
+      </c>
+      <c r="C17">
+        <v>64.78467336135607</v>
+      </c>
+      <c r="D17">
+        <v>73.41967336135608</v>
+      </c>
+      <c r="E17">
+        <v>-31.975</v>
+      </c>
+      <c r="F17">
+        <v>11.325</v>
+      </c>
+      <c r="G17">
+        <v>2.69</v>
+      </c>
+      <c r="H17">
+        <v>32.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>18.875</v>
+      </c>
+      <c r="K17">
+        <v>5.1</v>
+      </c>
+      <c r="L17">
+        <v>13.775</v>
+      </c>
+      <c r="M17">
+        <v>0.5062275000000001</v>
+      </c>
+      <c r="N17">
+        <v>13.2687725</v>
+      </c>
+      <c r="O17">
+        <v>1.990315875</v>
+      </c>
+      <c r="P17">
+        <v>11.278456625</v>
+      </c>
+      <c r="Q17">
+        <v>16.378456625</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1015334396470922</v>
+      </c>
+      <c r="T17">
+        <v>1.074639929193009</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.037995</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>27.21108592480653</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09191279747440173</v>
+      </c>
+      <c r="C18">
+        <v>64.09434915573328</v>
+      </c>
+      <c r="D18">
+        <v>73.48434915573328</v>
+      </c>
+      <c r="E18">
+        <v>-31.22</v>
+      </c>
+      <c r="F18">
+        <v>12.08</v>
+      </c>
+      <c r="G18">
+        <v>2.69</v>
+      </c>
+      <c r="H18">
+        <v>32.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>18.875</v>
+      </c>
+      <c r="K18">
+        <v>5.1</v>
+      </c>
+      <c r="L18">
+        <v>13.775</v>
+      </c>
+      <c r="M18">
+        <v>0.539976</v>
+      </c>
+      <c r="N18">
+        <v>13.235024</v>
+      </c>
+      <c r="O18">
+        <v>1.9852536</v>
+      </c>
+      <c r="P18">
+        <v>11.2497704</v>
+      </c>
+      <c r="Q18">
+        <v>16.3497704</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1021828541361925</v>
+      </c>
+      <c r="T18">
+        <v>1.085764566141177</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.037995</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>25.51039305450613</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.0918229212487751</v>
+      </c>
+      <c r="C19">
+        <v>63.4041389971016</v>
+      </c>
+      <c r="D19">
+        <v>73.54913899710161</v>
+      </c>
+      <c r="E19">
+        <v>-30.465</v>
+      </c>
+      <c r="F19">
+        <v>12.835</v>
+      </c>
+      <c r="G19">
+        <v>2.69</v>
+      </c>
+      <c r="H19">
+        <v>32.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>18.875</v>
+      </c>
+      <c r="K19">
+        <v>5.1</v>
+      </c>
+      <c r="L19">
+        <v>13.775</v>
+      </c>
+      <c r="M19">
+        <v>0.5737245000000001</v>
+      </c>
+      <c r="N19">
+        <v>13.2012755</v>
+      </c>
+      <c r="O19">
+        <v>1.980191325</v>
+      </c>
+      <c r="P19">
+        <v>11.221084175</v>
+      </c>
+      <c r="Q19">
+        <v>16.321084175</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1028479171671989</v>
+      </c>
+      <c r="T19">
+        <v>1.097157266630264</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.037995</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>24.0097816983587</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09173304502314845</v>
+      </c>
+      <c r="C20">
+        <v>62.71404318738688</v>
+      </c>
+      <c r="D20">
+        <v>73.61404318738688</v>
+      </c>
+      <c r="E20">
+        <v>-29.71</v>
+      </c>
+      <c r="F20">
+        <v>13.59</v>
+      </c>
+      <c r="G20">
+        <v>2.69</v>
+      </c>
+      <c r="H20">
+        <v>32.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>18.875</v>
+      </c>
+      <c r="K20">
+        <v>5.1</v>
+      </c>
+      <c r="L20">
+        <v>13.775</v>
+      </c>
+      <c r="M20">
+        <v>0.607473</v>
+      </c>
+      <c r="N20">
+        <v>13.167527</v>
+      </c>
+      <c r="O20">
+        <v>1.97512905</v>
+      </c>
+      <c r="P20">
+        <v>11.19239795</v>
+      </c>
+      <c r="Q20">
+        <v>16.29239795</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.103529201247742</v>
+      </c>
+      <c r="T20">
+        <v>1.108827837862988</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.037995</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>22.67590493733878</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09164316879752182</v>
+      </c>
+      <c r="C21">
+        <v>62.02406202958156</v>
+      </c>
+      <c r="D21">
+        <v>73.67906202958156</v>
+      </c>
+      <c r="E21">
+        <v>-28.955</v>
+      </c>
+      <c r="F21">
+        <v>14.345</v>
+      </c>
+      <c r="G21">
+        <v>2.69</v>
+      </c>
+      <c r="H21">
+        <v>32.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>18.875</v>
+      </c>
+      <c r="K21">
+        <v>5.1</v>
+      </c>
+      <c r="L21">
+        <v>13.775</v>
+      </c>
+      <c r="M21">
+        <v>0.6412215000000001</v>
+      </c>
+      <c r="N21">
+        <v>13.1337785</v>
+      </c>
+      <c r="O21">
+        <v>1.970066775</v>
+      </c>
+      <c r="P21">
+        <v>11.163711725</v>
+      </c>
+      <c r="Q21">
+        <v>16.263711725</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1042273071574343</v>
+      </c>
+      <c r="T21">
+        <v>1.120786571348372</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.037995</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>21.48243625642621</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09155329257189518</v>
+      </c>
+      <c r="C22">
+        <v>61.33419582774957</v>
+      </c>
+      <c r="D22">
+        <v>73.74419582774958</v>
+      </c>
+      <c r="E22">
+        <v>-28.2</v>
+      </c>
+      <c r="F22">
+        <v>15.1</v>
+      </c>
+      <c r="G22">
+        <v>2.69</v>
+      </c>
+      <c r="H22">
+        <v>32.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>18.875</v>
+      </c>
+      <c r="K22">
+        <v>5.1</v>
+      </c>
+      <c r="L22">
+        <v>13.775</v>
+      </c>
+      <c r="M22">
+        <v>0.6749700000000001</v>
+      </c>
+      <c r="N22">
+        <v>13.10003</v>
+      </c>
+      <c r="O22">
+        <v>1.9650045</v>
+      </c>
+      <c r="P22">
+        <v>11.1350255</v>
+      </c>
+      <c r="Q22">
+        <v>16.2350255</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.104942865714869</v>
+      </c>
+      <c r="T22">
+        <v>1.13304427317089</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.037995</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>20.4083144436049</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09146341634626852</v>
+      </c>
+      <c r="C23">
+        <v>60.64444488703098</v>
+      </c>
+      <c r="D23">
+        <v>73.80944488703098</v>
+      </c>
+      <c r="E23">
+        <v>-27.445</v>
+      </c>
+      <c r="F23">
+        <v>15.855</v>
+      </c>
+      <c r="G23">
+        <v>2.69</v>
+      </c>
+      <c r="H23">
+        <v>32.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>18.875</v>
+      </c>
+      <c r="K23">
+        <v>5.1</v>
+      </c>
+      <c r="L23">
+        <v>13.775</v>
+      </c>
+      <c r="M23">
+        <v>0.7087185</v>
+      </c>
+      <c r="N23">
+        <v>13.0662815</v>
+      </c>
+      <c r="O23">
+        <v>1.959942225</v>
+      </c>
+      <c r="P23">
+        <v>11.106339275</v>
+      </c>
+      <c r="Q23">
+        <v>16.206339275</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1056765396788209</v>
+      </c>
+      <c r="T23">
+        <v>1.145612296558535</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.037995</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>19.43648994629038</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09137354012064189</v>
+      </c>
+      <c r="C24">
+        <v>59.95480951364669</v>
+      </c>
+      <c r="D24">
+        <v>73.8748095136467</v>
+      </c>
+      <c r="E24">
+        <v>-26.69</v>
+      </c>
+      <c r="F24">
+        <v>16.61</v>
+      </c>
+      <c r="G24">
+        <v>2.69</v>
+      </c>
+      <c r="H24">
+        <v>32.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>18.875</v>
+      </c>
+      <c r="K24">
+        <v>5.1</v>
+      </c>
+      <c r="L24">
+        <v>13.775</v>
+      </c>
+      <c r="M24">
+        <v>0.742467</v>
+      </c>
+      <c r="N24">
+        <v>13.032533</v>
+      </c>
+      <c r="O24">
+        <v>1.95487995</v>
+      </c>
+      <c r="P24">
+        <v>11.07765305</v>
+      </c>
+      <c r="Q24">
+        <v>16.17765305</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1064290257956947</v>
+      </c>
+      <c r="T24">
+        <v>1.15850257695612</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.037995</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>18.55301313054991</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09128366389501526</v>
+      </c>
+      <c r="C25">
+        <v>59.26529001490338</v>
+      </c>
+      <c r="D25">
+        <v>73.94029001490338</v>
+      </c>
+      <c r="E25">
+        <v>-25.935</v>
+      </c>
+      <c r="F25">
+        <v>17.365</v>
+      </c>
+      <c r="G25">
+        <v>2.69</v>
+      </c>
+      <c r="H25">
+        <v>32.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>18.875</v>
+      </c>
+      <c r="K25">
+        <v>5.1</v>
+      </c>
+      <c r="L25">
+        <v>13.775</v>
+      </c>
+      <c r="M25">
+        <v>0.7762155000000002</v>
+      </c>
+      <c r="N25">
+        <v>12.9987845</v>
+      </c>
+      <c r="O25">
+        <v>1.949817675</v>
+      </c>
+      <c r="P25">
+        <v>11.048966825</v>
+      </c>
+      <c r="Q25">
+        <v>16.148966825</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1072010570065133</v>
+      </c>
+      <c r="T25">
+        <v>1.171727669831564</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.037995</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>17.74636038574339</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.0911937876693886</v>
+      </c>
+      <c r="C26">
+        <v>58.57588669919826</v>
+      </c>
+      <c r="D26">
+        <v>74.00588669919827</v>
+      </c>
+      <c r="E26">
+        <v>-25.18</v>
+      </c>
+      <c r="F26">
+        <v>18.12</v>
+      </c>
+      <c r="G26">
+        <v>2.69</v>
+      </c>
+      <c r="H26">
+        <v>32.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>18.875</v>
+      </c>
+      <c r="K26">
+        <v>5.1</v>
+      </c>
+      <c r="L26">
+        <v>13.775</v>
+      </c>
+      <c r="M26">
+        <v>0.8099640000000001</v>
+      </c>
+      <c r="N26">
+        <v>12.965036</v>
+      </c>
+      <c r="O26">
+        <v>1.9447554</v>
+      </c>
+      <c r="P26">
+        <v>11.0202806</v>
+      </c>
+      <c r="Q26">
+        <v>16.1202806</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1079934048281429</v>
+      </c>
+      <c r="T26">
+        <v>1.185300791466888</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.037995</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>17.00692870300408</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09110391144376195</v>
+      </c>
+      <c r="C27">
+        <v>57.88659987602385</v>
+      </c>
+      <c r="D27">
+        <v>74.07159987602385</v>
+      </c>
+      <c r="E27">
+        <v>-24.425</v>
+      </c>
+      <c r="F27">
+        <v>18.875</v>
+      </c>
+      <c r="G27">
+        <v>2.69</v>
+      </c>
+      <c r="H27">
+        <v>32.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>18.875</v>
+      </c>
+      <c r="K27">
+        <v>5.1</v>
+      </c>
+      <c r="L27">
+        <v>13.775</v>
+      </c>
+      <c r="M27">
+        <v>0.8437125000000001</v>
+      </c>
+      <c r="N27">
+        <v>12.9312875</v>
+      </c>
+      <c r="O27">
+        <v>1.939693125</v>
+      </c>
+      <c r="P27">
+        <v>10.991594375</v>
+      </c>
+      <c r="Q27">
+        <v>16.091594375</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1088068819250159</v>
+      </c>
+      <c r="T27">
+        <v>1.199235863012488</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.037995</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>16.32665155488392</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09101403521813532</v>
+      </c>
+      <c r="C28">
+        <v>57.19742985597289</v>
+      </c>
+      <c r="D28">
+        <v>74.13742985597288</v>
+      </c>
+      <c r="E28">
+        <v>-23.67</v>
+      </c>
+      <c r="F28">
+        <v>19.63</v>
+      </c>
+      <c r="G28">
+        <v>2.69</v>
+      </c>
+      <c r="H28">
+        <v>32.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>18.875</v>
+      </c>
+      <c r="K28">
+        <v>5.1</v>
+      </c>
+      <c r="L28">
+        <v>13.775</v>
+      </c>
+      <c r="M28">
+        <v>0.877461</v>
+      </c>
+      <c r="N28">
+        <v>12.897539</v>
+      </c>
+      <c r="O28">
+        <v>1.93463085</v>
+      </c>
+      <c r="P28">
+        <v>10.96290815</v>
+      </c>
+      <c r="Q28">
+        <v>16.06290815</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1096423448893721</v>
+      </c>
+      <c r="T28">
+        <v>1.213547558113374</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.037995</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>15.69870341815762</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09092415899250869</v>
+      </c>
+      <c r="C29">
+        <v>56.50837695074325</v>
+      </c>
+      <c r="D29">
+        <v>74.20337695074326</v>
+      </c>
+      <c r="E29">
+        <v>-22.915</v>
+      </c>
+      <c r="F29">
+        <v>20.385</v>
+      </c>
+      <c r="G29">
+        <v>2.69</v>
+      </c>
+      <c r="H29">
+        <v>32.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>18.875</v>
+      </c>
+      <c r="K29">
+        <v>5.1</v>
+      </c>
+      <c r="L29">
+        <v>13.775</v>
+      </c>
+      <c r="M29">
+        <v>0.9112095000000001</v>
+      </c>
+      <c r="N29">
+        <v>12.8637905</v>
+      </c>
+      <c r="O29">
+        <v>1.929568575</v>
+      </c>
+      <c r="P29">
+        <v>10.934221925</v>
+      </c>
+      <c r="Q29">
+        <v>16.034221925</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1105006972500119</v>
+      </c>
+      <c r="T29">
+        <v>1.228251354449901</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.037995</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>15.11726995822585</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09083428276688203</v>
+      </c>
+      <c r="C30">
+        <v>55.81944147314293</v>
+      </c>
+      <c r="D30">
+        <v>74.26944147314293</v>
+      </c>
+      <c r="E30">
+        <v>-22.16</v>
+      </c>
+      <c r="F30">
+        <v>21.14</v>
+      </c>
+      <c r="G30">
+        <v>2.69</v>
+      </c>
+      <c r="H30">
+        <v>32.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>18.875</v>
+      </c>
+      <c r="K30">
+        <v>5.1</v>
+      </c>
+      <c r="L30">
+        <v>13.775</v>
+      </c>
+      <c r="M30">
+        <v>0.9449580000000001</v>
+      </c>
+      <c r="N30">
+        <v>12.830042</v>
+      </c>
+      <c r="O30">
+        <v>1.9245063</v>
+      </c>
+      <c r="P30">
+        <v>10.9055357</v>
+      </c>
+      <c r="Q30">
+        <v>16.0055357</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1113828927317806</v>
+      </c>
+      <c r="T30">
+        <v>1.243363589573554</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.037995</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>14.57736745971779</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.0907444065412554</v>
+      </c>
+      <c r="C31">
+        <v>55.13062373709477</v>
+      </c>
+      <c r="D31">
+        <v>74.33562373709476</v>
+      </c>
+      <c r="E31">
+        <v>-21.405</v>
+      </c>
+      <c r="F31">
+        <v>21.895</v>
+      </c>
+      <c r="G31">
+        <v>2.69</v>
+      </c>
+      <c r="H31">
+        <v>32.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>18.875</v>
+      </c>
+      <c r="K31">
+        <v>5.1</v>
+      </c>
+      <c r="L31">
+        <v>13.775</v>
+      </c>
+      <c r="M31">
+        <v>0.9787065</v>
+      </c>
+      <c r="N31">
+        <v>12.7962935</v>
+      </c>
+      <c r="O31">
+        <v>1.919444025</v>
+      </c>
+      <c r="P31">
+        <v>10.876849475</v>
+      </c>
+      <c r="Q31">
+        <v>15.976849475</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1122899387905006</v>
+      </c>
+      <c r="T31">
+        <v>1.258901521461253</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.037995</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>14.07469961627924</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09065453031562876</v>
+      </c>
+      <c r="C32">
+        <v>54.44192405764166</v>
+      </c>
+      <c r="D32">
+        <v>74.40192405764166</v>
+      </c>
+      <c r="E32">
+        <v>-20.65</v>
+      </c>
+      <c r="F32">
+        <v>22.65</v>
+      </c>
+      <c r="G32">
+        <v>2.69</v>
+      </c>
+      <c r="H32">
+        <v>32.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>18.875</v>
+      </c>
+      <c r="K32">
+        <v>5.1</v>
+      </c>
+      <c r="L32">
+        <v>13.775</v>
+      </c>
+      <c r="M32">
+        <v>1.012455</v>
+      </c>
+      <c r="N32">
+        <v>12.762545</v>
+      </c>
+      <c r="O32">
+        <v>1.91438175</v>
+      </c>
+      <c r="P32">
+        <v>10.84816325</v>
+      </c>
+      <c r="Q32">
+        <v>15.94816325</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1132229004508982</v>
+      </c>
+      <c r="T32">
+        <v>1.274883394260029</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.037995</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>13.60554296240327</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.0905646540900021</v>
+      </c>
+      <c r="C33">
+        <v>53.75334275095143</v>
+      </c>
+      <c r="D33">
+        <v>74.46834275095144</v>
+      </c>
+      <c r="E33">
+        <v>-19.895</v>
+      </c>
+      <c r="F33">
+        <v>23.405</v>
+      </c>
+      <c r="G33">
+        <v>2.69</v>
+      </c>
+      <c r="H33">
+        <v>32.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>18.875</v>
+      </c>
+      <c r="K33">
+        <v>5.1</v>
+      </c>
+      <c r="L33">
+        <v>13.775</v>
+      </c>
+      <c r="M33">
+        <v>1.0462035</v>
+      </c>
+      <c r="N33">
+        <v>12.7287965</v>
+      </c>
+      <c r="O33">
+        <v>1.909319475</v>
+      </c>
+      <c r="P33">
+        <v>10.819477025</v>
+      </c>
+      <c r="Q33">
+        <v>15.919477025</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1141829044782639</v>
+      </c>
+      <c r="T33">
+        <v>1.291328509748625</v>
+      </c>
+      <c r="U33">
+        <v>0.0447</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.037995</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>13.1666544797451</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09077397786437545</v>
+      </c>
+      <c r="C34">
+        <v>52.84383525039885</v>
+      </c>
+      <c r="D34">
+        <v>74.31383525039885</v>
+      </c>
+      <c r="E34">
+        <v>-19.14</v>
+      </c>
+      <c r="F34">
+        <v>24.16</v>
+      </c>
+      <c r="G34">
+        <v>2.69</v>
+      </c>
+      <c r="H34">
+        <v>32.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>18.875</v>
+      </c>
+      <c r="K34">
+        <v>5.1</v>
+      </c>
+      <c r="L34">
+        <v>13.775</v>
+      </c>
+      <c r="M34">
+        <v>1.106528</v>
+      </c>
+      <c r="N34">
+        <v>12.668472</v>
+      </c>
+      <c r="O34">
+        <v>1.9002708</v>
+      </c>
+      <c r="P34">
+        <v>10.7682012</v>
+      </c>
+      <c r="Q34">
+        <v>15.8682012</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1151711439181992</v>
+      </c>
+      <c r="T34">
+        <v>1.308257305104533</v>
+      </c>
+      <c r="U34">
+        <v>0.0458</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.03893</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>12.44884901240638</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09069345163874881</v>
+      </c>
+      <c r="C35">
+        <v>52.14819787856098</v>
+      </c>
+      <c r="D35">
+        <v>74.37319787856099</v>
+      </c>
+      <c r="E35">
+        <v>-18.38499999999999</v>
+      </c>
+      <c r="F35">
+        <v>24.915</v>
+      </c>
+      <c r="G35">
+        <v>2.69</v>
+      </c>
+      <c r="H35">
+        <v>32.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>18.875</v>
+      </c>
+      <c r="K35">
+        <v>5.1</v>
+      </c>
+      <c r="L35">
+        <v>13.775</v>
+      </c>
+      <c r="M35">
+        <v>1.141107</v>
+      </c>
+      <c r="N35">
+        <v>12.633893</v>
+      </c>
+      <c r="O35">
+        <v>1.89508395</v>
+      </c>
+      <c r="P35">
+        <v>10.73880905</v>
+      </c>
+      <c r="Q35">
+        <v>15.83880905</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1161888830429087</v>
+      </c>
+      <c r="T35">
+        <v>1.325691437635243</v>
+      </c>
+      <c r="U35">
+        <v>0.0458</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.03893</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>12.07161116354557</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09061292541312217</v>
+      </c>
+      <c r="C36">
+        <v>51.45265542145346</v>
+      </c>
+      <c r="D36">
+        <v>74.43265542145346</v>
+      </c>
+      <c r="E36">
+        <v>-17.63</v>
+      </c>
+      <c r="F36">
+        <v>25.67</v>
+      </c>
+      <c r="G36">
+        <v>2.69</v>
+      </c>
+      <c r="H36">
+        <v>32.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>18.875</v>
+      </c>
+      <c r="K36">
+        <v>5.1</v>
+      </c>
+      <c r="L36">
+        <v>13.775</v>
+      </c>
+      <c r="M36">
+        <v>1.175686</v>
+      </c>
+      <c r="N36">
+        <v>12.599314</v>
+      </c>
+      <c r="O36">
+        <v>1.8898971</v>
+      </c>
+      <c r="P36">
+        <v>10.7094169</v>
+      </c>
+      <c r="Q36">
+        <v>15.8094169</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1172374627471548</v>
+      </c>
+      <c r="T36">
+        <v>1.343653877212339</v>
+      </c>
+      <c r="U36">
+        <v>0.0458</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.03893</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>11.71656377638247</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09053239918749553</v>
+      </c>
+      <c r="C37">
+        <v>50.75720810689671</v>
+      </c>
+      <c r="D37">
+        <v>74.49220810689671</v>
+      </c>
+      <c r="E37">
+        <v>-16.87499999999999</v>
+      </c>
+      <c r="F37">
+        <v>26.425</v>
+      </c>
+      <c r="G37">
+        <v>2.69</v>
+      </c>
+      <c r="H37">
+        <v>32.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>18.875</v>
+      </c>
+      <c r="K37">
+        <v>5.1</v>
+      </c>
+      <c r="L37">
+        <v>13.775</v>
+      </c>
+      <c r="M37">
+        <v>1.210265</v>
+      </c>
+      <c r="N37">
+        <v>12.564735</v>
+      </c>
+      <c r="O37">
+        <v>1.88471025</v>
+      </c>
+      <c r="P37">
+        <v>10.68002475</v>
+      </c>
+      <c r="Q37">
+        <v>15.78002475</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1183183064423008</v>
+      </c>
+      <c r="T37">
+        <v>1.362169007237961</v>
+      </c>
+      <c r="U37">
+        <v>0.0458</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.03893</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>11.38180481134297</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.09045187296186889</v>
+      </c>
+      <c r="C38">
+        <v>50.06185616344087</v>
+      </c>
+      <c r="D38">
+        <v>74.55185616344087</v>
+      </c>
+      <c r="E38">
+        <v>-16.12</v>
+      </c>
+      <c r="F38">
+        <v>27.18</v>
+      </c>
+      <c r="G38">
+        <v>2.69</v>
+      </c>
+      <c r="H38">
+        <v>32.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>18.875</v>
+      </c>
+      <c r="K38">
+        <v>5.1</v>
+      </c>
+      <c r="L38">
+        <v>13.775</v>
+      </c>
+      <c r="M38">
+        <v>1.244844</v>
+      </c>
+      <c r="N38">
+        <v>12.530156</v>
+      </c>
+      <c r="O38">
+        <v>1.8795234</v>
+      </c>
+      <c r="P38">
+        <v>10.6506326</v>
+      </c>
+      <c r="Q38">
+        <v>15.7506326</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1194329265029201</v>
+      </c>
+      <c r="T38">
+        <v>1.381262735076884</v>
+      </c>
+      <c r="U38">
+        <v>0.0458</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.03893</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>11.06564356658344</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09037134673624227</v>
+      </c>
+      <c r="C39">
+        <v>49.36659982036872</v>
+      </c>
+      <c r="D39">
+        <v>74.61159982036872</v>
+      </c>
+      <c r="E39">
+        <v>-15.365</v>
+      </c>
+      <c r="F39">
+        <v>27.935</v>
+      </c>
+      <c r="G39">
+        <v>2.69</v>
+      </c>
+      <c r="H39">
+        <v>32.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>18.875</v>
+      </c>
+      <c r="K39">
+        <v>5.1</v>
+      </c>
+      <c r="L39">
+        <v>13.775</v>
+      </c>
+      <c r="M39">
+        <v>1.279423</v>
+      </c>
+      <c r="N39">
+        <v>12.495577</v>
+      </c>
+      <c r="O39">
+        <v>1.87433655</v>
+      </c>
+      <c r="P39">
+        <v>10.62124045</v>
+      </c>
+      <c r="Q39">
+        <v>15.72124045</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1205829313273687</v>
+      </c>
+      <c r="T39">
+        <v>1.400962613005931</v>
+      </c>
+      <c r="U39">
+        <v>0.0458</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.03893</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>10.76657211883795</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09029082051061561</v>
+      </c>
+      <c r="C40">
+        <v>48.67143930769855</v>
+      </c>
+      <c r="D40">
+        <v>74.67143930769855</v>
+      </c>
+      <c r="E40">
+        <v>-14.61</v>
+      </c>
+      <c r="F40">
+        <v>28.69</v>
+      </c>
+      <c r="G40">
+        <v>2.69</v>
+      </c>
+      <c r="H40">
+        <v>32.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>18.875</v>
+      </c>
+      <c r="K40">
+        <v>5.1</v>
+      </c>
+      <c r="L40">
+        <v>13.775</v>
+      </c>
+      <c r="M40">
+        <v>1.314002</v>
+      </c>
+      <c r="N40">
+        <v>12.460998</v>
+      </c>
+      <c r="O40">
+        <v>1.8691497</v>
+      </c>
+      <c r="P40">
+        <v>10.5918483</v>
+      </c>
+      <c r="Q40">
+        <v>15.6918483</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1217700330816381</v>
+      </c>
+      <c r="T40">
+        <v>1.421297970868173</v>
+      </c>
+      <c r="U40">
+        <v>0.0458</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.03893</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>10.48324127360537</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.09021029428498897</v>
+      </c>
+      <c r="C41">
+        <v>47.97637485618719</v>
+      </c>
+      <c r="D41">
+        <v>74.73137485618719</v>
+      </c>
+      <c r="E41">
+        <v>-13.855</v>
+      </c>
+      <c r="F41">
+        <v>29.445</v>
+      </c>
+      <c r="G41">
+        <v>2.69</v>
+      </c>
+      <c r="H41">
+        <v>32.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>18.875</v>
+      </c>
+      <c r="K41">
+        <v>5.1</v>
+      </c>
+      <c r="L41">
+        <v>13.775</v>
+      </c>
+      <c r="M41">
+        <v>1.348581</v>
+      </c>
+      <c r="N41">
+        <v>12.426419</v>
+      </c>
+      <c r="O41">
+        <v>1.86396285</v>
+      </c>
+      <c r="P41">
+        <v>10.56245615</v>
+      </c>
+      <c r="Q41">
+        <v>15.66245615</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1229960562049</v>
+      </c>
+      <c r="T41">
+        <v>1.442300061775079</v>
+      </c>
+      <c r="U41">
+        <v>0.0458</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.03893</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>10.21444021530779</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.09012976805936233</v>
+      </c>
+      <c r="C42">
+        <v>47.28140669733288</v>
+      </c>
+      <c r="D42">
+        <v>74.79140669733289</v>
+      </c>
+      <c r="E42">
+        <v>-13.09999999999999</v>
+      </c>
+      <c r="F42">
+        <v>30.2</v>
+      </c>
+      <c r="G42">
+        <v>2.69</v>
+      </c>
+      <c r="H42">
+        <v>32.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>18.875</v>
+      </c>
+      <c r="K42">
+        <v>5.1</v>
+      </c>
+      <c r="L42">
+        <v>13.775</v>
+      </c>
+      <c r="M42">
+        <v>1.38316</v>
+      </c>
+      <c r="N42">
+        <v>12.39184</v>
+      </c>
+      <c r="O42">
+        <v>1.858776</v>
+      </c>
+      <c r="P42">
+        <v>10.533064</v>
+      </c>
+      <c r="Q42">
+        <v>15.633064</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1242629467656039</v>
+      </c>
+      <c r="T42">
+        <v>1.464002222378882</v>
+      </c>
+      <c r="U42">
+        <v>0.0458</v>
+      </c>
+      <c r="V42">
+        <v>0.15</v>
+      </c>
+      <c r="W42">
+        <v>0.03893</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>9.959079209925099</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09081594183373569</v>
+      </c>
+      <c r="C43">
+        <v>46.0179376357376</v>
+      </c>
+      <c r="D43">
+        <v>74.2829376357376</v>
+      </c>
+      <c r="E43">
+        <v>-12.345</v>
+      </c>
+      <c r="F43">
+        <v>30.955</v>
+      </c>
+      <c r="G43">
+        <v>2.69</v>
+      </c>
+      <c r="H43">
+        <v>32.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>18.875</v>
+      </c>
+      <c r="K43">
+        <v>5.1</v>
+      </c>
+      <c r="L43">
+        <v>13.775</v>
+      </c>
+      <c r="M43">
+        <v>1.48584</v>
+      </c>
+      <c r="N43">
+        <v>12.28916</v>
+      </c>
+      <c r="O43">
+        <v>1.843374</v>
+      </c>
+      <c r="P43">
+        <v>10.445786</v>
+      </c>
+      <c r="Q43">
+        <v>15.545786</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1255727827690435</v>
+      </c>
+      <c r="T43">
+        <v>1.48644004944383</v>
+      </c>
+      <c r="U43">
+        <v>0.048</v>
+      </c>
+      <c r="V43">
+        <v>0.15</v>
+      </c>
+      <c r="W43">
+        <v>0.0408</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>9.270850158832715</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09075411560810905</v>
+      </c>
+      <c r="C44">
+        <v>45.30846857771451</v>
+      </c>
+      <c r="D44">
+        <v>74.3284685777145</v>
+      </c>
+      <c r="E44">
+        <v>-11.59</v>
+      </c>
+      <c r="F44">
+        <v>31.71</v>
+      </c>
+      <c r="G44">
+        <v>2.69</v>
+      </c>
+      <c r="H44">
+        <v>32.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>18.875</v>
+      </c>
+      <c r="K44">
+        <v>5.1</v>
+      </c>
+      <c r="L44">
+        <v>13.775</v>
+      </c>
+      <c r="M44">
+        <v>1.52208</v>
+      </c>
+      <c r="N44">
+        <v>12.25292</v>
+      </c>
+      <c r="O44">
+        <v>1.837938</v>
+      </c>
+      <c r="P44">
+        <v>10.414982</v>
+      </c>
+      <c r="Q44">
+        <v>15.514982</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1269277855312225</v>
+      </c>
+      <c r="T44">
+        <v>1.509651594683432</v>
+      </c>
+      <c r="U44">
+        <v>0.048</v>
+      </c>
+      <c r="V44">
+        <v>0.15</v>
+      </c>
+      <c r="W44">
+        <v>0.0408</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>9.050115631241459</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.09069228938248242</v>
+      </c>
+      <c r="C45">
+        <v>44.59905536934375</v>
+      </c>
+      <c r="D45">
+        <v>74.37405536934375</v>
+      </c>
+      <c r="E45">
+        <v>-10.835</v>
+      </c>
+      <c r="F45">
+        <v>32.465</v>
+      </c>
+      <c r="G45">
+        <v>2.69</v>
+      </c>
+      <c r="H45">
+        <v>32.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>18.875</v>
+      </c>
+      <c r="K45">
+        <v>5.1</v>
+      </c>
+      <c r="L45">
+        <v>13.775</v>
+      </c>
+      <c r="M45">
+        <v>1.55832</v>
+      </c>
+      <c r="N45">
+        <v>12.21668</v>
+      </c>
+      <c r="O45">
+        <v>1.832502</v>
+      </c>
+      <c r="P45">
+        <v>10.384178</v>
+      </c>
+      <c r="Q45">
+        <v>15.484178</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1283303322499691</v>
+      </c>
+      <c r="T45">
+        <v>1.53367758010688</v>
+      </c>
+      <c r="U45">
+        <v>0.048</v>
+      </c>
+      <c r="V45">
+        <v>0.15</v>
+      </c>
+      <c r="W45">
+        <v>0.0408</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>8.83964782586375</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.09063046315685577</v>
+      </c>
+      <c r="C46">
+        <v>43.88969811344873</v>
+      </c>
+      <c r="D46">
+        <v>74.41969811344873</v>
+      </c>
+      <c r="E46">
+        <v>-10.08</v>
+      </c>
+      <c r="F46">
+        <v>33.22</v>
+      </c>
+      <c r="G46">
+        <v>2.69</v>
+      </c>
+      <c r="H46">
+        <v>32.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>18.875</v>
+      </c>
+      <c r="K46">
+        <v>5.1</v>
+      </c>
+      <c r="L46">
+        <v>13.775</v>
+      </c>
+      <c r="M46">
+        <v>1.59456</v>
+      </c>
+      <c r="N46">
+        <v>12.18044</v>
+      </c>
+      <c r="O46">
+        <v>1.827066</v>
+      </c>
+      <c r="P46">
+        <v>10.353374</v>
+      </c>
+      <c r="Q46">
+        <v>15.453374</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1297829699229567</v>
+      </c>
+      <c r="T46">
+        <v>1.558561636438308</v>
+      </c>
+      <c r="U46">
+        <v>0.048</v>
+      </c>
+      <c r="V46">
+        <v>0.15</v>
+      </c>
+      <c r="W46">
+        <v>0.0408</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>8.638746738912303</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.09056863693122913</v>
+      </c>
+      <c r="C47">
+        <v>43.18039691310546</v>
+      </c>
+      <c r="D47">
+        <v>74.46539691310547</v>
+      </c>
+      <c r="E47">
+        <v>-9.324999999999996</v>
+      </c>
+      <c r="F47">
+        <v>33.975</v>
+      </c>
+      <c r="G47">
+        <v>2.69</v>
+      </c>
+      <c r="H47">
+        <v>32.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>18.875</v>
+      </c>
+      <c r="K47">
+        <v>5.1</v>
+      </c>
+      <c r="L47">
+        <v>13.775</v>
+      </c>
+      <c r="M47">
+        <v>1.6308</v>
+      </c>
+      <c r="N47">
+        <v>12.1442</v>
+      </c>
+      <c r="O47">
+        <v>1.82163</v>
+      </c>
+      <c r="P47">
+        <v>10.32257</v>
+      </c>
+      <c r="Q47">
+        <v>15.42257</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1312884307840529</v>
+      </c>
+      <c r="T47">
+        <v>1.584350567545424</v>
+      </c>
+      <c r="U47">
+        <v>0.048</v>
+      </c>
+      <c r="V47">
+        <v>0.15</v>
+      </c>
+      <c r="W47">
+        <v>0.0408</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>8.446774589158695</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.0905068107056025</v>
+      </c>
+      <c r="C48">
+        <v>42.47115187164323</v>
+      </c>
+      <c r="D48">
+        <v>74.51115187164324</v>
+      </c>
+      <c r="E48">
+        <v>-8.569999999999993</v>
+      </c>
+      <c r="F48">
+        <v>34.73</v>
+      </c>
+      <c r="G48">
+        <v>2.69</v>
+      </c>
+      <c r="H48">
+        <v>32.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>18.875</v>
+      </c>
+      <c r="K48">
+        <v>5.1</v>
+      </c>
+      <c r="L48">
+        <v>13.775</v>
+      </c>
+      <c r="M48">
+        <v>1.66704</v>
+      </c>
+      <c r="N48">
+        <v>12.10796</v>
+      </c>
+      <c r="O48">
+        <v>1.816194</v>
+      </c>
+      <c r="P48">
+        <v>10.291766</v>
+      </c>
+      <c r="Q48">
+        <v>15.391766</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1328496494548194</v>
+      </c>
+      <c r="T48">
+        <v>1.6110946442491</v>
+      </c>
+      <c r="U48">
+        <v>0.048</v>
+      </c>
+      <c r="V48">
+        <v>0.15</v>
+      </c>
+      <c r="W48">
+        <v>0.0408</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>8.263149054611766</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.09044498447997584</v>
+      </c>
+      <c r="C49">
+        <v>41.76196309264549</v>
+      </c>
+      <c r="D49">
+        <v>74.55696309264549</v>
+      </c>
+      <c r="E49">
+        <v>-7.814999999999998</v>
+      </c>
+      <c r="F49">
+        <v>35.485</v>
+      </c>
+      <c r="G49">
+        <v>2.69</v>
+      </c>
+      <c r="H49">
+        <v>32.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>18.875</v>
+      </c>
+      <c r="K49">
+        <v>5.1</v>
+      </c>
+      <c r="L49">
+        <v>13.775</v>
+      </c>
+      <c r="M49">
+        <v>1.70328</v>
+      </c>
+      <c r="N49">
+        <v>12.07172</v>
+      </c>
+      <c r="O49">
+        <v>1.810758</v>
+      </c>
+      <c r="P49">
+        <v>10.260962</v>
+      </c>
+      <c r="Q49">
+        <v>15.360962</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1344697820376903</v>
+      </c>
+      <c r="T49">
+        <v>1.638847931394425</v>
+      </c>
+      <c r="U49">
+        <v>0.048</v>
+      </c>
+      <c r="V49">
+        <v>0.15</v>
+      </c>
+      <c r="W49">
+        <v>0.0408</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>8.087337372598752</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.0903831582543492</v>
+      </c>
+      <c r="C50">
+        <v>41.05283067995054</v>
+      </c>
+      <c r="D50">
+        <v>74.60283067995054</v>
+      </c>
+      <c r="E50">
+        <v>-7.059999999999995</v>
+      </c>
+      <c r="F50">
+        <v>36.24</v>
+      </c>
+      <c r="G50">
+        <v>2.69</v>
+      </c>
+      <c r="H50">
+        <v>32.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>18.875</v>
+      </c>
+      <c r="K50">
+        <v>5.1</v>
+      </c>
+      <c r="L50">
+        <v>13.775</v>
+      </c>
+      <c r="M50">
+        <v>1.73952</v>
+      </c>
+      <c r="N50">
+        <v>12.03548</v>
+      </c>
+      <c r="O50">
+        <v>1.805322</v>
+      </c>
+      <c r="P50">
+        <v>10.230158</v>
+      </c>
+      <c r="Q50">
+        <v>15.330158</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.13615222741221</v>
+      </c>
+      <c r="T50">
+        <v>1.667668652660723</v>
+      </c>
+      <c r="U50">
+        <v>0.048</v>
+      </c>
+      <c r="V50">
+        <v>0.15</v>
+      </c>
+      <c r="W50">
+        <v>0.0408</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>7.918851177336276</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.09032133202872254</v>
+      </c>
+      <c r="C51">
+        <v>40.34375473765241</v>
+      </c>
+      <c r="D51">
+        <v>74.64875473765241</v>
+      </c>
+      <c r="E51">
+        <v>-6.305</v>
+      </c>
+      <c r="F51">
+        <v>36.995</v>
+      </c>
+      <c r="G51">
+        <v>2.69</v>
+      </c>
+      <c r="H51">
+        <v>32.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>18.875</v>
+      </c>
+      <c r="K51">
+        <v>5.1</v>
+      </c>
+      <c r="L51">
+        <v>13.775</v>
+      </c>
+      <c r="M51">
+        <v>1.77576</v>
+      </c>
+      <c r="N51">
+        <v>11.99924</v>
+      </c>
+      <c r="O51">
+        <v>1.799886</v>
+      </c>
+      <c r="P51">
+        <v>10.199354</v>
+      </c>
+      <c r="Q51">
+        <v>15.299354</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1379006510367109</v>
+      </c>
+      <c r="T51">
+        <v>1.697619598290405</v>
+      </c>
+      <c r="U51">
+        <v>0.048</v>
+      </c>
+      <c r="V51">
+        <v>0.15</v>
+      </c>
+      <c r="W51">
+        <v>0.0408</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>7.757241969635537</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.09089700580309591</v>
+      </c>
+      <c r="C52">
+        <v>39.16332381185724</v>
+      </c>
+      <c r="D52">
+        <v>74.22332381185724</v>
+      </c>
+      <c r="E52">
+        <v>-5.549999999999997</v>
+      </c>
+      <c r="F52">
+        <v>37.75</v>
+      </c>
+      <c r="G52">
+        <v>2.69</v>
+      </c>
+      <c r="H52">
+        <v>32.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>18.875</v>
+      </c>
+      <c r="K52">
+        <v>5.1</v>
+      </c>
+      <c r="L52">
+        <v>13.775</v>
+      </c>
+      <c r="M52">
+        <v>1.868625</v>
+      </c>
+      <c r="N52">
+        <v>11.906375</v>
+      </c>
+      <c r="O52">
+        <v>1.78595625</v>
+      </c>
+      <c r="P52">
+        <v>10.12041875</v>
+      </c>
+      <c r="Q52">
+        <v>15.22041875</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1397190116061918</v>
+      </c>
+      <c r="T52">
+        <v>1.728768581745275</v>
+      </c>
+      <c r="U52">
+        <v>0.0495</v>
+      </c>
+      <c r="V52">
+        <v>0.15</v>
+      </c>
+      <c r="W52">
+        <v>0.042075</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>7.371730550538498</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.09084792957746926</v>
+      </c>
+      <c r="C53">
+        <v>38.44440265888446</v>
+      </c>
+      <c r="D53">
+        <v>74.25940265888447</v>
+      </c>
+      <c r="E53">
+        <v>-4.794999999999995</v>
+      </c>
+      <c r="F53">
+        <v>38.505</v>
+      </c>
+      <c r="G53">
+        <v>2.69</v>
+      </c>
+      <c r="H53">
+        <v>32.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>18.875</v>
+      </c>
+      <c r="K53">
+        <v>5.1</v>
+      </c>
+      <c r="L53">
+        <v>13.775</v>
+      </c>
+      <c r="M53">
+        <v>1.9059975</v>
+      </c>
+      <c r="N53">
+        <v>11.8690025</v>
+      </c>
+      <c r="O53">
+        <v>1.780350375</v>
+      </c>
+      <c r="P53">
+        <v>10.088652125</v>
+      </c>
+      <c r="Q53">
+        <v>15.188652125</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1416115909744271</v>
+      </c>
+      <c r="T53">
+        <v>1.761188952279936</v>
+      </c>
+      <c r="U53">
+        <v>0.0495</v>
+      </c>
+      <c r="V53">
+        <v>0.15</v>
+      </c>
+      <c r="W53">
+        <v>0.042075</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>7.227186814253429</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.09079885335184262</v>
+      </c>
+      <c r="C54">
+        <v>37.72551659774461</v>
+      </c>
+      <c r="D54">
+        <v>74.29551659774461</v>
+      </c>
+      <c r="E54">
+        <v>-4.039999999999999</v>
+      </c>
+      <c r="F54">
+        <v>39.26</v>
+      </c>
+      <c r="G54">
+        <v>2.69</v>
+      </c>
+      <c r="H54">
+        <v>32.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>18.875</v>
+      </c>
+      <c r="K54">
+        <v>5.1</v>
+      </c>
+      <c r="L54">
+        <v>13.775</v>
+      </c>
+      <c r="M54">
+        <v>1.94337</v>
+      </c>
+      <c r="N54">
+        <v>11.83163</v>
+      </c>
+      <c r="O54">
+        <v>1.7747445</v>
+      </c>
+      <c r="P54">
+        <v>10.0568855</v>
+      </c>
+      <c r="Q54">
+        <v>15.1568855</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1435830278163388</v>
+      </c>
+      <c r="T54">
+        <v>1.794960171586874</v>
+      </c>
+      <c r="U54">
+        <v>0.0495</v>
+      </c>
+      <c r="V54">
+        <v>0.15</v>
+      </c>
+      <c r="W54">
+        <v>0.042075</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>7.088202452440863</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.09074977712621599</v>
+      </c>
+      <c r="C55">
+        <v>37.00666567966032</v>
+      </c>
+      <c r="D55">
+        <v>74.33166567966032</v>
+      </c>
+      <c r="E55">
+        <v>-3.284999999999997</v>
+      </c>
+      <c r="F55">
+        <v>40.015</v>
+      </c>
+      <c r="G55">
+        <v>2.69</v>
+      </c>
+      <c r="H55">
+        <v>32.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>18.875</v>
+      </c>
+      <c r="K55">
+        <v>5.1</v>
+      </c>
+      <c r="L55">
+        <v>13.775</v>
+      </c>
+      <c r="M55">
+        <v>1.9807425</v>
+      </c>
+      <c r="N55">
+        <v>11.7942575</v>
+      </c>
+      <c r="O55">
+        <v>1.769138625</v>
+      </c>
+      <c r="P55">
+        <v>10.025118875</v>
+      </c>
+      <c r="Q55">
+        <v>15.125118875</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1456383555876936</v>
+      </c>
+      <c r="T55">
+        <v>1.830168464055809</v>
+      </c>
+      <c r="U55">
+        <v>0.0495</v>
+      </c>
+      <c r="V55">
+        <v>0.15</v>
+      </c>
+      <c r="W55">
+        <v>0.042075</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>6.954462783526885</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.09070070090058935</v>
+      </c>
+      <c r="C56">
+        <v>36.28784995595398</v>
+      </c>
+      <c r="D56">
+        <v>74.36784995595399</v>
+      </c>
+      <c r="E56">
+        <v>-2.529999999999994</v>
+      </c>
+      <c r="F56">
+        <v>40.77</v>
+      </c>
+      <c r="G56">
+        <v>2.69</v>
+      </c>
+      <c r="H56">
+        <v>32.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>18.875</v>
+      </c>
+      <c r="K56">
+        <v>5.1</v>
+      </c>
+      <c r="L56">
+        <v>13.775</v>
+      </c>
+      <c r="M56">
+        <v>2.018115</v>
+      </c>
+      <c r="N56">
+        <v>11.756885</v>
+      </c>
+      <c r="O56">
+        <v>1.76353275</v>
+      </c>
+      <c r="P56">
+        <v>9.993352250000001</v>
+      </c>
+      <c r="Q56">
+        <v>15.09335225</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1477830454360638</v>
+      </c>
+      <c r="T56">
+        <v>1.866907551849481</v>
+      </c>
+      <c r="U56">
+        <v>0.0495</v>
+      </c>
+      <c r="V56">
+        <v>0.15</v>
+      </c>
+      <c r="W56">
+        <v>0.042075</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>6.825676435683794</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.0906516246749627</v>
+      </c>
+      <c r="C57">
+        <v>35.56906947804798</v>
+      </c>
+      <c r="D57">
+        <v>74.40406947804799</v>
+      </c>
+      <c r="E57">
+        <v>-1.774999999999991</v>
+      </c>
+      <c r="F57">
+        <v>41.52500000000001</v>
+      </c>
+      <c r="G57">
+        <v>2.69</v>
+      </c>
+      <c r="H57">
+        <v>32.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>18.875</v>
+      </c>
+      <c r="K57">
+        <v>5.1</v>
+      </c>
+      <c r="L57">
+        <v>13.775</v>
+      </c>
+      <c r="M57">
+        <v>2.0554875</v>
+      </c>
+      <c r="N57">
+        <v>11.7195125</v>
+      </c>
+      <c r="O57">
+        <v>1.757926875</v>
+      </c>
+      <c r="P57">
+        <v>9.961585625</v>
+      </c>
+      <c r="Q57">
+        <v>15.061585625</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1500230548332505</v>
+      </c>
+      <c r="T57">
+        <v>1.905279487989538</v>
+      </c>
+      <c r="U57">
+        <v>0.0495</v>
+      </c>
+      <c r="V57">
+        <v>0.15</v>
+      </c>
+      <c r="W57">
+        <v>0.042075</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>6.70157322776227</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.09060254844933606</v>
+      </c>
+      <c r="C58">
+        <v>34.85032429746487</v>
+      </c>
+      <c r="D58">
+        <v>74.44032429746487</v>
+      </c>
+      <c r="E58">
+        <v>-1.019999999999996</v>
+      </c>
+      <c r="F58">
+        <v>42.28</v>
+      </c>
+      <c r="G58">
+        <v>2.69</v>
+      </c>
+      <c r="H58">
+        <v>32.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>18.875</v>
+      </c>
+      <c r="K58">
+        <v>5.1</v>
+      </c>
+      <c r="L58">
+        <v>13.775</v>
+      </c>
+      <c r="M58">
+        <v>2.09286</v>
+      </c>
+      <c r="N58">
+        <v>11.68214</v>
+      </c>
+      <c r="O58">
+        <v>1.752321</v>
+      </c>
+      <c r="P58">
+        <v>9.929819</v>
+      </c>
+      <c r="Q58">
+        <v>15.029819</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1523648828394001</v>
+      </c>
+      <c r="T58">
+        <v>1.945395603045052</v>
+      </c>
+      <c r="U58">
+        <v>0.0495</v>
+      </c>
+      <c r="V58">
+        <v>0.15</v>
+      </c>
+      <c r="W58">
+        <v>0.042075</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>6.581902277266516</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.09055347222370944</v>
+      </c>
+      <c r="C59">
+        <v>34.13161446582769</v>
+      </c>
+      <c r="D59">
+        <v>74.47661446582769</v>
+      </c>
+      <c r="E59">
+        <v>-0.2649999999999935</v>
+      </c>
+      <c r="F59">
+        <v>43.035</v>
+      </c>
+      <c r="G59">
+        <v>2.69</v>
+      </c>
+      <c r="H59">
+        <v>32.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>18.875</v>
+      </c>
+      <c r="K59">
+        <v>5.1</v>
+      </c>
+      <c r="L59">
+        <v>13.775</v>
+      </c>
+      <c r="M59">
+        <v>2.1302325</v>
+      </c>
+      <c r="N59">
+        <v>11.6447675</v>
+      </c>
+      <c r="O59">
+        <v>1.746715125</v>
+      </c>
+      <c r="P59">
+        <v>9.898052375000001</v>
+      </c>
+      <c r="Q59">
+        <v>14.998052375</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.154815633078394</v>
+      </c>
+      <c r="T59">
+        <v>1.987377583917102</v>
+      </c>
+      <c r="U59">
+        <v>0.0495</v>
+      </c>
+      <c r="V59">
+        <v>0.15</v>
+      </c>
+      <c r="W59">
+        <v>0.042075</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>6.466430307489909</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.09050439599808277</v>
+      </c>
+      <c r="C60">
+        <v>33.41294003486031</v>
+      </c>
+      <c r="D60">
+        <v>74.51294003486031</v>
+      </c>
+      <c r="E60">
+        <v>0.490000000000002</v>
+      </c>
+      <c r="F60">
+        <v>43.79</v>
+      </c>
+      <c r="G60">
+        <v>2.69</v>
+      </c>
+      <c r="H60">
+        <v>32.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>18.875</v>
+      </c>
+      <c r="K60">
+        <v>5.1</v>
+      </c>
+      <c r="L60">
+        <v>13.775</v>
+      </c>
+      <c r="M60">
+        <v>2.167605</v>
+      </c>
+      <c r="N60">
+        <v>11.607395</v>
+      </c>
+      <c r="O60">
+        <v>1.74110925</v>
+      </c>
+      <c r="P60">
+        <v>9.866285749999999</v>
+      </c>
+      <c r="Q60">
+        <v>14.96628575</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1573830857097209</v>
+      </c>
+      <c r="T60">
+        <v>2.031358706735439</v>
+      </c>
+      <c r="U60">
+        <v>0.0495</v>
+      </c>
+      <c r="V60">
+        <v>0.15</v>
+      </c>
+      <c r="W60">
+        <v>0.042075</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>6.354940129774567</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.09045531977245613</v>
+      </c>
+      <c r="C61">
+        <v>32.69430105638737</v>
+      </c>
+      <c r="D61">
+        <v>74.54930105638736</v>
+      </c>
+      <c r="E61">
+        <v>1.244999999999997</v>
+      </c>
+      <c r="F61">
+        <v>44.54499999999999</v>
+      </c>
+      <c r="G61">
+        <v>2.69</v>
+      </c>
+      <c r="H61">
+        <v>32.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>18.875</v>
+      </c>
+      <c r="K61">
+        <v>5.1</v>
+      </c>
+      <c r="L61">
+        <v>13.775</v>
+      </c>
+      <c r="M61">
+        <v>2.2049775</v>
+      </c>
+      <c r="N61">
+        <v>11.5700225</v>
+      </c>
+      <c r="O61">
+        <v>1.735503375</v>
+      </c>
+      <c r="P61">
+        <v>9.834519125</v>
+      </c>
+      <c r="Q61">
+        <v>14.934519125</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1600757799328198</v>
+      </c>
+      <c r="T61">
+        <v>2.077485250179061</v>
+      </c>
+      <c r="U61">
+        <v>0.0495</v>
+      </c>
+      <c r="V61">
+        <v>0.15</v>
+      </c>
+      <c r="W61">
+        <v>0.042075</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>6.247229280117371</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.09112024354682947</v>
+      </c>
+      <c r="C62">
+        <v>31.44964995217305</v>
+      </c>
+      <c r="D62">
+        <v>74.05964995217305</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62">
+        <v>45.3</v>
+      </c>
+      <c r="G62">
+        <v>2.69</v>
+      </c>
+      <c r="H62">
+        <v>32.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>18.875</v>
+      </c>
+      <c r="K62">
+        <v>5.1</v>
+      </c>
+      <c r="L62">
+        <v>13.775</v>
+      </c>
+      <c r="M62">
+        <v>2.30577</v>
+      </c>
+      <c r="N62">
+        <v>11.46923</v>
+      </c>
+      <c r="O62">
+        <v>1.7203845</v>
+      </c>
+      <c r="P62">
+        <v>9.7488455</v>
+      </c>
+      <c r="Q62">
+        <v>14.8488455</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1629031088670737</v>
+      </c>
+      <c r="T62">
+        <v>2.125918120794865</v>
+      </c>
+      <c r="U62">
+        <v>0.0509</v>
+      </c>
+      <c r="V62">
+        <v>0.15</v>
+      </c>
+      <c r="W62">
+        <v>0.043265</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>5.974143127892201</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.09108306732120285</v>
+      </c>
+      <c r="C63">
+        <v>30.72185677106651</v>
+      </c>
+      <c r="D63">
+        <v>74.08685677106651</v>
+      </c>
+      <c r="E63">
+        <v>2.755000000000003</v>
+      </c>
+      <c r="F63">
+        <v>46.055</v>
+      </c>
+      <c r="G63">
+        <v>2.69</v>
+      </c>
+      <c r="H63">
+        <v>32.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>18.875</v>
+      </c>
+      <c r="K63">
+        <v>5.1</v>
+      </c>
+      <c r="L63">
+        <v>13.775</v>
+      </c>
+      <c r="M63">
+        <v>2.3441995</v>
+      </c>
+      <c r="N63">
+        <v>11.4308005</v>
+      </c>
+      <c r="O63">
+        <v>1.714620075</v>
+      </c>
+      <c r="P63">
+        <v>9.716180425000001</v>
+      </c>
+      <c r="Q63">
+        <v>14.816180425</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1658754290287252</v>
+      </c>
+      <c r="T63">
+        <v>2.176834728365325</v>
+      </c>
+      <c r="U63">
+        <v>0.0509</v>
+      </c>
+      <c r="V63">
+        <v>0.15</v>
+      </c>
+      <c r="W63">
+        <v>0.043265</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>5.876206355303804</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.0910458910955762</v>
+      </c>
+      <c r="C64">
+        <v>29.99408358689544</v>
+      </c>
+      <c r="D64">
+        <v>74.11408358689545</v>
+      </c>
+      <c r="E64">
+        <v>3.510000000000005</v>
+      </c>
+      <c r="F64">
+        <v>46.81</v>
+      </c>
+      <c r="G64">
+        <v>2.69</v>
+      </c>
+      <c r="H64">
+        <v>32.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>18.875</v>
+      </c>
+      <c r="K64">
+        <v>5.1</v>
+      </c>
+      <c r="L64">
+        <v>13.775</v>
+      </c>
+      <c r="M64">
+        <v>2.382629</v>
+      </c>
+      <c r="N64">
+        <v>11.392371</v>
+      </c>
+      <c r="O64">
+        <v>1.70885565</v>
+      </c>
+      <c r="P64">
+        <v>9.68351535</v>
+      </c>
+      <c r="Q64">
+        <v>14.78351535</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1690041870936216</v>
+      </c>
+      <c r="T64">
+        <v>2.230431157386863</v>
+      </c>
+      <c r="U64">
+        <v>0.0509</v>
+      </c>
+      <c r="V64">
+        <v>0.15</v>
+      </c>
+      <c r="W64">
+        <v>0.043265</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>5.781428833444066</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.09100871486994956</v>
+      </c>
+      <c r="C65">
+        <v>29.26633042171451</v>
+      </c>
+      <c r="D65">
+        <v>74.14133042171451</v>
+      </c>
+      <c r="E65">
+        <v>4.265000000000001</v>
+      </c>
+      <c r="F65">
+        <v>47.565</v>
+      </c>
+      <c r="G65">
+        <v>2.69</v>
+      </c>
+      <c r="H65">
+        <v>32.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>18.875</v>
+      </c>
+      <c r="K65">
+        <v>5.1</v>
+      </c>
+      <c r="L65">
+        <v>13.775</v>
+      </c>
+      <c r="M65">
+        <v>2.4210585</v>
+      </c>
+      <c r="N65">
+        <v>11.3539415</v>
+      </c>
+      <c r="O65">
+        <v>1.703091225</v>
+      </c>
+      <c r="P65">
+        <v>9.650850275000002</v>
+      </c>
+      <c r="Q65">
+        <v>14.750850275</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1723020672160799</v>
+      </c>
+      <c r="T65">
+        <v>2.286924690679835</v>
+      </c>
+      <c r="U65">
+        <v>0.0509</v>
+      </c>
+      <c r="V65">
+        <v>0.15</v>
+      </c>
+      <c r="W65">
+        <v>0.043265</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>5.689660121802096</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.09097153864432292</v>
+      </c>
+      <c r="C66">
+        <v>28.53859729761079</v>
+      </c>
+      <c r="D66">
+        <v>74.16859729761079</v>
+      </c>
+      <c r="E66">
+        <v>5.020000000000003</v>
+      </c>
+      <c r="F66">
+        <v>48.32</v>
+      </c>
+      <c r="G66">
+        <v>2.69</v>
+      </c>
+      <c r="H66">
+        <v>32.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>18.875</v>
+      </c>
+      <c r="K66">
+        <v>5.1</v>
+      </c>
+      <c r="L66">
+        <v>13.775</v>
+      </c>
+      <c r="M66">
+        <v>2.459488</v>
+      </c>
+      <c r="N66">
+        <v>11.315512</v>
+      </c>
+      <c r="O66">
+        <v>1.6973268</v>
+      </c>
+      <c r="P66">
+        <v>9.618185199999999</v>
+      </c>
+      <c r="Q66">
+        <v>14.7181852</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.175783162900897</v>
+      </c>
+      <c r="T66">
+        <v>2.346556753600193</v>
+      </c>
+      <c r="U66">
+        <v>0.0509</v>
+      </c>
+      <c r="V66">
+        <v>0.15</v>
+      </c>
+      <c r="W66">
+        <v>0.043265</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>5.600759182398939</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.09093436241869629</v>
+      </c>
+      <c r="C67">
+        <v>27.81088423670383</v>
+      </c>
+      <c r="D67">
+        <v>74.19588423670383</v>
+      </c>
+      <c r="E67">
+        <v>5.775000000000006</v>
+      </c>
+      <c r="F67">
+        <v>49.075</v>
+      </c>
+      <c r="G67">
+        <v>2.69</v>
+      </c>
+      <c r="H67">
+        <v>32.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>18.875</v>
+      </c>
+      <c r="K67">
+        <v>5.1</v>
+      </c>
+      <c r="L67">
+        <v>13.775</v>
+      </c>
+      <c r="M67">
+        <v>2.4979175</v>
+      </c>
+      <c r="N67">
+        <v>11.2770825</v>
+      </c>
+      <c r="O67">
+        <v>1.691562375</v>
+      </c>
+      <c r="P67">
+        <v>9.585520125</v>
+      </c>
+      <c r="Q67">
+        <v>14.685520125</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1794631783391323</v>
+      </c>
+      <c r="T67">
+        <v>2.409596362973145</v>
+      </c>
+      <c r="U67">
+        <v>0.0509</v>
+      </c>
+      <c r="V67">
+        <v>0.15</v>
+      </c>
+      <c r="W67">
+        <v>0.043265</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>5.514593656515878</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.09089718619306963</v>
+      </c>
+      <c r="C68">
+        <v>27.08319126114586</v>
+      </c>
+      <c r="D68">
+        <v>74.22319126114587</v>
+      </c>
+      <c r="E68">
+        <v>6.530000000000008</v>
+      </c>
+      <c r="F68">
+        <v>49.83000000000001</v>
+      </c>
+      <c r="G68">
+        <v>2.69</v>
+      </c>
+      <c r="H68">
+        <v>32.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>18.875</v>
+      </c>
+      <c r="K68">
+        <v>5.1</v>
+      </c>
+      <c r="L68">
+        <v>13.775</v>
+      </c>
+      <c r="M68">
+        <v>2.536347</v>
+      </c>
+      <c r="N68">
+        <v>11.238653</v>
+      </c>
+      <c r="O68">
+        <v>1.68579795</v>
+      </c>
+      <c r="P68">
+        <v>9.55285505</v>
+      </c>
+      <c r="Q68">
+        <v>14.65285505</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1833596652737343</v>
+      </c>
+      <c r="T68">
+        <v>2.476344184662151</v>
+      </c>
+      <c r="U68">
+        <v>0.0509</v>
+      </c>
+      <c r="V68">
+        <v>0.15</v>
+      </c>
+      <c r="W68">
+        <v>0.043265</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>5.431039207174727</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.09086000996744299</v>
+      </c>
+      <c r="C69">
+        <v>26.35551839312161</v>
+      </c>
+      <c r="D69">
+        <v>74.25051839312161</v>
+      </c>
+      <c r="E69">
+        <v>7.285000000000004</v>
+      </c>
+      <c r="F69">
+        <v>50.585</v>
+      </c>
+      <c r="G69">
+        <v>2.69</v>
+      </c>
+      <c r="H69">
+        <v>32.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>18.875</v>
+      </c>
+      <c r="K69">
+        <v>5.1</v>
+      </c>
+      <c r="L69">
+        <v>13.775</v>
+      </c>
+      <c r="M69">
+        <v>2.5747765</v>
+      </c>
+      <c r="N69">
+        <v>11.2002235</v>
+      </c>
+      <c r="O69">
+        <v>1.680033525</v>
+      </c>
+      <c r="P69">
+        <v>9.520189974999999</v>
+      </c>
+      <c r="Q69">
+        <v>14.620189975</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1874923029316455</v>
+      </c>
+      <c r="T69">
+        <v>2.547137328877764</v>
+      </c>
+      <c r="U69">
+        <v>0.0509</v>
+      </c>
+      <c r="V69">
+        <v>0.15</v>
+      </c>
+      <c r="W69">
+        <v>0.043265</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>5.349978920500479</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.09082283374181635</v>
+      </c>
+      <c r="C70">
+        <v>25.62786565484853</v>
+      </c>
+      <c r="D70">
+        <v>74.27786565484854</v>
+      </c>
+      <c r="E70">
+        <v>8.040000000000006</v>
+      </c>
+      <c r="F70">
+        <v>51.34</v>
+      </c>
+      <c r="G70">
+        <v>2.69</v>
+      </c>
+      <c r="H70">
+        <v>32.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>18.875</v>
+      </c>
+      <c r="K70">
+        <v>5.1</v>
+      </c>
+      <c r="L70">
+        <v>13.775</v>
+      </c>
+      <c r="M70">
+        <v>2.613206</v>
+      </c>
+      <c r="N70">
+        <v>11.161794</v>
+      </c>
+      <c r="O70">
+        <v>1.6742691</v>
+      </c>
+      <c r="P70">
+        <v>9.4875249</v>
+      </c>
+      <c r="Q70">
+        <v>14.5875249</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1918832304431761</v>
+      </c>
+      <c r="T70">
+        <v>2.622355044606854</v>
+      </c>
+      <c r="U70">
+        <v>0.0509</v>
+      </c>
+      <c r="V70">
+        <v>0.15</v>
+      </c>
+      <c r="W70">
+        <v>0.043265</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>5.271302759904883</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.09078565751618971</v>
+      </c>
+      <c r="C71">
+        <v>24.90023306857686</v>
+      </c>
+      <c r="D71">
+        <v>74.30523306857687</v>
+      </c>
+      <c r="E71">
+        <v>8.795000000000009</v>
+      </c>
+      <c r="F71">
+        <v>52.09500000000001</v>
+      </c>
+      <c r="G71">
+        <v>2.69</v>
+      </c>
+      <c r="H71">
+        <v>32.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>18.875</v>
+      </c>
+      <c r="K71">
+        <v>5.1</v>
+      </c>
+      <c r="L71">
+        <v>13.775</v>
+      </c>
+      <c r="M71">
+        <v>2.6516355</v>
+      </c>
+      <c r="N71">
+        <v>11.1233645</v>
+      </c>
+      <c r="O71">
+        <v>1.668504675</v>
+      </c>
+      <c r="P71">
+        <v>9.454859825000002</v>
+      </c>
+      <c r="Q71">
+        <v>14.554859825</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.196557443600612</v>
+      </c>
+      <c r="T71">
+        <v>2.702425516189432</v>
+      </c>
+      <c r="U71">
+        <v>0.0509</v>
+      </c>
+      <c r="V71">
+        <v>0.15</v>
+      </c>
+      <c r="W71">
+        <v>0.043265</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>5.194907067732348</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.09074848129056307</v>
+      </c>
+      <c r="C72">
+        <v>24.17262065658959</v>
+      </c>
+      <c r="D72">
+        <v>74.3326206565896</v>
+      </c>
+      <c r="E72">
+        <v>9.550000000000011</v>
+      </c>
+      <c r="F72">
+        <v>52.85000000000001</v>
+      </c>
+      <c r="G72">
+        <v>2.69</v>
+      </c>
+      <c r="H72">
+        <v>32.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>18.875</v>
+      </c>
+      <c r="K72">
+        <v>5.1</v>
+      </c>
+      <c r="L72">
+        <v>13.775</v>
+      </c>
+      <c r="M72">
+        <v>2.690065000000001</v>
+      </c>
+      <c r="N72">
+        <v>11.084935</v>
+      </c>
+      <c r="O72">
+        <v>1.66274025</v>
+      </c>
+      <c r="P72">
+        <v>9.422194749999999</v>
+      </c>
+      <c r="Q72">
+        <v>14.52219475</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2015432709685436</v>
+      </c>
+      <c r="T72">
+        <v>2.78783401921085</v>
+      </c>
+      <c r="U72">
+        <v>0.0509</v>
+      </c>
+      <c r="V72">
+        <v>0.15</v>
+      </c>
+      <c r="W72">
+        <v>0.043265</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>5.120694109621885</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.09071130506493642</v>
+      </c>
+      <c r="C73">
+        <v>23.44502844120259</v>
+      </c>
+      <c r="D73">
+        <v>74.36002844120259</v>
+      </c>
+      <c r="E73">
+        <v>10.305</v>
+      </c>
+      <c r="F73">
+        <v>53.605</v>
+      </c>
+      <c r="G73">
+        <v>2.69</v>
+      </c>
+      <c r="H73">
+        <v>32.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>18.875</v>
+      </c>
+      <c r="K73">
+        <v>5.1</v>
+      </c>
+      <c r="L73">
+        <v>13.775</v>
+      </c>
+      <c r="M73">
+        <v>2.7284945</v>
+      </c>
+      <c r="N73">
+        <v>11.0465055</v>
+      </c>
+      <c r="O73">
+        <v>1.656975825</v>
+      </c>
+      <c r="P73">
+        <v>9.389529675</v>
+      </c>
+      <c r="Q73">
+        <v>14.489529675</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2068729484997808</v>
+      </c>
+      <c r="T73">
+        <v>2.87913276381995</v>
+      </c>
+      <c r="U73">
+        <v>0.0509</v>
+      </c>
+      <c r="V73">
+        <v>0.15</v>
+      </c>
+      <c r="W73">
+        <v>0.043265</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>5.048571657373691</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.09067412883930978</v>
+      </c>
+      <c r="C74">
+        <v>22.71745644476465</v>
+      </c>
+      <c r="D74">
+        <v>74.38745644476465</v>
+      </c>
+      <c r="E74">
+        <v>11.06</v>
+      </c>
+      <c r="F74">
+        <v>54.36</v>
+      </c>
+      <c r="G74">
+        <v>2.69</v>
+      </c>
+      <c r="H74">
+        <v>32.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>18.875</v>
+      </c>
+      <c r="K74">
+        <v>5.1</v>
+      </c>
+      <c r="L74">
+        <v>13.775</v>
+      </c>
+      <c r="M74">
+        <v>2.766924</v>
+      </c>
+      <c r="N74">
+        <v>11.008076</v>
+      </c>
+      <c r="O74">
+        <v>1.6512114</v>
+      </c>
+      <c r="P74">
+        <v>9.356864600000002</v>
+      </c>
+      <c r="Q74">
+        <v>14.4568646</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2125833172832492</v>
+      </c>
+      <c r="T74">
+        <v>2.976952847329701</v>
+      </c>
+      <c r="U74">
+        <v>0.0509</v>
+      </c>
+      <c r="V74">
+        <v>0.15</v>
+      </c>
+      <c r="W74">
+        <v>0.043265</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>4.978452606576834</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.09063695261368314</v>
+      </c>
+      <c r="C75">
+        <v>21.98990468965757</v>
+      </c>
+      <c r="D75">
+        <v>74.41490468965758</v>
+      </c>
+      <c r="E75">
+        <v>11.815</v>
+      </c>
+      <c r="F75">
+        <v>55.115</v>
+      </c>
+      <c r="G75">
+        <v>2.69</v>
+      </c>
+      <c r="H75">
+        <v>32.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>18.875</v>
+      </c>
+      <c r="K75">
+        <v>5.1</v>
+      </c>
+      <c r="L75">
+        <v>13.775</v>
+      </c>
+      <c r="M75">
+        <v>2.8053535</v>
+      </c>
+      <c r="N75">
+        <v>10.9696465</v>
+      </c>
+      <c r="O75">
+        <v>1.645446975</v>
+      </c>
+      <c r="P75">
+        <v>9.324199524999999</v>
+      </c>
+      <c r="Q75">
+        <v>14.424199525</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2187166763469746</v>
+      </c>
+      <c r="T75">
+        <v>3.082018862951286</v>
+      </c>
+      <c r="U75">
+        <v>0.0509</v>
+      </c>
+      <c r="V75">
+        <v>0.15</v>
+      </c>
+      <c r="W75">
+        <v>0.043265</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>4.910254625664822</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.0905997763880565</v>
+      </c>
+      <c r="C76">
+        <v>21.26237319829618</v>
+      </c>
+      <c r="D76">
+        <v>74.44237319829618</v>
+      </c>
+      <c r="E76">
+        <v>12.57</v>
+      </c>
+      <c r="F76">
+        <v>55.87</v>
+      </c>
+      <c r="G76">
+        <v>2.69</v>
+      </c>
+      <c r="H76">
+        <v>32.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>18.875</v>
+      </c>
+      <c r="K76">
+        <v>5.1</v>
+      </c>
+      <c r="L76">
+        <v>13.775</v>
+      </c>
+      <c r="M76">
+        <v>2.843783</v>
+      </c>
+      <c r="N76">
+        <v>10.931217</v>
+      </c>
+      <c r="O76">
+        <v>1.63968255</v>
+      </c>
+      <c r="P76">
+        <v>9.29153445</v>
+      </c>
+      <c r="Q76">
+        <v>14.39153445</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2253218322617558</v>
+      </c>
+      <c r="T76">
+        <v>3.195166879774531</v>
+      </c>
+      <c r="U76">
+        <v>0.0509</v>
+      </c>
+      <c r="V76">
+        <v>0.15</v>
+      </c>
+      <c r="W76">
+        <v>0.043265</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>4.843899833426109</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.09056260016242985</v>
+      </c>
+      <c r="C77">
+        <v>20.53486199312842</v>
+      </c>
+      <c r="D77">
+        <v>74.46986199312842</v>
+      </c>
+      <c r="E77">
+        <v>13.325</v>
+      </c>
+      <c r="F77">
+        <v>56.625</v>
+      </c>
+      <c r="G77">
+        <v>2.69</v>
+      </c>
+      <c r="H77">
+        <v>32.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>18.875</v>
+      </c>
+      <c r="K77">
+        <v>5.1</v>
+      </c>
+      <c r="L77">
+        <v>13.775</v>
+      </c>
+      <c r="M77">
+        <v>2.8822125</v>
+      </c>
+      <c r="N77">
+        <v>10.8927875</v>
+      </c>
+      <c r="O77">
+        <v>1.633918125</v>
+      </c>
+      <c r="P77">
+        <v>9.258869375</v>
+      </c>
+      <c r="Q77">
+        <v>14.358869375</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2324554006497194</v>
+      </c>
+      <c r="T77">
+        <v>3.317366737943636</v>
+      </c>
+      <c r="U77">
+        <v>0.0509</v>
+      </c>
+      <c r="V77">
+        <v>0.15</v>
+      </c>
+      <c r="W77">
+        <v>0.043265</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>4.779314502313761</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.09052542393680321</v>
+      </c>
+      <c r="C78">
+        <v>19.80737109663539</v>
+      </c>
+      <c r="D78">
+        <v>74.49737109663539</v>
+      </c>
+      <c r="E78">
+        <v>14.08000000000001</v>
+      </c>
+      <c r="F78">
+        <v>57.38</v>
+      </c>
+      <c r="G78">
+        <v>2.69</v>
+      </c>
+      <c r="H78">
+        <v>32.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>18.875</v>
+      </c>
+      <c r="K78">
+        <v>5.1</v>
+      </c>
+      <c r="L78">
+        <v>13.775</v>
+      </c>
+      <c r="M78">
+        <v>2.920642</v>
+      </c>
+      <c r="N78">
+        <v>10.854358</v>
+      </c>
+      <c r="O78">
+        <v>1.6281537</v>
+      </c>
+      <c r="P78">
+        <v>9.226204300000001</v>
+      </c>
+      <c r="Q78">
+        <v>14.3262043</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2401834330700134</v>
+      </c>
+      <c r="T78">
+        <v>3.449749917626833</v>
+      </c>
+      <c r="U78">
+        <v>0.0509</v>
+      </c>
+      <c r="V78">
+        <v>0.15</v>
+      </c>
+      <c r="W78">
+        <v>0.043265</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>4.716428785178054</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.09048824771117657</v>
+      </c>
+      <c r="C79">
+        <v>19.07990053133143</v>
+      </c>
+      <c r="D79">
+        <v>74.52490053133143</v>
+      </c>
+      <c r="E79">
+        <v>14.835</v>
+      </c>
+      <c r="F79">
+        <v>58.135</v>
+      </c>
+      <c r="G79">
+        <v>2.69</v>
+      </c>
+      <c r="H79">
+        <v>32.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>18.875</v>
+      </c>
+      <c r="K79">
+        <v>5.1</v>
+      </c>
+      <c r="L79">
+        <v>13.775</v>
+      </c>
+      <c r="M79">
+        <v>2.9590715</v>
+      </c>
+      <c r="N79">
+        <v>10.8159285</v>
+      </c>
+      <c r="O79">
+        <v>1.622389275</v>
+      </c>
+      <c r="P79">
+        <v>9.193539225</v>
+      </c>
+      <c r="Q79">
+        <v>14.293539225</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2485834683094634</v>
+      </c>
+      <c r="T79">
+        <v>3.593644678152047</v>
+      </c>
+      <c r="U79">
+        <v>0.0509</v>
+      </c>
+      <c r="V79">
+        <v>0.15</v>
+      </c>
+      <c r="W79">
+        <v>0.043265</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>4.655176463292625</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.09045107148554993</v>
+      </c>
+      <c r="C80">
+        <v>18.35245031976417</v>
+      </c>
+      <c r="D80">
+        <v>74.55245031976418</v>
+      </c>
+      <c r="E80">
+        <v>15.59</v>
+      </c>
+      <c r="F80">
+        <v>58.89</v>
+      </c>
+      <c r="G80">
+        <v>2.69</v>
+      </c>
+      <c r="H80">
+        <v>32.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>18.875</v>
+      </c>
+      <c r="K80">
+        <v>5.1</v>
+      </c>
+      <c r="L80">
+        <v>13.775</v>
+      </c>
+      <c r="M80">
+        <v>2.997501</v>
+      </c>
+      <c r="N80">
+        <v>10.777499</v>
+      </c>
+      <c r="O80">
+        <v>1.61662485</v>
+      </c>
+      <c r="P80">
+        <v>9.160874150000001</v>
+      </c>
+      <c r="Q80">
+        <v>14.26087415</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2577471431161361</v>
+      </c>
+      <c r="T80">
+        <v>3.750620780543189</v>
+      </c>
+      <c r="U80">
+        <v>0.0509</v>
+      </c>
+      <c r="V80">
+        <v>0.15</v>
+      </c>
+      <c r="W80">
+        <v>0.043265</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>4.595494713763232</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.09041389525992327</v>
+      </c>
+      <c r="C81">
+        <v>17.6250204845146</v>
+      </c>
+      <c r="D81">
+        <v>74.58002048451461</v>
+      </c>
+      <c r="E81">
+        <v>16.34500000000001</v>
+      </c>
+      <c r="F81">
+        <v>59.645</v>
+      </c>
+      <c r="G81">
+        <v>2.69</v>
+      </c>
+      <c r="H81">
+        <v>32.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>18.875</v>
+      </c>
+      <c r="K81">
+        <v>5.1</v>
+      </c>
+      <c r="L81">
+        <v>13.775</v>
+      </c>
+      <c r="M81">
+        <v>3.0359305</v>
+      </c>
+      <c r="N81">
+        <v>10.7390695</v>
+      </c>
+      <c r="O81">
+        <v>1.610860425</v>
+      </c>
+      <c r="P81">
+        <v>9.128209074999999</v>
+      </c>
+      <c r="Q81">
+        <v>14.228209075</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2677835488567776</v>
+      </c>
+      <c r="T81">
+        <v>3.922546987923965</v>
+      </c>
+      <c r="U81">
+        <v>0.0509</v>
+      </c>
+      <c r="V81">
+        <v>0.15</v>
+      </c>
+      <c r="W81">
+        <v>0.043265</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>4.537323894601672</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.09214471903429663</v>
+      </c>
+      <c r="C82">
+        <v>15.60768800250452</v>
+      </c>
+      <c r="D82">
+        <v>73.31768800250453</v>
+      </c>
+      <c r="E82">
+        <v>17.10000000000001</v>
+      </c>
+      <c r="F82">
+        <v>60.40000000000001</v>
+      </c>
+      <c r="G82">
+        <v>2.69</v>
+      </c>
+      <c r="H82">
+        <v>32.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>18.875</v>
+      </c>
+      <c r="K82">
+        <v>5.1</v>
+      </c>
+      <c r="L82">
+        <v>13.775</v>
+      </c>
+      <c r="M82">
+        <v>3.2314</v>
+      </c>
+      <c r="N82">
+        <v>10.5436</v>
+      </c>
+      <c r="O82">
+        <v>1.58154</v>
+      </c>
+      <c r="P82">
+        <v>8.962059999999999</v>
+      </c>
+      <c r="Q82">
+        <v>14.06206</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2788235951714833</v>
+      </c>
+      <c r="T82">
+        <v>4.111665816042817</v>
+      </c>
+      <c r="U82">
+        <v>0.0535</v>
+      </c>
+      <c r="V82">
+        <v>0.15</v>
+      </c>
+      <c r="W82">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>4.262858203874481</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.09212964280867</v>
+      </c>
+      <c r="C83">
+        <v>14.8634989518027</v>
+      </c>
+      <c r="D83">
+        <v>73.3284989518027</v>
+      </c>
+      <c r="E83">
+        <v>17.855</v>
+      </c>
+      <c r="F83">
+        <v>61.155</v>
+      </c>
+      <c r="G83">
+        <v>2.69</v>
+      </c>
+      <c r="H83">
+        <v>32.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>18.875</v>
+      </c>
+      <c r="K83">
+        <v>5.1</v>
+      </c>
+      <c r="L83">
+        <v>13.775</v>
+      </c>
+      <c r="M83">
+        <v>3.2717925</v>
+      </c>
+      <c r="N83">
+        <v>10.5032075</v>
+      </c>
+      <c r="O83">
+        <v>1.575481125</v>
+      </c>
+      <c r="P83">
+        <v>8.927726375000001</v>
+      </c>
+      <c r="Q83">
+        <v>14.027726375</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2910257516245791</v>
+      </c>
+      <c r="T83">
+        <v>4.320691889226813</v>
+      </c>
+      <c r="U83">
+        <v>0.0535</v>
+      </c>
+      <c r="V83">
+        <v>0.15</v>
+      </c>
+      <c r="W83">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>4.210230324814303</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.09211456658304334</v>
+      </c>
+      <c r="C84">
+        <v>14.1193130897956</v>
+      </c>
+      <c r="D84">
+        <v>73.33931308979561</v>
+      </c>
+      <c r="E84">
+        <v>18.61000000000001</v>
+      </c>
+      <c r="F84">
+        <v>61.91</v>
+      </c>
+      <c r="G84">
+        <v>2.69</v>
+      </c>
+      <c r="H84">
+        <v>32.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>18.875</v>
+      </c>
+      <c r="K84">
+        <v>5.1</v>
+      </c>
+      <c r="L84">
+        <v>13.775</v>
+      </c>
+      <c r="M84">
+        <v>3.312185</v>
+      </c>
+      <c r="N84">
+        <v>10.462815</v>
+      </c>
+      <c r="O84">
+        <v>1.56942225</v>
+      </c>
+      <c r="P84">
+        <v>8.89339275</v>
+      </c>
+      <c r="Q84">
+        <v>13.99339275</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3045837032391299</v>
+      </c>
+      <c r="T84">
+        <v>4.552943081653474</v>
+      </c>
+      <c r="U84">
+        <v>0.0535</v>
+      </c>
+      <c r="V84">
+        <v>0.15</v>
+      </c>
+      <c r="W84">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>4.158886052560471</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.09209949035741673</v>
+      </c>
+      <c r="C85">
+        <v>13.37513041789413</v>
+      </c>
+      <c r="D85">
+        <v>73.35013041789414</v>
+      </c>
+      <c r="E85">
+        <v>19.36500000000001</v>
+      </c>
+      <c r="F85">
+        <v>62.66500000000001</v>
+      </c>
+      <c r="G85">
+        <v>2.69</v>
+      </c>
+      <c r="H85">
+        <v>32.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>18.875</v>
+      </c>
+      <c r="K85">
+        <v>5.1</v>
+      </c>
+      <c r="L85">
+        <v>13.775</v>
+      </c>
+      <c r="M85">
+        <v>3.3525775</v>
+      </c>
+      <c r="N85">
+        <v>10.4224225</v>
+      </c>
+      <c r="O85">
+        <v>1.563363375</v>
+      </c>
+      <c r="P85">
+        <v>8.859059125</v>
+      </c>
+      <c r="Q85">
+        <v>13.959059125</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3197367079848044</v>
+      </c>
+      <c r="T85">
+        <v>4.81251794377739</v>
+      </c>
+      <c r="U85">
+        <v>0.0535</v>
+      </c>
+      <c r="V85">
+        <v>0.15</v>
+      </c>
+      <c r="W85">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>4.108778991686247</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.09208441413179008</v>
+      </c>
+      <c r="C86">
+        <v>12.63095093751013</v>
+      </c>
+      <c r="D86">
+        <v>73.36095093751013</v>
+      </c>
+      <c r="E86">
+        <v>20.12</v>
+      </c>
+      <c r="F86">
+        <v>63.41999999999999</v>
+      </c>
+      <c r="G86">
+        <v>2.69</v>
+      </c>
+      <c r="H86">
+        <v>32.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>18.875</v>
+      </c>
+      <c r="K86">
+        <v>5.1</v>
+      </c>
+      <c r="L86">
+        <v>13.775</v>
+      </c>
+      <c r="M86">
+        <v>3.39297</v>
+      </c>
+      <c r="N86">
+        <v>10.38203</v>
+      </c>
+      <c r="O86">
+        <v>1.5573045</v>
+      </c>
+      <c r="P86">
+        <v>8.8247255</v>
+      </c>
+      <c r="Q86">
+        <v>13.9247255</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.336783838323688</v>
+      </c>
+      <c r="T86">
+        <v>5.104539663666792</v>
+      </c>
+      <c r="U86">
+        <v>0.0535</v>
+      </c>
+      <c r="V86">
+        <v>0.15</v>
+      </c>
+      <c r="W86">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>4.059864956070935</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.09206933790616342</v>
+      </c>
+      <c r="C87">
+        <v>11.88677465005622</v>
+      </c>
+      <c r="D87">
+        <v>73.37177465005622</v>
+      </c>
+      <c r="E87">
+        <v>20.875</v>
+      </c>
+      <c r="F87">
+        <v>64.175</v>
+      </c>
+      <c r="G87">
+        <v>2.69</v>
+      </c>
+      <c r="H87">
+        <v>32.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>18.875</v>
+      </c>
+      <c r="K87">
+        <v>5.1</v>
+      </c>
+      <c r="L87">
+        <v>13.775</v>
+      </c>
+      <c r="M87">
+        <v>3.4333625</v>
+      </c>
+      <c r="N87">
+        <v>10.3416375</v>
+      </c>
+      <c r="O87">
+        <v>1.551245625</v>
+      </c>
+      <c r="P87">
+        <v>8.790391875000001</v>
+      </c>
+      <c r="Q87">
+        <v>13.890391875</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3561039193744229</v>
+      </c>
+      <c r="T87">
+        <v>5.435497612874784</v>
+      </c>
+      <c r="U87">
+        <v>0.0535</v>
+      </c>
+      <c r="V87">
+        <v>0.15</v>
+      </c>
+      <c r="W87">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>4.012101838940689</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.09402796168053679</v>
+      </c>
+      <c r="C88">
+        <v>9.751857319167172</v>
+      </c>
+      <c r="D88">
+        <v>71.99185731916717</v>
+      </c>
+      <c r="E88">
+        <v>21.63</v>
+      </c>
+      <c r="F88">
+        <v>64.92999999999999</v>
+      </c>
+      <c r="G88">
+        <v>2.69</v>
+      </c>
+      <c r="H88">
+        <v>32.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>18.875</v>
+      </c>
+      <c r="K88">
+        <v>5.1</v>
+      </c>
+      <c r="L88">
+        <v>13.775</v>
+      </c>
+      <c r="M88">
+        <v>3.649065999999999</v>
+      </c>
+      <c r="N88">
+        <v>10.125934</v>
+      </c>
+      <c r="O88">
+        <v>1.5188901</v>
+      </c>
+      <c r="P88">
+        <v>8.607043900000001</v>
+      </c>
+      <c r="Q88">
+        <v>13.7070439</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3781840120038342</v>
+      </c>
+      <c r="T88">
+        <v>5.813735269112488</v>
+      </c>
+      <c r="U88">
+        <v>0.0562</v>
+      </c>
+      <c r="V88">
+        <v>0.15</v>
+      </c>
+      <c r="W88">
+        <v>0.04777</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>3.774938573322599</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.09403583545491015</v>
+      </c>
+      <c r="C89">
+        <v>8.991414717709816</v>
+      </c>
+      <c r="D89">
+        <v>71.98641471770982</v>
+      </c>
+      <c r="E89">
+        <v>22.38500000000001</v>
+      </c>
+      <c r="F89">
+        <v>65.685</v>
+      </c>
+      <c r="G89">
+        <v>2.69</v>
+      </c>
+      <c r="H89">
+        <v>32.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>18.875</v>
+      </c>
+      <c r="K89">
+        <v>5.1</v>
+      </c>
+      <c r="L89">
+        <v>13.775</v>
+      </c>
+      <c r="M89">
+        <v>3.691497</v>
+      </c>
+      <c r="N89">
+        <v>10.083503</v>
+      </c>
+      <c r="O89">
+        <v>1.51252545</v>
+      </c>
+      <c r="P89">
+        <v>8.57097755</v>
+      </c>
+      <c r="Q89">
+        <v>13.67097755</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4036610419608473</v>
+      </c>
+      <c r="T89">
+        <v>6.250163334002148</v>
+      </c>
+      <c r="U89">
+        <v>0.0562</v>
+      </c>
+      <c r="V89">
+        <v>0.15</v>
+      </c>
+      <c r="W89">
+        <v>0.04777</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>3.73154847477866</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.09404370922928351</v>
+      </c>
+      <c r="C90">
+        <v>8.230972939114196</v>
+      </c>
+      <c r="D90">
+        <v>71.9809729391142</v>
+      </c>
+      <c r="E90">
+        <v>23.14</v>
+      </c>
+      <c r="F90">
+        <v>66.44</v>
+      </c>
+      <c r="G90">
+        <v>2.69</v>
+      </c>
+      <c r="H90">
+        <v>32.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>18.875</v>
+      </c>
+      <c r="K90">
+        <v>5.1</v>
+      </c>
+      <c r="L90">
+        <v>13.775</v>
+      </c>
+      <c r="M90">
+        <v>3.733928</v>
+      </c>
+      <c r="N90">
+        <v>10.041072</v>
+      </c>
+      <c r="O90">
+        <v>1.5061608</v>
+      </c>
+      <c r="P90">
+        <v>8.5349112</v>
+      </c>
+      <c r="Q90">
+        <v>13.6349112</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4333842435773626</v>
+      </c>
+      <c r="T90">
+        <v>6.759329409706752</v>
+      </c>
+      <c r="U90">
+        <v>0.0562</v>
+      </c>
+      <c r="V90">
+        <v>0.15</v>
+      </c>
+      <c r="W90">
+        <v>0.04777</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>3.689144514837994</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.09405158300365687</v>
+      </c>
+      <c r="C91">
+        <v>7.470531983193666</v>
+      </c>
+      <c r="D91">
+        <v>71.97553198319368</v>
+      </c>
+      <c r="E91">
+        <v>23.89500000000001</v>
+      </c>
+      <c r="F91">
+        <v>67.19500000000001</v>
+      </c>
+      <c r="G91">
+        <v>2.69</v>
+      </c>
+      <c r="H91">
+        <v>32.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>18.875</v>
+      </c>
+      <c r="K91">
+        <v>5.1</v>
+      </c>
+      <c r="L91">
+        <v>13.775</v>
+      </c>
+      <c r="M91">
+        <v>3.776359</v>
+      </c>
+      <c r="N91">
+        <v>9.998640999999999</v>
+      </c>
+      <c r="O91">
+        <v>1.49979615</v>
+      </c>
+      <c r="P91">
+        <v>8.498844849999999</v>
+      </c>
+      <c r="Q91">
+        <v>13.59884485</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4685116636696079</v>
+      </c>
+      <c r="T91">
+        <v>7.361071135539465</v>
+      </c>
+      <c r="U91">
+        <v>0.0562</v>
+      </c>
+      <c r="V91">
+        <v>0.15</v>
+      </c>
+      <c r="W91">
+        <v>0.04777</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>3.647693452873522</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.09405945677803022</v>
+      </c>
+      <c r="C92">
+        <v>6.710091849761724</v>
+      </c>
+      <c r="D92">
+        <v>71.97009184976173</v>
+      </c>
+      <c r="E92">
+        <v>24.65000000000001</v>
+      </c>
+      <c r="F92">
+        <v>67.95</v>
+      </c>
+      <c r="G92">
+        <v>2.69</v>
+      </c>
+      <c r="H92">
+        <v>32.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>18.875</v>
+      </c>
+      <c r="K92">
+        <v>5.1</v>
+      </c>
+      <c r="L92">
+        <v>13.775</v>
+      </c>
+      <c r="M92">
+        <v>3.81879</v>
+      </c>
+      <c r="N92">
+        <v>9.95621</v>
+      </c>
+      <c r="O92">
+        <v>1.4934315</v>
+      </c>
+      <c r="P92">
+        <v>8.462778500000001</v>
+      </c>
+      <c r="Q92">
+        <v>13.5627785</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5106645677803023</v>
+      </c>
+      <c r="T92">
+        <v>8.083161206538721</v>
+      </c>
+      <c r="U92">
+        <v>0.0562</v>
+      </c>
+      <c r="V92">
+        <v>0.15</v>
+      </c>
+      <c r="W92">
+        <v>0.04777</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>3.607163525619371</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.09406733055240359</v>
+      </c>
+      <c r="C93">
+        <v>5.949652538631852</v>
+      </c>
+      <c r="D93">
+        <v>71.96465253863185</v>
+      </c>
+      <c r="E93">
+        <v>25.405</v>
+      </c>
+      <c r="F93">
+        <v>68.705</v>
+      </c>
+      <c r="G93">
+        <v>2.69</v>
+      </c>
+      <c r="H93">
+        <v>32.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>18.875</v>
+      </c>
+      <c r="K93">
+        <v>5.1</v>
+      </c>
+      <c r="L93">
+        <v>13.775</v>
+      </c>
+      <c r="M93">
+        <v>3.861221</v>
+      </c>
+      <c r="N93">
+        <v>9.913779</v>
+      </c>
+      <c r="O93">
+        <v>1.48706685</v>
+      </c>
+      <c r="P93">
+        <v>8.42671215</v>
+      </c>
+      <c r="Q93">
+        <v>13.52671215</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5621847839155956</v>
+      </c>
+      <c r="T93">
+        <v>8.965715737760034</v>
+      </c>
+      <c r="U93">
+        <v>0.0562</v>
+      </c>
+      <c r="V93">
+        <v>0.15</v>
+      </c>
+      <c r="W93">
+        <v>0.04777</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>3.567524365997181</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.09407520432677695</v>
+      </c>
+      <c r="C94">
+        <v>5.189214049617647</v>
+      </c>
+      <c r="D94">
+        <v>71.95921404961766</v>
+      </c>
+      <c r="E94">
+        <v>26.16000000000001</v>
+      </c>
+      <c r="F94">
+        <v>69.46000000000001</v>
+      </c>
+      <c r="G94">
+        <v>2.69</v>
+      </c>
+      <c r="H94">
+        <v>32.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>18.875</v>
+      </c>
+      <c r="K94">
+        <v>5.1</v>
+      </c>
+      <c r="L94">
+        <v>13.775</v>
+      </c>
+      <c r="M94">
+        <v>3.903652000000001</v>
+      </c>
+      <c r="N94">
+        <v>9.871347999999999</v>
+      </c>
+      <c r="O94">
+        <v>1.4807022</v>
+      </c>
+      <c r="P94">
+        <v>8.3906458</v>
+      </c>
+      <c r="Q94">
+        <v>13.4906458</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6265850540847122</v>
+      </c>
+      <c r="T94">
+        <v>10.06890890178668</v>
+      </c>
+      <c r="U94">
+        <v>0.0562</v>
+      </c>
+      <c r="V94">
+        <v>0.15</v>
+      </c>
+      <c r="W94">
+        <v>0.04777</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>3.528746927236341</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.0977984281011503</v>
+      </c>
+      <c r="C95">
+        <v>1.951464530876081</v>
+      </c>
+      <c r="D95">
+        <v>69.47646453087609</v>
+      </c>
+      <c r="E95">
+        <v>26.91500000000001</v>
+      </c>
+      <c r="F95">
+        <v>70.215</v>
+      </c>
+      <c r="G95">
+        <v>2.69</v>
+      </c>
+      <c r="H95">
+        <v>32.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>18.875</v>
+      </c>
+      <c r="K95">
+        <v>5.1</v>
+      </c>
+      <c r="L95">
+        <v>13.775</v>
+      </c>
+      <c r="M95">
+        <v>4.2760935</v>
+      </c>
+      <c r="N95">
+        <v>9.4989065</v>
+      </c>
+      <c r="O95">
+        <v>1.424835975</v>
+      </c>
+      <c r="P95">
+        <v>8.074070525</v>
+      </c>
+      <c r="Q95">
+        <v>13.174070525</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7093854014450047</v>
+      </c>
+      <c r="T95">
+        <v>11.48730011267807</v>
+      </c>
+      <c r="U95">
+        <v>0.0609</v>
+      </c>
+      <c r="V95">
+        <v>0.15</v>
+      </c>
+      <c r="W95">
+        <v>0.051765</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>3.22139822246637</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.09784625187552365</v>
+      </c>
+      <c r="C96">
+        <v>1.165688224903434</v>
+      </c>
+      <c r="D96">
+        <v>69.44568822490344</v>
+      </c>
+      <c r="E96">
+        <v>27.67</v>
+      </c>
+      <c r="F96">
+        <v>70.97</v>
+      </c>
+      <c r="G96">
+        <v>2.69</v>
+      </c>
+      <c r="H96">
+        <v>32.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>18.875</v>
+      </c>
+      <c r="K96">
+        <v>5.1</v>
+      </c>
+      <c r="L96">
+        <v>13.775</v>
+      </c>
+      <c r="M96">
+        <v>4.322073</v>
+      </c>
+      <c r="N96">
+        <v>9.452926999999999</v>
+      </c>
+      <c r="O96">
+        <v>1.41793905</v>
+      </c>
+      <c r="P96">
+        <v>8.03498795</v>
+      </c>
+      <c r="Q96">
+        <v>13.13498795</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8197858645920617</v>
+      </c>
+      <c r="T96">
+        <v>13.3784883938666</v>
+      </c>
+      <c r="U96">
+        <v>0.0609</v>
+      </c>
+      <c r="V96">
+        <v>0.15</v>
+      </c>
+      <c r="W96">
+        <v>0.051765</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>3.187128028610345</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.09789407564989702</v>
+      </c>
+      <c r="C97">
+        <v>0.3799391730987338</v>
+      </c>
+      <c r="D97">
+        <v>69.41493917309874</v>
+      </c>
+      <c r="E97">
+        <v>28.42500000000001</v>
+      </c>
+      <c r="F97">
+        <v>71.72500000000001</v>
+      </c>
+      <c r="G97">
+        <v>2.69</v>
+      </c>
+      <c r="H97">
+        <v>32.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>18.875</v>
+      </c>
+      <c r="K97">
+        <v>5.1</v>
+      </c>
+      <c r="L97">
+        <v>13.775</v>
+      </c>
+      <c r="M97">
+        <v>4.368052500000001</v>
+      </c>
+      <c r="N97">
+        <v>9.406947499999999</v>
+      </c>
+      <c r="O97">
+        <v>1.411042125</v>
+      </c>
+      <c r="P97">
+        <v>7.995905375</v>
+      </c>
+      <c r="Q97">
+        <v>13.095905375</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9743465129979416</v>
+      </c>
+      <c r="T97">
+        <v>16.02615198753055</v>
+      </c>
+      <c r="U97">
+        <v>0.0609</v>
+      </c>
+      <c r="V97">
+        <v>0.15</v>
+      </c>
+      <c r="W97">
+        <v>0.051765</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>3.153579312519709</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.09794189942427037</v>
+      </c>
+      <c r="C98">
+        <v>-0.4057826607245687</v>
+      </c>
+      <c r="D98">
+        <v>69.38421733927544</v>
+      </c>
+      <c r="E98">
+        <v>29.18000000000001</v>
+      </c>
+      <c r="F98">
+        <v>72.48</v>
+      </c>
+      <c r="G98">
+        <v>2.69</v>
+      </c>
+      <c r="H98">
+        <v>32.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>18.875</v>
+      </c>
+      <c r="K98">
+        <v>5.1</v>
+      </c>
+      <c r="L98">
+        <v>13.775</v>
+      </c>
+      <c r="M98">
+        <v>4.414032000000001</v>
+      </c>
+      <c r="N98">
+        <v>9.360968</v>
+      </c>
+      <c r="O98">
+        <v>1.4041452</v>
+      </c>
+      <c r="P98">
+        <v>7.956822799999999</v>
+      </c>
+      <c r="Q98">
+        <v>13.0568228</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.206187485606758</v>
+      </c>
+      <c r="T98">
+        <v>19.99764737802641</v>
+      </c>
+      <c r="U98">
+        <v>0.0609</v>
+      </c>
+      <c r="V98">
+        <v>0.15</v>
+      </c>
+      <c r="W98">
+        <v>0.051765</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>3.120729528014296</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.09798972319864373</v>
+      </c>
+      <c r="C99">
+        <v>-1.191477312689159</v>
+      </c>
+      <c r="D99">
+        <v>69.35352268731084</v>
+      </c>
+      <c r="E99">
+        <v>29.935</v>
+      </c>
+      <c r="F99">
+        <v>73.235</v>
+      </c>
+      <c r="G99">
+        <v>2.69</v>
+      </c>
+      <c r="H99">
+        <v>32.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>18.875</v>
+      </c>
+      <c r="K99">
+        <v>5.1</v>
+      </c>
+      <c r="L99">
+        <v>13.775</v>
+      </c>
+      <c r="M99">
+        <v>4.4600115</v>
+      </c>
+      <c r="N99">
+        <v>9.3149885</v>
+      </c>
+      <c r="O99">
+        <v>1.397248275</v>
+      </c>
+      <c r="P99">
+        <v>7.917740225</v>
+      </c>
+      <c r="Q99">
+        <v>13.017740225</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.592589106621456</v>
+      </c>
+      <c r="T99">
+        <v>26.61680636218624</v>
+      </c>
+      <c r="U99">
+        <v>0.0609</v>
+      </c>
+      <c r="V99">
+        <v>0.15</v>
+      </c>
+      <c r="W99">
+        <v>0.051765</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>3.088557058653324</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.09803754697301709</v>
+      </c>
+      <c r="C100">
+        <v>-1.977144818853731</v>
+      </c>
+      <c r="D100">
+        <v>69.32285518114627</v>
+      </c>
+      <c r="E100">
+        <v>30.69</v>
+      </c>
+      <c r="F100">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="G100">
+        <v>2.69</v>
+      </c>
+      <c r="H100">
+        <v>32.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>18.875</v>
+      </c>
+      <c r="K100">
+        <v>5.1</v>
+      </c>
+      <c r="L100">
+        <v>13.775</v>
+      </c>
+      <c r="M100">
+        <v>4.505991</v>
+      </c>
+      <c r="N100">
+        <v>9.269009</v>
+      </c>
+      <c r="O100">
+        <v>1.39035135</v>
+      </c>
+      <c r="P100">
+        <v>7.878657650000001</v>
+      </c>
+      <c r="Q100">
+        <v>12.97865765</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.365392348650853</v>
+      </c>
+      <c r="T100">
+        <v>39.8551243305059</v>
+      </c>
+      <c r="U100">
+        <v>0.0609</v>
+      </c>
+      <c r="V100">
+        <v>0.15</v>
+      </c>
+      <c r="W100">
+        <v>0.051765</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>3.057041170299719</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.09808537074739045</v>
+      </c>
+      <c r="C101">
+        <v>-2.762785215213299</v>
+      </c>
+      <c r="D101">
+        <v>69.29221478478671</v>
+      </c>
+      <c r="E101">
+        <v>31.44500000000001</v>
+      </c>
+      <c r="F101">
+        <v>74.745</v>
+      </c>
+      <c r="G101">
+        <v>2.69</v>
+      </c>
+      <c r="H101">
+        <v>32.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>18.875</v>
+      </c>
+      <c r="K101">
+        <v>5.1</v>
+      </c>
+      <c r="L101">
+        <v>13.775</v>
+      </c>
+      <c r="M101">
+        <v>4.5519705</v>
+      </c>
+      <c r="N101">
+        <v>9.223029499999999</v>
+      </c>
+      <c r="O101">
+        <v>1.383454425</v>
+      </c>
+      <c r="P101">
+        <v>7.839575074999999</v>
+      </c>
+      <c r="Q101">
+        <v>12.939575075</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.683802074739041</v>
+      </c>
+      <c r="T101">
+        <v>79.57007823546489</v>
+      </c>
+      <c r="U101">
+        <v>0.0609</v>
+      </c>
+      <c r="V101">
+        <v>0.15</v>
+      </c>
+      <c r="W101">
+        <v>0.051765</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>3.026161966559317</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/lithuania/lithuania_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_furn_home_furnishings.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0968211076043245</v>
+        <v>0.09671412594291799</v>
       </c>
       <c r="C2">
-        <v>70.63538354369057</v>
+        <v>69.97800218929052</v>
       </c>
       <c r="D2">
-        <v>70.26038354369057</v>
+        <v>70.31400218929052</v>
       </c>
       <c r="E2">
-        <v>-28.5</v>
+        <v>-27.789</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="G2">
         <v>0.375</v>
@@ -1451,28 +1451,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0357633</v>
       </c>
       <c r="N2">
-        <v>13.87142857142857</v>
+        <v>13.83566527142857</v>
       </c>
       <c r="O2">
-        <v>2.080714285714286</v>
+        <v>2.075349790714286</v>
       </c>
       <c r="P2">
-        <v>11.79071428571428</v>
+        <v>11.76031548071428</v>
       </c>
       <c r="Q2">
-        <v>16.49071428571428</v>
+        <v>16.46031548071429</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0968211076043245</v>
+        <v>0.09725916761910909</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460947</v>
+        <v>0.9424927266571974</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>387.8676903817201</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09671412594291799</v>
+        <v>0.09660714428151151</v>
       </c>
       <c r="C3">
-        <v>69.97800218929052</v>
+        <v>69.32070273466636</v>
       </c>
       <c r="D3">
-        <v>70.31400218929052</v>
+        <v>70.36770273466635</v>
       </c>
       <c r="E3">
-        <v>-27.789</v>
+        <v>-27.078</v>
       </c>
       <c r="F3">
-        <v>0.711</v>
+        <v>1.422</v>
       </c>
       <c r="G3">
         <v>0.375</v>
@@ -1533,28 +1533,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M3">
-        <v>0.0357633</v>
+        <v>0.0715266</v>
       </c>
       <c r="N3">
-        <v>13.83566527142857</v>
+        <v>13.79990197142857</v>
       </c>
       <c r="O3">
-        <v>2.075349790714286</v>
+        <v>2.069985295714285</v>
       </c>
       <c r="P3">
-        <v>11.76031548071428</v>
+        <v>11.72991667571428</v>
       </c>
       <c r="Q3">
-        <v>16.46031548071429</v>
+        <v>16.42991667571428</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09725916761910909</v>
+        <v>0.09770616763419543</v>
       </c>
       <c r="T3">
-        <v>0.9424927266571974</v>
+        <v>0.950679688913425</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>387.8676903817201</v>
+        <v>193.93384519086</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09660714428151151</v>
+        <v>0.09650016262010502</v>
       </c>
       <c r="C4">
-        <v>69.32070273466636</v>
+        <v>68.66348536760819</v>
       </c>
       <c r="D4">
-        <v>70.36770273466635</v>
+        <v>70.42148536760818</v>
       </c>
       <c r="E4">
-        <v>-27.078</v>
+        <v>-26.367</v>
       </c>
       <c r="F4">
-        <v>1.422</v>
+        <v>2.133</v>
       </c>
       <c r="G4">
         <v>0.375</v>
@@ -1615,28 +1615,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M4">
-        <v>0.0715266</v>
+        <v>0.1072899</v>
       </c>
       <c r="N4">
-        <v>13.79990197142857</v>
+        <v>13.76413867142857</v>
       </c>
       <c r="O4">
-        <v>2.069985295714285</v>
+        <v>2.064620800714286</v>
       </c>
       <c r="P4">
-        <v>11.72991667571428</v>
+        <v>11.69951787071428</v>
       </c>
       <c r="Q4">
-        <v>16.42991667571428</v>
+        <v>16.39951787071428</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09770616763419543</v>
+        <v>0.09816238414443818</v>
       </c>
       <c r="T4">
-        <v>0.950679688913425</v>
+        <v>0.9590354545151415</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>193.93384519086</v>
+        <v>129.2892301272401</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09650016262010502</v>
+        <v>0.09639318095869853</v>
       </c>
       <c r="C5">
-        <v>68.66348536760819</v>
+        <v>68.00635027648065</v>
       </c>
       <c r="D5">
-        <v>70.42148536760818</v>
+        <v>70.47535027648064</v>
       </c>
       <c r="E5">
-        <v>-26.367</v>
+        <v>-25.656</v>
       </c>
       <c r="F5">
-        <v>2.133</v>
+        <v>2.844</v>
       </c>
       <c r="G5">
         <v>0.375</v>
@@ -1697,28 +1697,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M5">
-        <v>0.1072899</v>
+        <v>0.1430532</v>
       </c>
       <c r="N5">
-        <v>13.76413867142857</v>
+        <v>13.72837537142857</v>
       </c>
       <c r="O5">
-        <v>2.064620800714286</v>
+        <v>2.059256305714285</v>
       </c>
       <c r="P5">
-        <v>11.69951787071428</v>
+        <v>11.66911906571428</v>
       </c>
       <c r="Q5">
-        <v>16.39951787071428</v>
+        <v>16.36911906571428</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09816238414443818</v>
+        <v>0.09862810516531098</v>
       </c>
       <c r="T5">
-        <v>0.9590354545151415</v>
+        <v>0.9675652985668939</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>129.2892301272401</v>
+        <v>96.96692259543002</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09639318095869853</v>
+        <v>0.09628619929729205</v>
       </c>
       <c r="C6">
-        <v>68.00635027648065</v>
+        <v>67.34929765022511</v>
       </c>
       <c r="D6">
-        <v>70.47535027648064</v>
+        <v>70.52929765022512</v>
       </c>
       <c r="E6">
-        <v>-25.656</v>
+        <v>-24.945</v>
       </c>
       <c r="F6">
-        <v>2.844</v>
+        <v>3.555</v>
       </c>
       <c r="G6">
         <v>0.375</v>
@@ -1779,28 +1779,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M6">
-        <v>0.1430532</v>
+        <v>0.1788165</v>
       </c>
       <c r="N6">
-        <v>13.72837537142857</v>
+        <v>13.69261207142857</v>
       </c>
       <c r="O6">
-        <v>2.059256305714285</v>
+        <v>2.053891810714286</v>
       </c>
       <c r="P6">
-        <v>11.66911906571428</v>
+        <v>11.63872026071429</v>
       </c>
       <c r="Q6">
-        <v>16.36911906571428</v>
+        <v>16.33872026071428</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09862810516531098</v>
+        <v>0.0991036308392548</v>
       </c>
       <c r="T6">
-        <v>0.9675652985668939</v>
+        <v>0.9762747182828937</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>96.96692259543002</v>
+        <v>77.57353807634402</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09628619929729205</v>
+        <v>0.09617921763588556</v>
       </c>
       <c r="C7">
-        <v>67.34929765022511</v>
+        <v>66.69232767836198</v>
       </c>
       <c r="D7">
-        <v>70.52929765022512</v>
+        <v>70.58332767836198</v>
       </c>
       <c r="E7">
-        <v>-24.945</v>
+        <v>-24.234</v>
       </c>
       <c r="F7">
-        <v>3.555</v>
+        <v>4.266</v>
       </c>
       <c r="G7">
         <v>0.375</v>
@@ -1861,28 +1861,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M7">
-        <v>0.1788165</v>
+        <v>0.2145798</v>
       </c>
       <c r="N7">
-        <v>13.69261207142857</v>
+        <v>13.65684877142857</v>
       </c>
       <c r="O7">
-        <v>2.053891810714286</v>
+        <v>2.048527315714285</v>
       </c>
       <c r="P7">
-        <v>11.63872026071429</v>
+        <v>11.60832145571429</v>
       </c>
       <c r="Q7">
-        <v>16.33872026071428</v>
+        <v>16.30832145571429</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0991036308392548</v>
+        <v>0.09958927408072932</v>
       </c>
       <c r="T7">
-        <v>0.9762747182828937</v>
+        <v>0.9851694448013615</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>77.57353807634402</v>
+        <v>64.64461506362002</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09617921763588555</v>
+        <v>0.09607223597447909</v>
       </c>
       <c r="C8">
-        <v>66.69232767836198</v>
+        <v>66.03544055099277</v>
       </c>
       <c r="D8">
-        <v>70.58332767836198</v>
+        <v>70.63744055099278</v>
       </c>
       <c r="E8">
-        <v>-24.234</v>
+        <v>-23.523</v>
       </c>
       <c r="F8">
-        <v>4.265999999999999</v>
+        <v>4.976999999999999</v>
       </c>
       <c r="G8">
         <v>0.375</v>
@@ -1943,28 +1943,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M8">
-        <v>0.2145797999999999</v>
+        <v>0.2503431</v>
       </c>
       <c r="N8">
-        <v>13.65684877142857</v>
+        <v>13.62108547142857</v>
       </c>
       <c r="O8">
-        <v>2.048527315714285</v>
+        <v>2.043162820714286</v>
       </c>
       <c r="P8">
-        <v>11.60832145571429</v>
+        <v>11.57792265071429</v>
       </c>
       <c r="Q8">
-        <v>16.30832145571429</v>
+        <v>16.27792265071428</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09958927408072932</v>
+        <v>0.1000853612628807</v>
       </c>
       <c r="T8">
-        <v>0.9851694448013615</v>
+        <v>0.9942554557610868</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>64.64461506362004</v>
+        <v>55.40967005453145</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09607223597447907</v>
+        <v>0.0959652543130726</v>
       </c>
       <c r="C9">
-        <v>66.03544055099277</v>
+        <v>65.37863645880246</v>
       </c>
       <c r="D9">
-        <v>70.63744055099278</v>
+        <v>70.69163645880246</v>
       </c>
       <c r="E9">
-        <v>-23.523</v>
+        <v>-22.812</v>
       </c>
       <c r="F9">
-        <v>4.977</v>
+        <v>5.688</v>
       </c>
       <c r="G9">
         <v>0.375</v>
@@ -2025,28 +2025,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M9">
-        <v>0.2503431</v>
+        <v>0.2861064</v>
       </c>
       <c r="N9">
-        <v>13.62108547142857</v>
+        <v>13.58532217142857</v>
       </c>
       <c r="O9">
-        <v>2.043162820714286</v>
+        <v>2.037798325714285</v>
       </c>
       <c r="P9">
-        <v>11.57792265071429</v>
+        <v>11.54752384571428</v>
       </c>
       <c r="Q9">
-        <v>16.27792265071428</v>
+        <v>16.24752384571428</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1000853612628807</v>
+        <v>0.1005922329489919</v>
       </c>
       <c r="T9">
-        <v>0.9942554557610868</v>
+        <v>1.003538988698197</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>55.40967005453145</v>
+        <v>48.48346129771502</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0959652543130726</v>
+        <v>0.09585827265166612</v>
       </c>
       <c r="C10">
-        <v>65.37863645880246</v>
+        <v>64.72191559306167</v>
       </c>
       <c r="D10">
-        <v>70.69163645880246</v>
+        <v>70.74591559306167</v>
       </c>
       <c r="E10">
-        <v>-22.812</v>
+        <v>-22.101</v>
       </c>
       <c r="F10">
-        <v>5.688</v>
+        <v>6.398999999999999</v>
       </c>
       <c r="G10">
         <v>0.375</v>
@@ -2107,28 +2107,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M10">
-        <v>0.2861064</v>
+        <v>0.3218696999999999</v>
       </c>
       <c r="N10">
-        <v>13.58532217142857</v>
+        <v>13.54955887142857</v>
       </c>
       <c r="O10">
-        <v>2.037798325714285</v>
+        <v>2.032433830714286</v>
       </c>
       <c r="P10">
-        <v>11.54752384571428</v>
+        <v>11.51712504071428</v>
       </c>
       <c r="Q10">
-        <v>16.24752384571428</v>
+        <v>16.21712504071428</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1005922329489919</v>
+        <v>0.1011102446721606</v>
       </c>
       <c r="T10">
-        <v>1.003538988698197</v>
+        <v>1.013026555326233</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>48.48346129771502</v>
+        <v>43.09641004241335</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09585827265166612</v>
+        <v>0.09575129099025963</v>
       </c>
       <c r="C11">
-        <v>64.72191559306167</v>
+        <v>64.06527814562889</v>
       </c>
       <c r="D11">
-        <v>70.74591559306167</v>
+        <v>70.80027814562889</v>
       </c>
       <c r="E11">
-        <v>-22.101</v>
+        <v>-21.39</v>
       </c>
       <c r="F11">
-        <v>6.398999999999999</v>
+        <v>7.109999999999999</v>
       </c>
       <c r="G11">
         <v>0.375</v>
@@ -2189,28 +2189,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M11">
-        <v>0.3218696999999999</v>
+        <v>0.3576329999999999</v>
       </c>
       <c r="N11">
-        <v>13.54955887142857</v>
+        <v>13.51379557142857</v>
       </c>
       <c r="O11">
-        <v>2.032433830714286</v>
+        <v>2.027069335714285</v>
       </c>
       <c r="P11">
-        <v>11.51712504071428</v>
+        <v>11.48672623571428</v>
       </c>
       <c r="Q11">
-        <v>16.21712504071428</v>
+        <v>16.18672623571428</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1011102446721606</v>
+        <v>0.1016397677669551</v>
       </c>
       <c r="T11">
-        <v>1.013026555326233</v>
+        <v>1.022724956768226</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>43.09641004241335</v>
+        <v>38.78676903817202</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09575129099025963</v>
+        <v>0.09564430932885315</v>
       </c>
       <c r="C12">
-        <v>64.06527814562889</v>
+        <v>63.40872430895284</v>
       </c>
       <c r="D12">
-        <v>70.80027814562889</v>
+        <v>70.85472430895284</v>
       </c>
       <c r="E12">
-        <v>-21.39</v>
+        <v>-20.679</v>
       </c>
       <c r="F12">
-        <v>7.109999999999999</v>
+        <v>7.821</v>
       </c>
       <c r="G12">
         <v>0.375</v>
@@ -2271,28 +2271,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M12">
-        <v>0.357633</v>
+        <v>0.3933963</v>
       </c>
       <c r="N12">
-        <v>13.51379557142857</v>
+        <v>13.47803227142857</v>
       </c>
       <c r="O12">
-        <v>2.027069335714285</v>
+        <v>2.021704840714285</v>
       </c>
       <c r="P12">
-        <v>11.48672623571428</v>
+        <v>11.45632743071429</v>
       </c>
       <c r="Q12">
-        <v>16.18672623571428</v>
+        <v>16.15632743071428</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1016397677669551</v>
+        <v>0.1021811902571384</v>
       </c>
       <c r="T12">
-        <v>1.022724956768226</v>
+        <v>1.032641299815656</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>38.78676903817201</v>
+        <v>35.26069912561092</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09564430932885315</v>
+        <v>0.09553732766744666</v>
       </c>
       <c r="C13">
-        <v>63.40872430895284</v>
+        <v>62.75225427607464</v>
       </c>
       <c r="D13">
-        <v>70.85472430895284</v>
+        <v>70.90925427607463</v>
       </c>
       <c r="E13">
-        <v>-20.679</v>
+        <v>-19.968</v>
       </c>
       <c r="F13">
-        <v>7.821</v>
+        <v>8.531999999999998</v>
       </c>
       <c r="G13">
         <v>0.375</v>
@@ -2353,28 +2353,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M13">
-        <v>0.3933963</v>
+        <v>0.4291595999999999</v>
       </c>
       <c r="N13">
-        <v>13.47803227142857</v>
+        <v>13.44226897142857</v>
       </c>
       <c r="O13">
-        <v>2.021704840714285</v>
+        <v>2.016340345714285</v>
       </c>
       <c r="P13">
-        <v>11.45632743071429</v>
+        <v>11.42592862571428</v>
       </c>
       <c r="Q13">
-        <v>16.15632743071428</v>
+        <v>16.12592862571428</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1021811902571384</v>
+        <v>0.1027349178039167</v>
       </c>
       <c r="T13">
-        <v>1.032641299815656</v>
+        <v>1.042783014295983</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>35.26069912561092</v>
+        <v>32.32230753181002</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09553732766744666</v>
+        <v>0.09543034600604015</v>
       </c>
       <c r="C14">
-        <v>62.75225427607464</v>
+        <v>62.09586824063012</v>
       </c>
       <c r="D14">
-        <v>70.90925427607463</v>
+        <v>70.96386824063012</v>
       </c>
       <c r="E14">
-        <v>-19.968</v>
+        <v>-19.257</v>
       </c>
       <c r="F14">
-        <v>8.531999999999998</v>
+        <v>9.243</v>
       </c>
       <c r="G14">
         <v>0.375</v>
@@ -2435,28 +2435,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M14">
-        <v>0.4291595999999999</v>
+        <v>0.4649229</v>
       </c>
       <c r="N14">
-        <v>13.44226897142857</v>
+        <v>13.40650567142857</v>
       </c>
       <c r="O14">
-        <v>2.016340345714285</v>
+        <v>2.010975850714285</v>
       </c>
       <c r="P14">
-        <v>11.42592862571428</v>
+        <v>11.39552982071429</v>
       </c>
       <c r="Q14">
-        <v>16.12592862571428</v>
+        <v>16.09552982071428</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1027349178039167</v>
+        <v>0.1033013747195864</v>
       </c>
       <c r="T14">
-        <v>1.042783014295983</v>
+        <v>1.053157871637926</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>32.32230753181002</v>
+        <v>29.83597618320924</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09543034600604015</v>
+        <v>0.09532336434463368</v>
       </c>
       <c r="C15">
-        <v>62.09586824063012</v>
+        <v>61.43956639685211</v>
       </c>
       <c r="D15">
-        <v>70.96386824063012</v>
+        <v>71.01856639685211</v>
       </c>
       <c r="E15">
-        <v>-19.257</v>
+        <v>-18.546</v>
       </c>
       <c r="F15">
-        <v>9.243</v>
+        <v>9.954000000000001</v>
       </c>
       <c r="G15">
         <v>0.375</v>
@@ -2517,28 +2517,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M15">
-        <v>0.4649229</v>
+        <v>0.5006862</v>
       </c>
       <c r="N15">
-        <v>13.40650567142857</v>
+        <v>13.37074237142857</v>
       </c>
       <c r="O15">
-        <v>2.010975850714285</v>
+        <v>2.005611355714285</v>
       </c>
       <c r="P15">
-        <v>11.39552982071429</v>
+        <v>11.36513101571428</v>
       </c>
       <c r="Q15">
-        <v>16.09552982071428</v>
+        <v>16.06513101571429</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1033013747195864</v>
+        <v>0.1038810050518996</v>
       </c>
       <c r="T15">
-        <v>1.053157871637926</v>
+        <v>1.063774004732008</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>29.83597618320924</v>
+        <v>27.70483502726572</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09532336434463368</v>
+        <v>0.09521638268322719</v>
       </c>
       <c r="C16">
-        <v>61.43956639685211</v>
+        <v>60.78334893957278</v>
       </c>
       <c r="D16">
-        <v>71.01856639685211</v>
+        <v>71.07334893957278</v>
       </c>
       <c r="E16">
-        <v>-18.546</v>
+        <v>-17.835</v>
       </c>
       <c r="F16">
-        <v>9.954000000000001</v>
+        <v>10.665</v>
       </c>
       <c r="G16">
         <v>0.375</v>
@@ -2599,28 +2599,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M16">
-        <v>0.5006862</v>
+        <v>0.5364495</v>
       </c>
       <c r="N16">
-        <v>13.37074237142857</v>
+        <v>13.33497907142857</v>
       </c>
       <c r="O16">
-        <v>2.005611355714285</v>
+        <v>2.000246860714285</v>
       </c>
       <c r="P16">
-        <v>11.36513101571428</v>
+        <v>11.33473221071429</v>
       </c>
       <c r="Q16">
-        <v>16.06513101571429</v>
+        <v>16.03473221071429</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1038810050518996</v>
+        <v>0.1044742737449732</v>
       </c>
       <c r="T16">
-        <v>1.063774004732008</v>
+        <v>1.074639929193009</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>27.70483502726572</v>
+        <v>25.857846025448</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09521638268322719</v>
+        <v>0.09510940102182069</v>
       </c>
       <c r="C17">
-        <v>60.78334893957278</v>
+        <v>60.12721606422594</v>
       </c>
       <c r="D17">
-        <v>71.07334893957278</v>
+        <v>71.12821606422594</v>
       </c>
       <c r="E17">
-        <v>-17.835</v>
+        <v>-17.124</v>
       </c>
       <c r="F17">
-        <v>10.665</v>
+        <v>11.376</v>
       </c>
       <c r="G17">
         <v>0.375</v>
@@ -2681,28 +2681,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M17">
-        <v>0.5364494999999999</v>
+        <v>0.5722128</v>
       </c>
       <c r="N17">
-        <v>13.33497907142857</v>
+        <v>13.29921577142857</v>
       </c>
       <c r="O17">
-        <v>2.000246860714285</v>
+        <v>1.994882365714286</v>
       </c>
       <c r="P17">
-        <v>11.33473221071429</v>
+        <v>11.30433340571429</v>
       </c>
       <c r="Q17">
-        <v>16.03473221071429</v>
+        <v>16.00433340571428</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1044742737449732</v>
+        <v>0.1050816678831199</v>
       </c>
       <c r="T17">
-        <v>1.074639929193009</v>
+        <v>1.085764566141177</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.85784602544801</v>
+        <v>24.24173064885751</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09510940102182069</v>
+        <v>0.09500241936041423</v>
       </c>
       <c r="C18">
-        <v>60.12721606422594</v>
+        <v>59.47116796684928</v>
       </c>
       <c r="D18">
-        <v>71.12821606422594</v>
+        <v>71.18316796684928</v>
       </c>
       <c r="E18">
-        <v>-17.124</v>
+        <v>-16.413</v>
       </c>
       <c r="F18">
-        <v>11.376</v>
+        <v>12.087</v>
       </c>
       <c r="G18">
         <v>0.375</v>
@@ -2763,28 +2763,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M18">
-        <v>0.5722128</v>
+        <v>0.6079760999999999</v>
       </c>
       <c r="N18">
-        <v>13.29921577142857</v>
+        <v>13.26345247142857</v>
       </c>
       <c r="O18">
-        <v>1.994882365714286</v>
+        <v>1.989517870714285</v>
       </c>
       <c r="P18">
-        <v>11.30433340571429</v>
+        <v>11.27393460071428</v>
       </c>
       <c r="Q18">
-        <v>16.00433340571428</v>
+        <v>15.97393460071428</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1050816678831199</v>
+        <v>0.1057036980245954</v>
       </c>
       <c r="T18">
-        <v>1.085764566141177</v>
+        <v>1.097157266630264</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.24173064885751</v>
+        <v>22.81574649304236</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09500241936041423</v>
+        <v>0.09489543769900773</v>
       </c>
       <c r="C19">
-        <v>59.47116796684928</v>
+        <v>58.81520484408688</v>
       </c>
       <c r="D19">
-        <v>71.18316796684928</v>
+        <v>71.23820484408688</v>
       </c>
       <c r="E19">
-        <v>-16.413</v>
+        <v>-15.702</v>
       </c>
       <c r="F19">
-        <v>12.087</v>
+        <v>12.798</v>
       </c>
       <c r="G19">
         <v>0.375</v>
@@ -2845,28 +2845,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M19">
-        <v>0.6079760999999999</v>
+        <v>0.6437394</v>
       </c>
       <c r="N19">
-        <v>13.26345247142857</v>
+        <v>13.22768917142857</v>
       </c>
       <c r="O19">
-        <v>1.989517870714285</v>
+        <v>1.984153375714286</v>
       </c>
       <c r="P19">
-        <v>11.27393460071428</v>
+        <v>11.24353579571429</v>
       </c>
       <c r="Q19">
-        <v>15.97393460071428</v>
+        <v>15.94353579571428</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1057036980245954</v>
+        <v>0.1063408996329362</v>
       </c>
       <c r="T19">
-        <v>1.097157266630264</v>
+        <v>1.108827837862988</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.81574649304236</v>
+        <v>21.54820502120667</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09489543769900774</v>
+        <v>0.09478845603760125</v>
       </c>
       <c r="C20">
-        <v>58.81520484408688</v>
+        <v>58.15932689319133</v>
       </c>
       <c r="D20">
-        <v>71.23820484408688</v>
+        <v>71.29332689319133</v>
       </c>
       <c r="E20">
-        <v>-15.702</v>
+        <v>-14.991</v>
       </c>
       <c r="F20">
-        <v>12.798</v>
+        <v>13.509</v>
       </c>
       <c r="G20">
         <v>0.375</v>
@@ -2927,28 +2927,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M20">
-        <v>0.6437393999999999</v>
+        <v>0.6795026999999999</v>
       </c>
       <c r="N20">
-        <v>13.22768917142857</v>
+        <v>13.19192587142857</v>
       </c>
       <c r="O20">
-        <v>1.984153375714286</v>
+        <v>1.978788880714285</v>
       </c>
       <c r="P20">
-        <v>11.24353579571429</v>
+        <v>11.21313699071428</v>
       </c>
       <c r="Q20">
-        <v>15.94353579571428</v>
+        <v>15.91313699071428</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1063408996329362</v>
+        <v>0.1069938346143225</v>
       </c>
       <c r="T20">
-        <v>1.108827837862988</v>
+        <v>1.120786571348372</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.54820502120668</v>
+        <v>20.41408896745896</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09478845603760125</v>
+        <v>0.09468147437619476</v>
       </c>
       <c r="C21">
-        <v>58.15932689319133</v>
+        <v>57.5035343120263</v>
       </c>
       <c r="D21">
-        <v>71.29332689319133</v>
+        <v>71.3485343120263</v>
       </c>
       <c r="E21">
-        <v>-14.991</v>
+        <v>-14.28</v>
       </c>
       <c r="F21">
-        <v>13.509</v>
+        <v>14.22</v>
       </c>
       <c r="G21">
         <v>0.375</v>
@@ -3009,28 +3009,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M21">
-        <v>0.6795026999999999</v>
+        <v>0.715266</v>
       </c>
       <c r="N21">
-        <v>13.19192587142857</v>
+        <v>13.15616257142857</v>
       </c>
       <c r="O21">
-        <v>1.978788880714285</v>
+        <v>1.973424385714285</v>
       </c>
       <c r="P21">
-        <v>11.21313699071428</v>
+        <v>11.18273818571429</v>
       </c>
       <c r="Q21">
-        <v>15.91313699071428</v>
+        <v>15.88273818571428</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1069938346143225</v>
+        <v>0.1076630929702434</v>
       </c>
       <c r="T21">
-        <v>1.120786571348372</v>
+        <v>1.13304427317089</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.41408896745896</v>
+        <v>19.39338451908601</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09468147437619476</v>
+        <v>0.09457449271478827</v>
       </c>
       <c r="C22">
-        <v>57.5035343120263</v>
+        <v>56.84782729906877</v>
       </c>
       <c r="D22">
-        <v>71.3485343120263</v>
+        <v>71.40382729906877</v>
       </c>
       <c r="E22">
-        <v>-14.28</v>
+        <v>-13.569</v>
       </c>
       <c r="F22">
-        <v>14.22</v>
+        <v>14.931</v>
       </c>
       <c r="G22">
         <v>0.375</v>
@@ -3091,28 +3091,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M22">
-        <v>0.715266</v>
+        <v>0.7510293</v>
       </c>
       <c r="N22">
-        <v>13.15616257142857</v>
+        <v>13.12039927142857</v>
       </c>
       <c r="O22">
-        <v>1.973424385714285</v>
+        <v>1.968059890714285</v>
       </c>
       <c r="P22">
-        <v>11.18273818571429</v>
+        <v>11.15233938071428</v>
       </c>
       <c r="Q22">
-        <v>15.88273818571428</v>
+        <v>15.85233938071428</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1076630929702434</v>
+        <v>0.1083492945756813</v>
       </c>
       <c r="T22">
-        <v>1.13304427317089</v>
+        <v>1.145612296558535</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.39338451908601</v>
+        <v>18.46989001817715</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09457449271478827</v>
+        <v>0.09446751105338179</v>
       </c>
       <c r="C23">
-        <v>56.84782729906877</v>
+        <v>56.19220605341145</v>
       </c>
       <c r="D23">
-        <v>71.40382729906877</v>
+        <v>71.45920605341145</v>
       </c>
       <c r="E23">
-        <v>-13.569</v>
+        <v>-12.858</v>
       </c>
       <c r="F23">
-        <v>14.931</v>
+        <v>15.642</v>
       </c>
       <c r="G23">
         <v>0.375</v>
@@ -3173,28 +3173,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M23">
-        <v>0.7510292999999998</v>
+        <v>0.7867926</v>
       </c>
       <c r="N23">
-        <v>13.12039927142857</v>
+        <v>13.08463597142857</v>
       </c>
       <c r="O23">
-        <v>1.968059890714286</v>
+        <v>1.962695395714285</v>
       </c>
       <c r="P23">
-        <v>11.15233938071428</v>
+        <v>11.12194057571428</v>
       </c>
       <c r="Q23">
-        <v>15.85233938071428</v>
+        <v>15.82194057571428</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1083492945756813</v>
+        <v>0.1090530910940792</v>
       </c>
       <c r="T23">
-        <v>1.145612296558535</v>
+        <v>1.15850257695612</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.46989001817715</v>
+        <v>17.63034956280546</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09446751105338179</v>
+        <v>0.09436052939197528</v>
       </c>
       <c r="C24">
-        <v>56.19220605341145</v>
+        <v>55.53667077476518</v>
       </c>
       <c r="D24">
-        <v>71.45920605341145</v>
+        <v>71.51467077476518</v>
       </c>
       <c r="E24">
-        <v>-12.858</v>
+        <v>-12.147</v>
       </c>
       <c r="F24">
-        <v>15.642</v>
+        <v>16.353</v>
       </c>
       <c r="G24">
         <v>0.375</v>
@@ -3255,28 +3255,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M24">
-        <v>0.7867926</v>
+        <v>0.8225558999999999</v>
       </c>
       <c r="N24">
-        <v>13.08463597142857</v>
+        <v>13.04887267142857</v>
       </c>
       <c r="O24">
-        <v>1.962695395714285</v>
+        <v>1.957330900714286</v>
       </c>
       <c r="P24">
-        <v>11.12194057571428</v>
+        <v>11.09154177071428</v>
       </c>
       <c r="Q24">
-        <v>15.82194057571428</v>
+        <v>15.79154177071428</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1090530910940792</v>
+        <v>0.1097751680415263</v>
       </c>
       <c r="T24">
-        <v>1.15850257695612</v>
+        <v>1.171727669831564</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.63034956280546</v>
+        <v>16.86381262529218</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09436052939197528</v>
+        <v>0.09425354773056881</v>
       </c>
       <c r="C25">
-        <v>55.53667077476518</v>
+        <v>54.88122166346134</v>
       </c>
       <c r="D25">
-        <v>71.51467077476518</v>
+        <v>71.57022166346134</v>
       </c>
       <c r="E25">
-        <v>-12.147</v>
+        <v>-11.436</v>
       </c>
       <c r="F25">
-        <v>16.353</v>
+        <v>17.064</v>
       </c>
       <c r="G25">
         <v>0.375</v>
@@ -3337,28 +3337,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M25">
-        <v>0.8225558999999999</v>
+        <v>0.8583191999999999</v>
       </c>
       <c r="N25">
-        <v>13.04887267142857</v>
+        <v>13.01310937142857</v>
       </c>
       <c r="O25">
-        <v>1.957330900714286</v>
+        <v>1.951966405714285</v>
       </c>
       <c r="P25">
-        <v>11.09154177071428</v>
+        <v>11.06114296571428</v>
       </c>
       <c r="Q25">
-        <v>15.79154177071428</v>
+        <v>15.76114296571428</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1097751680415263</v>
+        <v>0.1105162470139063</v>
       </c>
       <c r="T25">
-        <v>1.171727669831564</v>
+        <v>1.185300791466888</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.86381262529218</v>
+        <v>16.16115376590501</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09425354773056881</v>
+        <v>0.09414656606916232</v>
       </c>
       <c r="C26">
-        <v>54.88122166346135</v>
+        <v>54.22585892045422</v>
       </c>
       <c r="D26">
-        <v>71.57022166346134</v>
+        <v>71.62585892045422</v>
       </c>
       <c r="E26">
-        <v>-11.436</v>
+        <v>-10.725</v>
       </c>
       <c r="F26">
-        <v>17.064</v>
+        <v>17.775</v>
       </c>
       <c r="G26">
         <v>0.375</v>
@@ -3419,28 +3419,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M26">
-        <v>0.8583191999999997</v>
+        <v>0.8940824999999999</v>
       </c>
       <c r="N26">
-        <v>13.01310937142857</v>
+        <v>12.97734607142857</v>
       </c>
       <c r="O26">
-        <v>1.951966405714285</v>
+        <v>1.946601910714286</v>
       </c>
       <c r="P26">
-        <v>11.06114296571428</v>
+        <v>11.03074416071428</v>
       </c>
       <c r="Q26">
-        <v>15.76114296571428</v>
+        <v>15.73074416071428</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1105162470139063</v>
+        <v>0.1112770880922164</v>
       </c>
       <c r="T26">
-        <v>1.185300791466888</v>
+        <v>1.199235863012488</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.16115376590501</v>
+        <v>15.51470761526881</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09414656606916232</v>
+        <v>0.09403958440775584</v>
       </c>
       <c r="C27">
-        <v>54.22585892045422</v>
+        <v>53.57058274732348</v>
       </c>
       <c r="D27">
-        <v>71.62585892045422</v>
+        <v>71.68158274732349</v>
       </c>
       <c r="E27">
-        <v>-10.725</v>
+        <v>-10.014</v>
       </c>
       <c r="F27">
-        <v>17.775</v>
+        <v>18.486</v>
       </c>
       <c r="G27">
         <v>0.375</v>
@@ -3501,28 +3501,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M27">
-        <v>0.8940824999999999</v>
+        <v>0.9298457999999999</v>
       </c>
       <c r="N27">
-        <v>12.97734607142857</v>
+        <v>12.94158277142857</v>
       </c>
       <c r="O27">
-        <v>1.946601910714286</v>
+        <v>1.941237415714285</v>
       </c>
       <c r="P27">
-        <v>11.03074416071428</v>
+        <v>11.00034535571428</v>
       </c>
       <c r="Q27">
-        <v>15.73074416071428</v>
+        <v>15.70034535571428</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1112770880922164</v>
+        <v>0.1120584924429133</v>
       </c>
       <c r="T27">
-        <v>1.199235863012488</v>
+        <v>1.213547558113374</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.51470761526881</v>
+        <v>14.91798809160462</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09403958440775584</v>
+        <v>0.09393260274634935</v>
       </c>
       <c r="C28">
-        <v>53.57058274732348</v>
+        <v>52.91539334627657</v>
       </c>
       <c r="D28">
-        <v>71.68158274732349</v>
+        <v>71.73739334627658</v>
       </c>
       <c r="E28">
-        <v>-10.014</v>
+        <v>-9.303000000000001</v>
       </c>
       <c r="F28">
-        <v>18.486</v>
+        <v>19.197</v>
       </c>
       <c r="G28">
         <v>0.375</v>
@@ -3583,28 +3583,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M28">
-        <v>0.9298457999999999</v>
+        <v>0.9656090999999999</v>
       </c>
       <c r="N28">
-        <v>12.94158277142857</v>
+        <v>12.90581947142857</v>
       </c>
       <c r="O28">
-        <v>1.941237415714285</v>
+        <v>1.935872920714286</v>
       </c>
       <c r="P28">
-        <v>11.00034535571428</v>
+        <v>10.96994655071429</v>
       </c>
       <c r="Q28">
-        <v>15.70034535571428</v>
+        <v>15.66994655071428</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1120584924429133</v>
+        <v>0.1128613051319854</v>
       </c>
       <c r="T28">
-        <v>1.213547558113374</v>
+        <v>1.228251354449901</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.91798809160462</v>
+        <v>14.36547001413778</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09393260274634935</v>
+        <v>0.09382562108494286</v>
       </c>
       <c r="C29">
-        <v>52.91539334627657</v>
+        <v>52.26029092015119</v>
       </c>
       <c r="D29">
-        <v>71.73739334627658</v>
+        <v>71.79329092015119</v>
       </c>
       <c r="E29">
-        <v>-9.303000000000001</v>
+        <v>-8.591999999999999</v>
       </c>
       <c r="F29">
-        <v>19.197</v>
+        <v>19.908</v>
       </c>
       <c r="G29">
         <v>0.375</v>
@@ -3665,28 +3665,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M29">
-        <v>0.9656090999999999</v>
+        <v>1.0013724</v>
       </c>
       <c r="N29">
-        <v>12.90581947142857</v>
+        <v>12.87005617142857</v>
       </c>
       <c r="O29">
-        <v>1.935872920714286</v>
+        <v>1.930508425714285</v>
       </c>
       <c r="P29">
-        <v>10.96994655071429</v>
+        <v>10.93954774571429</v>
       </c>
       <c r="Q29">
-        <v>15.66994655071428</v>
+        <v>15.63954774571429</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1128613051319854</v>
+        <v>0.1136864181735318</v>
       </c>
       <c r="T29">
-        <v>1.228251354449901</v>
+        <v>1.243363589573554</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.36547001413778</v>
+        <v>13.85241751363286</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09382562108494286</v>
+        <v>0.09371863942353639</v>
       </c>
       <c r="C30">
-        <v>52.26029092015119</v>
+        <v>51.60527567241768</v>
       </c>
       <c r="D30">
-        <v>71.79329092015119</v>
+        <v>71.84927567241768</v>
       </c>
       <c r="E30">
-        <v>-8.591999999999999</v>
+        <v>-7.881</v>
       </c>
       <c r="F30">
-        <v>19.908</v>
+        <v>20.619</v>
       </c>
       <c r="G30">
         <v>0.375</v>
@@ -3747,28 +3747,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M30">
-        <v>1.0013724</v>
+        <v>1.0371357</v>
       </c>
       <c r="N30">
-        <v>12.87005617142857</v>
+        <v>12.83429287142857</v>
       </c>
       <c r="O30">
-        <v>1.930508425714285</v>
+        <v>1.925143930714285</v>
       </c>
       <c r="P30">
-        <v>10.93954774571429</v>
+        <v>10.90914894071429</v>
       </c>
       <c r="Q30">
-        <v>15.63954774571429</v>
+        <v>15.60914894071428</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1136864181735318</v>
+        <v>0.1145347738359667</v>
       </c>
       <c r="T30">
-        <v>1.243363589573554</v>
+        <v>1.258901521461253</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.85241751363286</v>
+        <v>13.37474794419725</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09371863942353638</v>
+        <v>0.09361165776212987</v>
       </c>
       <c r="C31">
-        <v>51.60527567241769</v>
+        <v>50.95034780718163</v>
       </c>
       <c r="D31">
-        <v>71.84927567241769</v>
+        <v>71.90534780718163</v>
       </c>
       <c r="E31">
-        <v>-7.881000000000004</v>
+        <v>-7.170000000000002</v>
       </c>
       <c r="F31">
-        <v>20.619</v>
+        <v>21.33</v>
       </c>
       <c r="G31">
         <v>0.375</v>
@@ -3829,28 +3829,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M31">
-        <v>1.0371357</v>
+        <v>1.072899</v>
       </c>
       <c r="N31">
-        <v>12.83429287142857</v>
+        <v>12.79852957142857</v>
       </c>
       <c r="O31">
-        <v>1.925143930714285</v>
+        <v>1.919779435714285</v>
       </c>
       <c r="P31">
-        <v>10.90914894071429</v>
+        <v>10.87875013571428</v>
       </c>
       <c r="Q31">
-        <v>15.60914894071428</v>
+        <v>15.57875013571428</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1145347738359667</v>
+        <v>0.1154073682316141</v>
       </c>
       <c r="T31">
-        <v>1.258901521461253</v>
+        <v>1.274883394260029</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.37474794419725</v>
+        <v>12.92892301272401</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09361165776212987</v>
+        <v>0.0938999261007234</v>
       </c>
       <c r="C32">
-        <v>50.95034780718163</v>
+        <v>50.08845755336577</v>
       </c>
       <c r="D32">
-        <v>71.90534780718163</v>
+        <v>71.75445755336577</v>
       </c>
       <c r="E32">
-        <v>-7.170000000000002</v>
+        <v>-6.459000000000003</v>
       </c>
       <c r="F32">
-        <v>21.33</v>
+        <v>22.041</v>
       </c>
       <c r="G32">
         <v>0.375</v>
@@ -3911,45 +3911,45 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M32">
-        <v>1.072899</v>
+        <v>1.1417238</v>
       </c>
       <c r="N32">
-        <v>12.79852957142857</v>
+        <v>12.72970477142857</v>
       </c>
       <c r="O32">
-        <v>1.919779435714285</v>
+        <v>1.909455715714286</v>
       </c>
       <c r="P32">
-        <v>10.87875013571428</v>
+        <v>10.82024905571429</v>
       </c>
       <c r="Q32">
-        <v>15.57875013571428</v>
+        <v>15.52024905571428</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1154073682316141</v>
+        <v>0.1163052552184397</v>
       </c>
       <c r="T32">
-        <v>1.274883394260029</v>
+        <v>1.291328509748625</v>
       </c>
       <c r="U32">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y32">
-        <v>12.92892301272401</v>
+        <v>12.14954840341296</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0938999261007234</v>
+        <v>0.09380569443931691</v>
       </c>
       <c r="C33">
-        <v>50.08845755336577</v>
+        <v>49.42671215355897</v>
       </c>
       <c r="D33">
-        <v>71.75445755336577</v>
+        <v>71.80371215355896</v>
       </c>
       <c r="E33">
-        <v>-6.459000000000003</v>
+        <v>-5.748000000000001</v>
       </c>
       <c r="F33">
-        <v>22.041</v>
+        <v>22.752</v>
       </c>
       <c r="G33">
         <v>0.375</v>
@@ -3993,28 +3993,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M33">
-        <v>1.1417238</v>
+        <v>1.1785536</v>
       </c>
       <c r="N33">
-        <v>12.72970477142857</v>
+        <v>12.69287497142857</v>
       </c>
       <c r="O33">
-        <v>1.909455715714286</v>
+        <v>1.903931245714285</v>
       </c>
       <c r="P33">
-        <v>10.82024905571429</v>
+        <v>10.78894372571428</v>
       </c>
       <c r="Q33">
-        <v>15.52024905571428</v>
+        <v>15.48894372571428</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1163052552184397</v>
+        <v>0.1172295506460543</v>
       </c>
       <c r="T33">
-        <v>1.291328509748625</v>
+        <v>1.308257305104533</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.14954840341296</v>
+        <v>11.7698750158063</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09380569443931691</v>
+        <v>0.09371146277791041</v>
       </c>
       <c r="C34">
-        <v>49.42671215355897</v>
+        <v>48.76503442012896</v>
       </c>
       <c r="D34">
-        <v>71.80371215355896</v>
+        <v>71.85303442012896</v>
       </c>
       <c r="E34">
-        <v>-5.748000000000001</v>
+        <v>-5.036999999999999</v>
       </c>
       <c r="F34">
-        <v>22.752</v>
+        <v>23.463</v>
       </c>
       <c r="G34">
         <v>0.375</v>
@@ -4075,28 +4075,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M34">
-        <v>1.1785536</v>
+        <v>1.2153834</v>
       </c>
       <c r="N34">
-        <v>12.69287497142857</v>
+        <v>12.65604517142857</v>
       </c>
       <c r="O34">
-        <v>1.903931245714285</v>
+        <v>1.898406775714285</v>
       </c>
       <c r="P34">
-        <v>10.78894372571428</v>
+        <v>10.75763839571428</v>
       </c>
       <c r="Q34">
-        <v>15.48894372571428</v>
+        <v>15.45763839571428</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1172295506460543</v>
+        <v>0.1181814369819559</v>
       </c>
       <c r="T34">
-        <v>1.308257305104533</v>
+        <v>1.325691437635243</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.7698750158063</v>
+        <v>11.41321213653944</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09371146277791041</v>
+        <v>0.09361723111650394</v>
       </c>
       <c r="C35">
-        <v>48.76503442012896</v>
+        <v>48.10342449261253</v>
       </c>
       <c r="D35">
-        <v>71.85303442012896</v>
+        <v>71.90242449261252</v>
       </c>
       <c r="E35">
-        <v>-5.036999999999999</v>
+        <v>-4.326000000000001</v>
       </c>
       <c r="F35">
-        <v>23.463</v>
+        <v>24.174</v>
       </c>
       <c r="G35">
         <v>0.375</v>
@@ -4157,28 +4157,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M35">
-        <v>1.2153834</v>
+        <v>1.2522132</v>
       </c>
       <c r="N35">
-        <v>12.65604517142857</v>
+        <v>12.61921537142857</v>
       </c>
       <c r="O35">
-        <v>1.898406775714285</v>
+        <v>1.892882305714285</v>
       </c>
       <c r="P35">
-        <v>10.75763839571428</v>
+        <v>10.72633306571428</v>
       </c>
       <c r="Q35">
-        <v>15.45763839571428</v>
+        <v>15.42633306571428</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1181814369819559</v>
+        <v>0.1191621683583393</v>
       </c>
       <c r="T35">
-        <v>1.325691437635243</v>
+        <v>1.343653877212339</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.41321213653944</v>
+        <v>11.07752942664122</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09361723111650394</v>
+        <v>0.09352299945509746</v>
       </c>
       <c r="C36">
-        <v>48.10342449261253</v>
+        <v>47.44188251093036</v>
       </c>
       <c r="D36">
-        <v>71.90242449261252</v>
+        <v>71.95188251093036</v>
       </c>
       <c r="E36">
-        <v>-4.326000000000001</v>
+        <v>-3.614999999999998</v>
       </c>
       <c r="F36">
-        <v>24.174</v>
+        <v>24.885</v>
       </c>
       <c r="G36">
         <v>0.375</v>
@@ -4239,28 +4239,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M36">
-        <v>1.2522132</v>
+        <v>1.289043</v>
       </c>
       <c r="N36">
-        <v>12.61921537142857</v>
+        <v>12.58238557142857</v>
       </c>
       <c r="O36">
-        <v>1.892882305714285</v>
+        <v>1.887357835714286</v>
       </c>
       <c r="P36">
-        <v>10.72633306571428</v>
+        <v>10.69502773571429</v>
       </c>
       <c r="Q36">
-        <v>15.42633306571428</v>
+        <v>15.39502773571428</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1191621683583393</v>
+        <v>0.1201730760847653</v>
       </c>
       <c r="T36">
-        <v>1.343653877212339</v>
+        <v>1.362169007237961</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.07752942664122</v>
+        <v>10.76102858588004</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09352299945509746</v>
+        <v>0.09342876779369096</v>
       </c>
       <c r="C37">
-        <v>47.44188251093036</v>
+        <v>46.78040861538844</v>
       </c>
       <c r="D37">
-        <v>71.95188251093036</v>
+        <v>72.00140861538844</v>
       </c>
       <c r="E37">
-        <v>-3.614999999999998</v>
+        <v>-2.904</v>
       </c>
       <c r="F37">
-        <v>24.885</v>
+        <v>25.596</v>
       </c>
       <c r="G37">
         <v>0.375</v>
@@ -4321,28 +4321,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M37">
-        <v>1.289043</v>
+        <v>1.3258728</v>
       </c>
       <c r="N37">
-        <v>12.58238557142857</v>
+        <v>12.54555577142857</v>
       </c>
       <c r="O37">
-        <v>1.887357835714286</v>
+        <v>1.881833365714286</v>
       </c>
       <c r="P37">
-        <v>10.69502773571429</v>
+        <v>10.66372240571429</v>
       </c>
       <c r="Q37">
-        <v>15.39502773571428</v>
+        <v>15.36372240571428</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1201730760847653</v>
+        <v>0.1212155746776421</v>
       </c>
       <c r="T37">
-        <v>1.362169007237961</v>
+        <v>1.381262735076884</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.76102858588004</v>
+        <v>10.46211112516115</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09342876779369096</v>
+        <v>0.0933345361322845</v>
       </c>
       <c r="C38">
-        <v>46.78040861538845</v>
+        <v>46.11900294667927</v>
       </c>
       <c r="D38">
-        <v>72.00140861538844</v>
+        <v>72.05100294667928</v>
       </c>
       <c r="E38">
-        <v>-2.904000000000003</v>
+        <v>-2.193000000000001</v>
       </c>
       <c r="F38">
-        <v>25.596</v>
+        <v>26.307</v>
       </c>
       <c r="G38">
         <v>0.375</v>
@@ -4403,28 +4403,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M38">
-        <v>1.3258728</v>
+        <v>1.3627026</v>
       </c>
       <c r="N38">
-        <v>12.54555577142857</v>
+        <v>12.50872597142857</v>
       </c>
       <c r="O38">
-        <v>1.881833365714286</v>
+        <v>1.876308895714285</v>
       </c>
       <c r="P38">
-        <v>10.66372240571429</v>
+        <v>10.63241707571428</v>
       </c>
       <c r="Q38">
-        <v>15.36372240571428</v>
+        <v>15.33241707571428</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1212155746776421</v>
+        <v>0.1222911684639436</v>
       </c>
       <c r="T38">
-        <v>1.381262735076884</v>
+        <v>1.400962613005931</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.46211112516116</v>
+        <v>10.17935136502166</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0933345361322845</v>
+        <v>0.093240304470878</v>
       </c>
       <c r="C39">
-        <v>46.11900294667927</v>
+        <v>45.4576656458833</v>
       </c>
       <c r="D39">
-        <v>72.05100294667928</v>
+        <v>72.1006656458833</v>
       </c>
       <c r="E39">
-        <v>-2.193000000000001</v>
+        <v>-1.482000000000003</v>
       </c>
       <c r="F39">
-        <v>26.307</v>
+        <v>27.018</v>
       </c>
       <c r="G39">
         <v>0.375</v>
@@ -4485,28 +4485,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M39">
-        <v>1.3627026</v>
+        <v>1.3995324</v>
       </c>
       <c r="N39">
-        <v>12.50872597142857</v>
+        <v>12.47189617142857</v>
       </c>
       <c r="O39">
-        <v>1.876308895714285</v>
+        <v>1.870784425714285</v>
       </c>
       <c r="P39">
-        <v>10.63241707571428</v>
+        <v>10.60111174571428</v>
       </c>
       <c r="Q39">
-        <v>15.33241707571428</v>
+        <v>15.30111174571428</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1222911684639436</v>
+        <v>0.1234014588239968</v>
       </c>
       <c r="T39">
-        <v>1.400962613005931</v>
+        <v>1.421297970868173</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.17935136502166</v>
+        <v>9.911473697521094</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.093240304470878</v>
+        <v>0.09370962280947151</v>
       </c>
       <c r="C40">
-        <v>45.4576656458833</v>
+        <v>44.49999816169995</v>
       </c>
       <c r="D40">
-        <v>72.1006656458833</v>
+        <v>71.85399816169995</v>
       </c>
       <c r="E40">
-        <v>-1.482000000000003</v>
+        <v>-0.7710000000000008</v>
       </c>
       <c r="F40">
-        <v>27.018</v>
+        <v>27.729</v>
       </c>
       <c r="G40">
         <v>0.375</v>
@@ -4567,45 +4567,45 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M40">
-        <v>1.3995324</v>
+        <v>1.4835015</v>
       </c>
       <c r="N40">
-        <v>12.47189617142857</v>
+        <v>12.38792707142857</v>
       </c>
       <c r="O40">
-        <v>1.870784425714285</v>
+        <v>1.858189060714285</v>
       </c>
       <c r="P40">
-        <v>10.60111174571428</v>
+        <v>10.52973801071429</v>
       </c>
       <c r="Q40">
-        <v>15.30111174571428</v>
+        <v>15.22973801071429</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1234014588239968</v>
+        <v>0.1245481521466746</v>
       </c>
       <c r="T40">
-        <v>1.421297970868173</v>
+        <v>1.442300061775079</v>
       </c>
       <c r="U40">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>9.911473697521094</v>
+        <v>9.350464810064951</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09370962280947151</v>
+        <v>0.09362984114806502</v>
       </c>
       <c r="C41">
-        <v>44.49999816169995</v>
+        <v>43.83081120419436</v>
       </c>
       <c r="D41">
-        <v>71.85399816169995</v>
+        <v>71.89581120419436</v>
       </c>
       <c r="E41">
-        <v>-0.7710000000000008</v>
+        <v>-0.06000000000000227</v>
       </c>
       <c r="F41">
-        <v>27.729</v>
+        <v>28.44</v>
       </c>
       <c r="G41">
         <v>0.375</v>
@@ -4649,28 +4649,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M41">
-        <v>1.4835015</v>
+        <v>1.52154</v>
       </c>
       <c r="N41">
-        <v>12.38792707142857</v>
+        <v>12.34988857142857</v>
       </c>
       <c r="O41">
-        <v>1.858189060714285</v>
+        <v>1.852483285714285</v>
       </c>
       <c r="P41">
-        <v>10.52973801071429</v>
+        <v>10.49740528571428</v>
       </c>
       <c r="Q41">
-        <v>15.22973801071429</v>
+        <v>15.19740528571428</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1245481521466746</v>
+        <v>0.1257330685801084</v>
       </c>
       <c r="T41">
-        <v>1.442300061775079</v>
+        <v>1.464002222378882</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.350464810064951</v>
+        <v>9.116703189813329</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09362984114806502</v>
+        <v>0.09355005948665852</v>
       </c>
       <c r="C42">
-        <v>43.83081120419436</v>
+        <v>43.16167293843989</v>
       </c>
       <c r="D42">
-        <v>71.89581120419436</v>
+        <v>71.93767293843989</v>
       </c>
       <c r="E42">
-        <v>-0.06000000000000227</v>
+        <v>0.6509999999999998</v>
       </c>
       <c r="F42">
-        <v>28.44</v>
+        <v>29.151</v>
       </c>
       <c r="G42">
         <v>0.375</v>
@@ -4731,28 +4731,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M42">
-        <v>1.52154</v>
+        <v>1.5595785</v>
       </c>
       <c r="N42">
-        <v>12.34988857142857</v>
+        <v>12.31185007142857</v>
       </c>
       <c r="O42">
-        <v>1.852483285714285</v>
+        <v>1.846777510714285</v>
       </c>
       <c r="P42">
-        <v>10.49740528571428</v>
+        <v>10.46507256071428</v>
       </c>
       <c r="Q42">
-        <v>15.19740528571428</v>
+        <v>15.16507256071428</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1257330685801084</v>
+        <v>0.1269581516723026</v>
       </c>
       <c r="T42">
-        <v>1.464002222378882</v>
+        <v>1.48644004944383</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.116703189813329</v>
+        <v>8.894344575427636</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09355005948665852</v>
+        <v>0.09347027782525205</v>
       </c>
       <c r="C43">
-        <v>43.16167293843989</v>
+        <v>42.4925834495392</v>
       </c>
       <c r="D43">
-        <v>71.93767293843989</v>
+        <v>71.97958344953921</v>
       </c>
       <c r="E43">
-        <v>0.6509999999999998</v>
+        <v>1.362000000000002</v>
       </c>
       <c r="F43">
-        <v>29.151</v>
+        <v>29.862</v>
       </c>
       <c r="G43">
         <v>0.375</v>
@@ -4813,28 +4813,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M43">
-        <v>1.5595785</v>
+        <v>1.597617</v>
       </c>
       <c r="N43">
-        <v>12.31185007142857</v>
+        <v>12.27381157142857</v>
       </c>
       <c r="O43">
-        <v>1.846777510714285</v>
+        <v>1.841071735714285</v>
       </c>
       <c r="P43">
-        <v>10.46507256071428</v>
+        <v>10.43273983571429</v>
       </c>
       <c r="Q43">
-        <v>15.16507256071428</v>
+        <v>15.13273983571428</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1269581516723026</v>
+        <v>0.1282254790090553</v>
       </c>
       <c r="T43">
-        <v>1.48644004944383</v>
+        <v>1.509651594683432</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.894344575427636</v>
+        <v>8.682574466488884</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09347027782525205</v>
+        <v>0.09339049616384557</v>
       </c>
       <c r="C44">
-        <v>42.49258344953921</v>
+        <v>41.82354282279346</v>
       </c>
       <c r="D44">
-        <v>71.97958344953921</v>
+        <v>72.02154282279345</v>
       </c>
       <c r="E44">
-        <v>1.361999999999995</v>
+        <v>2.072999999999997</v>
       </c>
       <c r="F44">
-        <v>29.86199999999999</v>
+        <v>30.573</v>
       </c>
       <c r="G44">
         <v>0.375</v>
@@ -4895,28 +4895,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M44">
-        <v>1.597617</v>
+        <v>1.6356555</v>
       </c>
       <c r="N44">
-        <v>12.27381157142857</v>
+        <v>12.23577307142857</v>
       </c>
       <c r="O44">
-        <v>1.841071735714285</v>
+        <v>1.835365960714285</v>
       </c>
       <c r="P44">
-        <v>10.43273983571429</v>
+        <v>10.40040711071428</v>
       </c>
       <c r="Q44">
-        <v>15.13273983571428</v>
+        <v>15.10040711071428</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1282254790090552</v>
+        <v>0.1295372739716589</v>
       </c>
       <c r="T44">
-        <v>1.509651594683432</v>
+        <v>1.53367758010688</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.682574466488886</v>
+        <v>8.480654130058911</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09339049616384557</v>
+        <v>0.09331071450243908</v>
       </c>
       <c r="C45">
-        <v>41.82354282279346</v>
+        <v>41.15455114370274</v>
       </c>
       <c r="D45">
-        <v>72.02154282279345</v>
+        <v>72.06355114370274</v>
       </c>
       <c r="E45">
-        <v>2.072999999999997</v>
+        <v>2.783999999999999</v>
       </c>
       <c r="F45">
-        <v>30.573</v>
+        <v>31.284</v>
       </c>
       <c r="G45">
         <v>0.375</v>
@@ -4977,28 +4977,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M45">
-        <v>1.6356555</v>
+        <v>1.673694</v>
       </c>
       <c r="N45">
-        <v>12.23577307142857</v>
+        <v>12.19773457142857</v>
       </c>
       <c r="O45">
-        <v>1.835365960714285</v>
+        <v>1.829660185714286</v>
       </c>
       <c r="P45">
-        <v>10.40040711071428</v>
+        <v>10.36807438571429</v>
       </c>
       <c r="Q45">
-        <v>15.10040711071428</v>
+        <v>15.06807438571428</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1295372739716589</v>
+        <v>0.1308959187543555</v>
       </c>
       <c r="T45">
-        <v>1.53367758010688</v>
+        <v>1.558561636438308</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.480654130058911</v>
+        <v>8.287911990739389</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09331071450243908</v>
+        <v>0.09323093284103259</v>
       </c>
       <c r="C46">
-        <v>41.15455114370274</v>
+        <v>40.4856084979668</v>
       </c>
       <c r="D46">
-        <v>72.06355114370274</v>
+        <v>72.1056084979668</v>
       </c>
       <c r="E46">
-        <v>2.783999999999999</v>
+        <v>3.494999999999997</v>
       </c>
       <c r="F46">
-        <v>31.284</v>
+        <v>31.995</v>
       </c>
       <c r="G46">
         <v>0.375</v>
@@ -5059,28 +5059,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M46">
-        <v>1.673694</v>
+        <v>1.7117325</v>
       </c>
       <c r="N46">
-        <v>12.19773457142857</v>
+        <v>12.15969607142857</v>
       </c>
       <c r="O46">
-        <v>1.829660185714286</v>
+        <v>1.823954410714285</v>
       </c>
       <c r="P46">
-        <v>10.36807438571429</v>
+        <v>10.33574166071428</v>
       </c>
       <c r="Q46">
-        <v>15.06807438571428</v>
+        <v>15.03574166071428</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1308959187543555</v>
+        <v>0.1323039688018774</v>
       </c>
       <c r="T46">
-        <v>1.558561636438308</v>
+        <v>1.584350567545424</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.287911990739389</v>
+        <v>8.103736168722957</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09323093284103259</v>
+        <v>0.09315115117962611</v>
       </c>
       <c r="C47">
-        <v>40.4856084979668</v>
+        <v>39.81671497148552</v>
       </c>
       <c r="D47">
-        <v>72.1056084979668</v>
+        <v>72.14771497148551</v>
       </c>
       <c r="E47">
-        <v>3.494999999999997</v>
+        <v>4.205999999999996</v>
       </c>
       <c r="F47">
-        <v>31.995</v>
+        <v>32.706</v>
       </c>
       <c r="G47">
         <v>0.375</v>
@@ -5141,28 +5141,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M47">
-        <v>1.7117325</v>
+        <v>1.749771</v>
       </c>
       <c r="N47">
-        <v>12.15969607142857</v>
+        <v>12.12165757142857</v>
       </c>
       <c r="O47">
-        <v>1.823954410714285</v>
+        <v>1.818248635714286</v>
       </c>
       <c r="P47">
-        <v>10.33574166071428</v>
+        <v>10.30340893571429</v>
       </c>
       <c r="Q47">
-        <v>15.03574166071428</v>
+        <v>15.00340893571429</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1323039688018774</v>
+        <v>0.1337641688511594</v>
       </c>
       <c r="T47">
-        <v>1.584350567545424</v>
+        <v>1.6110946442491</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.103736168722957</v>
+        <v>7.927567991142025</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09315115117962611</v>
+        <v>0.09307136951821961</v>
       </c>
       <c r="C48">
-        <v>39.81671497148552</v>
+        <v>39.14787065035958</v>
       </c>
       <c r="D48">
-        <v>72.14771497148551</v>
+        <v>72.18987065035958</v>
       </c>
       <c r="E48">
-        <v>4.205999999999996</v>
+        <v>4.917000000000002</v>
       </c>
       <c r="F48">
-        <v>32.706</v>
+        <v>33.417</v>
       </c>
       <c r="G48">
         <v>0.375</v>
@@ -5223,28 +5223,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M48">
-        <v>1.749771</v>
+        <v>1.7878095</v>
       </c>
       <c r="N48">
-        <v>12.12165757142857</v>
+        <v>12.08361907142857</v>
       </c>
       <c r="O48">
-        <v>1.818248635714286</v>
+        <v>1.812542860714285</v>
       </c>
       <c r="P48">
-        <v>10.30340893571429</v>
+        <v>10.27107621071428</v>
       </c>
       <c r="Q48">
-        <v>15.00340893571429</v>
+        <v>14.97107621071428</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1337641688511594</v>
+        <v>0.1352794707890936</v>
       </c>
       <c r="T48">
-        <v>1.6110946442491</v>
+        <v>1.638847931394425</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.927567991142025</v>
+        <v>7.758896331756024</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09307136951821961</v>
+        <v>0.09331798785681313</v>
       </c>
       <c r="C49">
-        <v>39.14787065035958</v>
+        <v>38.30671939392403</v>
       </c>
       <c r="D49">
-        <v>72.18987065035958</v>
+        <v>72.05971939392403</v>
       </c>
       <c r="E49">
-        <v>4.917000000000002</v>
+        <v>5.628</v>
       </c>
       <c r="F49">
-        <v>33.417</v>
+        <v>34.128</v>
       </c>
       <c r="G49">
         <v>0.375</v>
@@ -5305,45 +5305,45 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M49">
-        <v>1.7878095</v>
+        <v>1.8531504</v>
       </c>
       <c r="N49">
-        <v>12.08361907142857</v>
+        <v>12.01827817142857</v>
       </c>
       <c r="O49">
-        <v>1.812542860714285</v>
+        <v>1.802741725714285</v>
       </c>
       <c r="P49">
-        <v>10.27107621071428</v>
+        <v>10.21553644571429</v>
       </c>
       <c r="Q49">
-        <v>14.97107621071428</v>
+        <v>14.91553644571428</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1352794707890936</v>
+        <v>0.1368530535707945</v>
       </c>
       <c r="T49">
-        <v>1.638847931394425</v>
+        <v>1.667668652660723</v>
       </c>
       <c r="U49">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V49">
         <v>0.15</v>
       </c>
       <c r="W49">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y49">
-        <v>7.758896331756024</v>
+        <v>7.485322600598725</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09331798785681313</v>
+        <v>0.09324500619540664</v>
       </c>
       <c r="C50">
-        <v>38.30671939392403</v>
+        <v>37.63418608395101</v>
       </c>
       <c r="D50">
-        <v>72.05971939392403</v>
+        <v>72.09818608395101</v>
       </c>
       <c r="E50">
-        <v>5.627999999999993</v>
+        <v>6.338999999999999</v>
       </c>
       <c r="F50">
-        <v>34.12799999999999</v>
+        <v>34.839</v>
       </c>
       <c r="G50">
         <v>0.375</v>
@@ -5387,28 +5387,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M50">
-        <v>1.8531504</v>
+        <v>1.8917577</v>
       </c>
       <c r="N50">
-        <v>12.01827817142857</v>
+        <v>11.97967087142857</v>
       </c>
       <c r="O50">
-        <v>1.802741725714285</v>
+        <v>1.796950630714286</v>
       </c>
       <c r="P50">
-        <v>10.21553644571429</v>
+        <v>10.18272024071429</v>
       </c>
       <c r="Q50">
-        <v>14.91553644571428</v>
+        <v>14.88272024071428</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1368530535707945</v>
+        <v>0.1384883454811895</v>
       </c>
       <c r="T50">
-        <v>1.667668652660723</v>
+        <v>1.697619598290405</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.485322600598727</v>
+        <v>7.332560914872222</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09324500619540664</v>
+        <v>0.09317202453400016</v>
       </c>
       <c r="C51">
-        <v>37.63418608395101</v>
+        <v>36.96169386424469</v>
       </c>
       <c r="D51">
-        <v>72.09818608395101</v>
+        <v>72.13669386424469</v>
       </c>
       <c r="E51">
-        <v>6.338999999999999</v>
+        <v>7.049999999999997</v>
       </c>
       <c r="F51">
-        <v>34.839</v>
+        <v>35.55</v>
       </c>
       <c r="G51">
         <v>0.375</v>
@@ -5469,28 +5469,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M51">
-        <v>1.8917577</v>
+        <v>1.930365</v>
       </c>
       <c r="N51">
-        <v>11.97967087142857</v>
+        <v>11.94106357142857</v>
       </c>
       <c r="O51">
-        <v>1.796950630714286</v>
+        <v>1.791159535714286</v>
       </c>
       <c r="P51">
-        <v>10.18272024071429</v>
+        <v>10.14990403571428</v>
       </c>
       <c r="Q51">
-        <v>14.88272024071428</v>
+        <v>14.84990403571428</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1384883454811895</v>
+        <v>0.1401890490680003</v>
       </c>
       <c r="T51">
-        <v>1.697619598290405</v>
+        <v>1.728768581745275</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.332560914872222</v>
+        <v>7.185909696574778</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09317202453400016</v>
+        <v>0.09309904287259367</v>
       </c>
       <c r="C52">
-        <v>36.96169386424469</v>
+        <v>36.28924280067947</v>
       </c>
       <c r="D52">
-        <v>72.13669386424469</v>
+        <v>72.17524280067947</v>
       </c>
       <c r="E52">
-        <v>7.049999999999997</v>
+        <v>7.760999999999996</v>
       </c>
       <c r="F52">
-        <v>35.55</v>
+        <v>36.261</v>
       </c>
       <c r="G52">
         <v>0.375</v>
@@ -5551,28 +5551,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M52">
-        <v>1.930365</v>
+        <v>1.9689723</v>
       </c>
       <c r="N52">
-        <v>11.94106357142857</v>
+        <v>11.90245627142857</v>
       </c>
       <c r="O52">
-        <v>1.791159535714286</v>
+        <v>1.785368440714285</v>
       </c>
       <c r="P52">
-        <v>10.14990403571428</v>
+        <v>10.11708783071428</v>
       </c>
       <c r="Q52">
-        <v>14.84990403571428</v>
+        <v>14.81708783071428</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1401890490680003</v>
+        <v>0.1419591691277422</v>
       </c>
       <c r="T52">
-        <v>1.728768581745275</v>
+        <v>1.761188952279936</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.185909696574778</v>
+        <v>7.04500950644586</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09309904287259367</v>
+        <v>0.09302606121118719</v>
       </c>
       <c r="C53">
-        <v>36.28924280067947</v>
+        <v>35.61683295927055</v>
       </c>
       <c r="D53">
-        <v>72.17524280067947</v>
+        <v>72.21383295927055</v>
       </c>
       <c r="E53">
-        <v>7.760999999999996</v>
+        <v>8.472000000000001</v>
       </c>
       <c r="F53">
-        <v>36.261</v>
+        <v>36.972</v>
       </c>
       <c r="G53">
         <v>0.375</v>
@@ -5633,28 +5633,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M53">
-        <v>1.9689723</v>
+        <v>2.0075796</v>
       </c>
       <c r="N53">
-        <v>11.90245627142857</v>
+        <v>11.86384897142857</v>
       </c>
       <c r="O53">
-        <v>1.785368440714285</v>
+        <v>1.779577345714286</v>
       </c>
       <c r="P53">
-        <v>10.11708783071428</v>
+        <v>10.08427162571429</v>
       </c>
       <c r="Q53">
-        <v>14.81708783071428</v>
+        <v>14.78427162571428</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1419591691277422</v>
+        <v>0.1438030441899733</v>
       </c>
       <c r="T53">
-        <v>1.761188952279936</v>
+        <v>1.794960171586874</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.04500950644586</v>
+        <v>6.909528554398825</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09302606121118719</v>
+        <v>0.09295307954978069</v>
       </c>
       <c r="C54">
-        <v>35.61683295927055</v>
+        <v>34.94446440617447</v>
       </c>
       <c r="D54">
-        <v>72.21383295927055</v>
+        <v>72.25246440617447</v>
       </c>
       <c r="E54">
-        <v>8.472000000000001</v>
+        <v>9.183</v>
       </c>
       <c r="F54">
-        <v>36.972</v>
+        <v>37.683</v>
       </c>
       <c r="G54">
         <v>0.375</v>
@@ -5715,28 +5715,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M54">
-        <v>2.0075796</v>
+        <v>2.0461869</v>
       </c>
       <c r="N54">
-        <v>11.86384897142857</v>
+        <v>11.82524167142857</v>
       </c>
       <c r="O54">
-        <v>1.779577345714286</v>
+        <v>1.773786250714285</v>
       </c>
       <c r="P54">
-        <v>10.08427162571429</v>
+        <v>10.05145542071428</v>
       </c>
       <c r="Q54">
-        <v>14.78427162571428</v>
+        <v>14.75145542071428</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1438030441899733</v>
+        <v>0.14572538202081</v>
       </c>
       <c r="T54">
-        <v>1.794960171586874</v>
+        <v>1.830168464055809</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.909528554398825</v>
+        <v>6.779160091108281</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09295307954978069</v>
+        <v>0.0928800978883742</v>
       </c>
       <c r="C55">
-        <v>34.94446440617447</v>
+        <v>34.27213720768935</v>
       </c>
       <c r="D55">
-        <v>72.25246440617447</v>
+        <v>72.29113720768935</v>
       </c>
       <c r="E55">
-        <v>9.183</v>
+        <v>9.893999999999998</v>
       </c>
       <c r="F55">
-        <v>37.683</v>
+        <v>38.394</v>
       </c>
       <c r="G55">
         <v>0.375</v>
@@ -5797,28 +5797,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M55">
-        <v>2.0461869</v>
+        <v>2.0847942</v>
       </c>
       <c r="N55">
-        <v>11.82524167142857</v>
+        <v>11.78663437142857</v>
       </c>
       <c r="O55">
-        <v>1.773786250714285</v>
+        <v>1.767995155714285</v>
       </c>
       <c r="P55">
-        <v>10.05145542071428</v>
+        <v>10.01863921571428</v>
       </c>
       <c r="Q55">
-        <v>14.75145542071428</v>
+        <v>14.71863921571428</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.14572538202081</v>
+        <v>0.1477312997573352</v>
       </c>
       <c r="T55">
-        <v>1.830168464055809</v>
+        <v>1.866907551849481</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.779160091108281</v>
+        <v>6.653620089421089</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0928800978883742</v>
+        <v>0.09280711622696772</v>
       </c>
       <c r="C56">
-        <v>34.27213720768935</v>
+        <v>33.59985143025533</v>
       </c>
       <c r="D56">
-        <v>72.29113720768935</v>
+        <v>72.32985143025533</v>
       </c>
       <c r="E56">
-        <v>9.893999999999998</v>
+        <v>10.605</v>
       </c>
       <c r="F56">
-        <v>38.394</v>
+        <v>39.105</v>
       </c>
       <c r="G56">
         <v>0.375</v>
@@ -5879,28 +5879,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M56">
-        <v>2.0847942</v>
+        <v>2.1234015</v>
       </c>
       <c r="N56">
-        <v>11.78663437142857</v>
+        <v>11.74802707142857</v>
       </c>
       <c r="O56">
-        <v>1.767995155714285</v>
+        <v>1.762204060714285</v>
       </c>
       <c r="P56">
-        <v>10.01863921571428</v>
+        <v>9.985823010714284</v>
       </c>
       <c r="Q56">
-        <v>14.71863921571428</v>
+        <v>14.68582301071428</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1477312997573352</v>
+        <v>0.1498263693932616</v>
       </c>
       <c r="T56">
-        <v>1.866907551849481</v>
+        <v>1.905279487989538</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.653620089421089</v>
+        <v>6.532645178704343</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09280711622696772</v>
+        <v>0.09273413456556123</v>
       </c>
       <c r="C57">
-        <v>33.59985143025533</v>
+        <v>32.92760714045502</v>
       </c>
       <c r="D57">
-        <v>72.32985143025533</v>
+        <v>72.36860714045503</v>
       </c>
       <c r="E57">
-        <v>10.605</v>
+        <v>11.316</v>
       </c>
       <c r="F57">
-        <v>39.105</v>
+        <v>39.816</v>
       </c>
       <c r="G57">
         <v>0.375</v>
@@ -5961,28 +5961,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M57">
-        <v>2.1234015</v>
+        <v>2.1620088</v>
       </c>
       <c r="N57">
-        <v>11.74802707142857</v>
+        <v>11.70941977142857</v>
       </c>
       <c r="O57">
-        <v>1.762204060714285</v>
+        <v>1.756412965714285</v>
       </c>
       <c r="P57">
-        <v>9.985823010714284</v>
+        <v>9.953006805714285</v>
       </c>
       <c r="Q57">
-        <v>14.68582301071428</v>
+        <v>14.65300680571428</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1498263693932616</v>
+        <v>0.1520166694671846</v>
       </c>
       <c r="T57">
-        <v>1.905279487989538</v>
+        <v>1.945395603045052</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.532645178704343</v>
+        <v>6.415990800513193</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09273413456556123</v>
+        <v>0.09266115290415475</v>
       </c>
       <c r="C58">
-        <v>32.92760714045502</v>
+        <v>32.25540440501373</v>
       </c>
       <c r="D58">
-        <v>72.36860714045503</v>
+        <v>72.40740440501374</v>
       </c>
       <c r="E58">
-        <v>11.316</v>
+        <v>12.027</v>
       </c>
       <c r="F58">
-        <v>39.816</v>
+        <v>40.527</v>
       </c>
       <c r="G58">
         <v>0.375</v>
@@ -6043,28 +6043,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M58">
-        <v>2.1620088</v>
+        <v>2.2006161</v>
       </c>
       <c r="N58">
-        <v>11.70941977142857</v>
+        <v>11.67081247142857</v>
       </c>
       <c r="O58">
-        <v>1.756412965714285</v>
+        <v>1.750621870714286</v>
       </c>
       <c r="P58">
-        <v>9.953006805714285</v>
+        <v>9.920190600714285</v>
       </c>
       <c r="Q58">
-        <v>14.65300680571428</v>
+        <v>14.62019060071428</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1520166694671846</v>
+        <v>0.1543088439631506</v>
       </c>
       <c r="T58">
-        <v>1.945395603045052</v>
+        <v>1.987377583917102</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.415990800513193</v>
+        <v>6.303429558398927</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09266115290415475</v>
+        <v>0.09258817124274826</v>
       </c>
       <c r="C59">
-        <v>32.25540440501373</v>
+        <v>31.5832432908</v>
       </c>
       <c r="D59">
-        <v>72.40740440501374</v>
+        <v>72.4462432908</v>
       </c>
       <c r="E59">
-        <v>12.027</v>
+        <v>12.738</v>
       </c>
       <c r="F59">
-        <v>40.527</v>
+        <v>41.238</v>
       </c>
       <c r="G59">
         <v>0.375</v>
@@ -6125,28 +6125,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M59">
-        <v>2.2006161</v>
+        <v>2.2392234</v>
       </c>
       <c r="N59">
-        <v>11.67081247142857</v>
+        <v>11.63220517142857</v>
       </c>
       <c r="O59">
-        <v>1.750621870714286</v>
+        <v>1.744830775714285</v>
       </c>
       <c r="P59">
-        <v>9.920190600714285</v>
+        <v>9.887374395714284</v>
       </c>
       <c r="Q59">
-        <v>14.62019060071428</v>
+        <v>14.58737439571428</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1543088439631506</v>
+        <v>0.1567101696255911</v>
       </c>
       <c r="T59">
-        <v>1.987377583917102</v>
+        <v>2.03135870673544</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.303429558398927</v>
+        <v>6.194749738426531</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09258817124274826</v>
+        <v>0.09301668958134177</v>
       </c>
       <c r="C60">
-        <v>31.58324329080001</v>
+        <v>30.64479134040652</v>
       </c>
       <c r="D60">
-        <v>72.4462432908</v>
+        <v>72.21879134040651</v>
       </c>
       <c r="E60">
-        <v>12.73799999999999</v>
+        <v>13.44899999999999</v>
       </c>
       <c r="F60">
-        <v>41.23799999999999</v>
+        <v>41.94899999999999</v>
       </c>
       <c r="G60">
         <v>0.375</v>
@@ -6207,45 +6207,45 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M60">
-        <v>2.2392234</v>
+        <v>2.3197797</v>
       </c>
       <c r="N60">
-        <v>11.63220517142857</v>
+        <v>11.55164887142857</v>
       </c>
       <c r="O60">
-        <v>1.744830775714285</v>
+        <v>1.732747330714286</v>
       </c>
       <c r="P60">
-        <v>9.887374395714284</v>
+        <v>9.818901540714284</v>
       </c>
       <c r="Q60">
-        <v>14.58737439571428</v>
+        <v>14.51890154071428</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1567101696255911</v>
+        <v>0.1592286331252238</v>
       </c>
       <c r="T60">
-        <v>2.031358706735439</v>
+        <v>2.077485250179061</v>
       </c>
       <c r="U60">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V60">
         <v>0.15</v>
       </c>
       <c r="W60">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>6.194749738426533</v>
+        <v>5.979631846691551</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09301668958134177</v>
+        <v>0.09295220791993528</v>
       </c>
       <c r="C61">
-        <v>30.64479134040652</v>
+        <v>29.96792603653491</v>
       </c>
       <c r="D61">
-        <v>72.21879134040651</v>
+        <v>72.2529260365349</v>
       </c>
       <c r="E61">
-        <v>13.44899999999999</v>
+        <v>14.16</v>
       </c>
       <c r="F61">
-        <v>41.94899999999999</v>
+        <v>42.66</v>
       </c>
       <c r="G61">
         <v>0.375</v>
@@ -6289,28 +6289,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M61">
-        <v>2.3197797</v>
+        <v>2.359098</v>
       </c>
       <c r="N61">
-        <v>11.55164887142857</v>
+        <v>11.51233057142857</v>
       </c>
       <c r="O61">
-        <v>1.732747330714286</v>
+        <v>1.726849585714286</v>
       </c>
       <c r="P61">
-        <v>9.818901540714284</v>
+        <v>9.785480985714285</v>
       </c>
       <c r="Q61">
-        <v>14.51890154071428</v>
+        <v>14.48548098571428</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1592286331252238</v>
+        <v>0.1618730197998382</v>
       </c>
       <c r="T61">
-        <v>2.077485250179061</v>
+        <v>2.125918120794865</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.979631846691551</v>
+        <v>5.879971315913358</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09295220791993528</v>
+        <v>0.09288772625852879</v>
       </c>
       <c r="C62">
-        <v>29.96792603653491</v>
+        <v>29.29109301590833</v>
       </c>
       <c r="D62">
-        <v>72.2529260365349</v>
+        <v>72.28709301590833</v>
       </c>
       <c r="E62">
-        <v>14.16</v>
+        <v>14.871</v>
       </c>
       <c r="F62">
-        <v>42.66</v>
+        <v>43.371</v>
       </c>
       <c r="G62">
         <v>0.375</v>
@@ -6371,28 +6371,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M62">
-        <v>2.359098</v>
+        <v>2.3984163</v>
       </c>
       <c r="N62">
-        <v>11.51233057142857</v>
+        <v>11.47301227142857</v>
       </c>
       <c r="O62">
-        <v>1.726849585714286</v>
+        <v>1.720951840714286</v>
       </c>
       <c r="P62">
-        <v>9.785480985714285</v>
+        <v>9.752060430714286</v>
       </c>
       <c r="Q62">
-        <v>14.48548098571428</v>
+        <v>14.45206043071429</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1618730197998382</v>
+        <v>0.1646530160475097</v>
       </c>
       <c r="T62">
-        <v>2.125918120794865</v>
+        <v>2.176834728365325</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.879971315913358</v>
+        <v>5.783578343521336</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09288772625852879</v>
+        <v>0.09282324459712232</v>
       </c>
       <c r="C63">
-        <v>29.29109301590833</v>
+        <v>28.61429232434681</v>
       </c>
       <c r="D63">
-        <v>72.28709301590833</v>
+        <v>72.3212923243468</v>
       </c>
       <c r="E63">
-        <v>14.871</v>
+        <v>15.58199999999999</v>
       </c>
       <c r="F63">
-        <v>43.371</v>
+        <v>44.08199999999999</v>
       </c>
       <c r="G63">
         <v>0.375</v>
@@ -6453,28 +6453,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M63">
-        <v>2.3984163</v>
+        <v>2.4377346</v>
       </c>
       <c r="N63">
-        <v>11.47301227142857</v>
+        <v>11.43369397142857</v>
       </c>
       <c r="O63">
-        <v>1.720951840714286</v>
+        <v>1.715054095714286</v>
       </c>
       <c r="P63">
-        <v>9.752060430714286</v>
+        <v>9.718639875714285</v>
       </c>
       <c r="Q63">
-        <v>14.45206043071429</v>
+        <v>14.41863987571428</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1646530160475097</v>
+        <v>0.167579327887164</v>
       </c>
       <c r="T63">
-        <v>2.176834728365325</v>
+        <v>2.230431157386863</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.783578343521336</v>
+        <v>5.690294821851637</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09282324459712232</v>
+        <v>0.09275876293571583</v>
       </c>
       <c r="C64">
-        <v>28.61429232434681</v>
+        <v>27.93752400775704</v>
       </c>
       <c r="D64">
-        <v>72.3212923243468</v>
+        <v>72.35552400775704</v>
       </c>
       <c r="E64">
-        <v>15.58199999999999</v>
+        <v>16.293</v>
       </c>
       <c r="F64">
-        <v>44.08199999999999</v>
+        <v>44.793</v>
       </c>
       <c r="G64">
         <v>0.375</v>
@@ -6535,28 +6535,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M64">
-        <v>2.4377346</v>
+        <v>2.4770529</v>
       </c>
       <c r="N64">
-        <v>11.43369397142857</v>
+        <v>11.39437567142857</v>
       </c>
       <c r="O64">
-        <v>1.715054095714286</v>
+        <v>1.709156350714286</v>
       </c>
       <c r="P64">
-        <v>9.718639875714285</v>
+        <v>9.685219320714284</v>
       </c>
       <c r="Q64">
-        <v>14.41863987571428</v>
+        <v>14.38521932071428</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.167579327887164</v>
+        <v>0.1706638187451779</v>
       </c>
       <c r="T64">
-        <v>2.230431157386863</v>
+        <v>2.286924690679835</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.690294821851637</v>
+        <v>5.599972681822245</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09275876293571583</v>
+        <v>0.09269428127430936</v>
       </c>
       <c r="C65">
-        <v>27.93752400775704</v>
+        <v>27.26078811213279</v>
       </c>
       <c r="D65">
-        <v>72.35552400775704</v>
+        <v>72.38978811213279</v>
       </c>
       <c r="E65">
-        <v>16.293</v>
+        <v>17.004</v>
       </c>
       <c r="F65">
-        <v>44.793</v>
+        <v>45.504</v>
       </c>
       <c r="G65">
         <v>0.375</v>
@@ -6617,28 +6617,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M65">
-        <v>2.4770529</v>
+        <v>2.5163712</v>
       </c>
       <c r="N65">
-        <v>11.39437567142857</v>
+        <v>11.35505737142857</v>
       </c>
       <c r="O65">
-        <v>1.709156350714286</v>
+        <v>1.703258605714286</v>
       </c>
       <c r="P65">
-        <v>9.685219320714284</v>
+        <v>9.651798765714284</v>
       </c>
       <c r="Q65">
-        <v>14.38521932071428</v>
+        <v>14.35179876571428</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1706638187451779</v>
+        <v>0.1739196702064149</v>
       </c>
       <c r="T65">
-        <v>2.286924690679835</v>
+        <v>2.346556753600193</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.599972681822245</v>
+        <v>5.512473108668773</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09269428127430936</v>
+        <v>0.09262979961290285</v>
       </c>
       <c r="C66">
-        <v>27.26078811213279</v>
+        <v>26.58408468355491</v>
       </c>
       <c r="D66">
-        <v>72.38978811213279</v>
+        <v>72.42408468355491</v>
       </c>
       <c r="E66">
-        <v>17.004</v>
+        <v>17.715</v>
       </c>
       <c r="F66">
-        <v>45.504</v>
+        <v>46.215</v>
       </c>
       <c r="G66">
         <v>0.375</v>
@@ -6699,28 +6699,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M66">
-        <v>2.5163712</v>
+        <v>2.5556895</v>
       </c>
       <c r="N66">
-        <v>11.35505737142857</v>
+        <v>11.31573907142857</v>
       </c>
       <c r="O66">
-        <v>1.703258605714286</v>
+        <v>1.697360860714286</v>
       </c>
       <c r="P66">
-        <v>9.651798765714284</v>
+        <v>9.618378210714285</v>
       </c>
       <c r="Q66">
-        <v>14.35179876571428</v>
+        <v>14.31837821071428</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1739196702064149</v>
+        <v>0.1773615703225796</v>
       </c>
       <c r="T66">
-        <v>2.346556753600193</v>
+        <v>2.409596362973145</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.512473108668773</v>
+        <v>5.427665830073869</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09262979961290285</v>
+        <v>0.09256531795149638</v>
       </c>
       <c r="C67">
-        <v>26.58408468355491</v>
+        <v>25.90741376819157</v>
       </c>
       <c r="D67">
-        <v>72.42408468355491</v>
+        <v>72.45841376819158</v>
       </c>
       <c r="E67">
-        <v>17.715</v>
+        <v>18.426</v>
       </c>
       <c r="F67">
-        <v>46.215</v>
+        <v>46.926</v>
       </c>
       <c r="G67">
         <v>0.375</v>
@@ -6781,28 +6781,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M67">
-        <v>2.5556895</v>
+        <v>2.5950078</v>
       </c>
       <c r="N67">
-        <v>11.31573907142857</v>
+        <v>11.27642077142857</v>
       </c>
       <c r="O67">
-        <v>1.697360860714286</v>
+        <v>1.691463115714285</v>
       </c>
       <c r="P67">
-        <v>9.618378210714285</v>
+        <v>9.584957655714284</v>
       </c>
       <c r="Q67">
-        <v>14.31837821071428</v>
+        <v>14.28495765571428</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1773615703225796</v>
+        <v>0.1810059351514599</v>
       </c>
       <c r="T67">
-        <v>2.409596362973145</v>
+        <v>2.476344184662151</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.427665830073869</v>
+        <v>5.345428469012142</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09256531795149638</v>
+        <v>0.09250083629008987</v>
       </c>
       <c r="C68">
-        <v>25.90741376819157</v>
+        <v>25.23077541229864</v>
       </c>
       <c r="D68">
-        <v>72.45841376819158</v>
+        <v>72.49277541229864</v>
       </c>
       <c r="E68">
-        <v>18.426</v>
+        <v>19.137</v>
       </c>
       <c r="F68">
-        <v>46.926</v>
+        <v>47.637</v>
       </c>
       <c r="G68">
         <v>0.375</v>
@@ -6863,28 +6863,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M68">
-        <v>2.5950078</v>
+        <v>2.6343261</v>
       </c>
       <c r="N68">
-        <v>11.27642077142857</v>
+        <v>11.23710247142857</v>
       </c>
       <c r="O68">
-        <v>1.691463115714285</v>
+        <v>1.685565370714286</v>
       </c>
       <c r="P68">
-        <v>9.584957655714284</v>
+        <v>9.551537100714285</v>
       </c>
       <c r="Q68">
-        <v>14.28495765571428</v>
+        <v>14.25153710071428</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1810059351514599</v>
+        <v>0.1848711705760299</v>
       </c>
       <c r="T68">
-        <v>2.476344184662151</v>
+        <v>2.547137328877764</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.345428469012142</v>
+        <v>5.265645954549276</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09250083629008987</v>
+        <v>0.0924363546286834</v>
       </c>
       <c r="C69">
-        <v>25.23077541229864</v>
+        <v>24.55416966221969</v>
       </c>
       <c r="D69">
-        <v>72.49277541229864</v>
+        <v>72.52716966221969</v>
       </c>
       <c r="E69">
-        <v>19.137</v>
+        <v>19.848</v>
       </c>
       <c r="F69">
-        <v>47.637</v>
+        <v>48.348</v>
       </c>
       <c r="G69">
         <v>0.375</v>
@@ -6945,28 +6945,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M69">
-        <v>2.6343261</v>
+        <v>2.6736444</v>
       </c>
       <c r="N69">
-        <v>11.23710247142857</v>
+        <v>11.19778417142857</v>
       </c>
       <c r="O69">
-        <v>1.685565370714286</v>
+        <v>1.679667625714285</v>
       </c>
       <c r="P69">
-        <v>9.551537100714285</v>
+        <v>9.518116545714284</v>
       </c>
       <c r="Q69">
-        <v>14.25153710071428</v>
+        <v>14.21811654571428</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1848711705760299</v>
+        <v>0.1889779832146356</v>
       </c>
       <c r="T69">
-        <v>2.547137328877764</v>
+        <v>2.622355044606854</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.265645954549276</v>
+        <v>5.188209984629433</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0924363546286834</v>
+        <v>0.09237187296727691</v>
       </c>
       <c r="C70">
-        <v>24.55416966221969</v>
+        <v>23.87759656438632</v>
       </c>
       <c r="D70">
-        <v>72.52716966221969</v>
+        <v>72.56159656438632</v>
       </c>
       <c r="E70">
-        <v>19.848</v>
+        <v>20.559</v>
       </c>
       <c r="F70">
-        <v>48.348</v>
+        <v>49.059</v>
       </c>
       <c r="G70">
         <v>0.375</v>
@@ -7027,28 +7027,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M70">
-        <v>2.6736444</v>
+        <v>2.7129627</v>
       </c>
       <c r="N70">
-        <v>11.19778417142857</v>
+        <v>11.15846587142857</v>
       </c>
       <c r="O70">
-        <v>1.679667625714285</v>
+        <v>1.673769880714285</v>
       </c>
       <c r="P70">
-        <v>9.518116545714284</v>
+        <v>9.484695990714284</v>
       </c>
       <c r="Q70">
-        <v>14.21811654571428</v>
+        <v>14.18469599071428</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1889779832146356</v>
+        <v>0.1933497515073449</v>
       </c>
       <c r="T70">
-        <v>2.622355044606854</v>
+        <v>2.702425516189432</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.188209984629433</v>
+        <v>5.113018535576833</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09237187296727691</v>
+        <v>0.09230739130587041</v>
       </c>
       <c r="C71">
-        <v>23.87759656438632</v>
+        <v>23.2010561653183</v>
       </c>
       <c r="D71">
-        <v>72.56159656438632</v>
+        <v>72.5960561653183</v>
       </c>
       <c r="E71">
-        <v>20.559</v>
+        <v>21.27</v>
       </c>
       <c r="F71">
-        <v>49.059</v>
+        <v>49.77</v>
       </c>
       <c r="G71">
         <v>0.375</v>
@@ -7109,28 +7109,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M71">
-        <v>2.7129627</v>
+        <v>2.752281</v>
       </c>
       <c r="N71">
-        <v>11.15846587142857</v>
+        <v>11.11914757142857</v>
       </c>
       <c r="O71">
-        <v>1.673769880714285</v>
+        <v>1.667872135714285</v>
       </c>
       <c r="P71">
-        <v>9.484695990714284</v>
+        <v>9.451275435714285</v>
       </c>
       <c r="Q71">
-        <v>14.18469599071428</v>
+        <v>14.15127543571428</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1933497515073449</v>
+        <v>0.1980129710195681</v>
       </c>
       <c r="T71">
-        <v>2.702425516189432</v>
+        <v>2.78783401921085</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.113018535576833</v>
+        <v>5.03997541364002</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09230739130587041</v>
+        <v>0.09224290964446394</v>
       </c>
       <c r="C72">
-        <v>23.2010561653183</v>
+        <v>22.52454851162383</v>
       </c>
       <c r="D72">
-        <v>72.5960561653183</v>
+        <v>72.63054851162383</v>
       </c>
       <c r="E72">
-        <v>21.27</v>
+        <v>21.981</v>
       </c>
       <c r="F72">
-        <v>49.77</v>
+        <v>50.481</v>
       </c>
       <c r="G72">
         <v>0.375</v>
@@ -7191,28 +7191,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M72">
-        <v>2.752281</v>
+        <v>2.7915993</v>
       </c>
       <c r="N72">
-        <v>11.11914757142857</v>
+        <v>11.07982927142857</v>
       </c>
       <c r="O72">
-        <v>1.667872135714285</v>
+        <v>1.661974390714285</v>
       </c>
       <c r="P72">
-        <v>9.451275435714285</v>
+        <v>9.417854880714286</v>
       </c>
       <c r="Q72">
-        <v>14.15127543571428</v>
+        <v>14.11785488071428</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1980129710195681</v>
+        <v>0.2029977918774619</v>
       </c>
       <c r="T72">
-        <v>2.78783401921085</v>
+        <v>2.879132763819952</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.03997541364002</v>
+        <v>4.968989844433823</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09224290964446394</v>
+        <v>0.09217842798305745</v>
       </c>
       <c r="C73">
-        <v>22.52454851162383</v>
+        <v>21.84807364999975</v>
       </c>
       <c r="D73">
-        <v>72.63054851162383</v>
+        <v>72.66507364999974</v>
       </c>
       <c r="E73">
-        <v>21.98099999999999</v>
+        <v>22.69199999999999</v>
       </c>
       <c r="F73">
-        <v>50.48099999999999</v>
+        <v>51.19199999999999</v>
       </c>
       <c r="G73">
         <v>0.375</v>
@@ -7273,28 +7273,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M73">
-        <v>2.7915993</v>
+        <v>2.8309176</v>
       </c>
       <c r="N73">
-        <v>11.07982927142857</v>
+        <v>11.04051097142857</v>
       </c>
       <c r="O73">
-        <v>1.661974390714285</v>
+        <v>1.656076645714285</v>
       </c>
       <c r="P73">
-        <v>9.417854880714286</v>
+        <v>9.384434325714285</v>
       </c>
       <c r="Q73">
-        <v>14.11785488071428</v>
+        <v>14.08443432571428</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2029977918774618</v>
+        <v>0.2083386713680623</v>
       </c>
       <c r="T73">
-        <v>2.87913276381995</v>
+        <v>2.976952847329701</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.968989844433824</v>
+        <v>4.899976096594465</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09217842798305745</v>
+        <v>0.09211394632165096</v>
       </c>
       <c r="C74">
-        <v>21.84807364999975</v>
+        <v>21.17163162723169</v>
       </c>
       <c r="D74">
-        <v>72.66507364999974</v>
+        <v>72.69963162723168</v>
       </c>
       <c r="E74">
-        <v>22.69199999999999</v>
+        <v>23.40299999999999</v>
       </c>
       <c r="F74">
-        <v>51.19199999999999</v>
+        <v>51.90299999999999</v>
       </c>
       <c r="G74">
         <v>0.375</v>
@@ -7355,28 +7355,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M74">
-        <v>2.8309176</v>
+        <v>2.8702359</v>
       </c>
       <c r="N74">
-        <v>11.04051097142857</v>
+        <v>11.00119267142857</v>
       </c>
       <c r="O74">
-        <v>1.656076645714285</v>
+        <v>1.650178900714286</v>
       </c>
       <c r="P74">
-        <v>9.384434325714285</v>
+        <v>9.351013770714285</v>
       </c>
       <c r="Q74">
-        <v>14.08443432571428</v>
+        <v>14.05101377071428</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2083386713680623</v>
+        <v>0.2140751715616702</v>
       </c>
       <c r="T74">
-        <v>2.976952847329701</v>
+        <v>3.082018862951286</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.899976096594465</v>
+        <v>4.832853136367144</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09211394632165096</v>
+        <v>0.09204946466024447</v>
       </c>
       <c r="C75">
-        <v>21.17163162723169</v>
+        <v>20.49522249019434</v>
       </c>
       <c r="D75">
-        <v>72.69963162723168</v>
+        <v>72.73422249019434</v>
       </c>
       <c r="E75">
-        <v>23.40299999999999</v>
+        <v>24.114</v>
       </c>
       <c r="F75">
-        <v>51.90299999999999</v>
+        <v>52.614</v>
       </c>
       <c r="G75">
         <v>0.375</v>
@@ -7437,28 +7437,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M75">
-        <v>2.8702359</v>
+        <v>2.9095542</v>
       </c>
       <c r="N75">
-        <v>11.00119267142857</v>
+        <v>10.96187437142857</v>
       </c>
       <c r="O75">
-        <v>1.650178900714286</v>
+        <v>1.644281155714285</v>
       </c>
       <c r="P75">
-        <v>9.351013770714285</v>
+        <v>9.317593215714284</v>
       </c>
       <c r="Q75">
-        <v>14.05101377071428</v>
+        <v>14.01759321571428</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2140751715616702</v>
+        <v>0.2202529410009403</v>
       </c>
       <c r="T75">
-        <v>3.082018862951286</v>
+        <v>3.195166879774531</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.832853136367144</v>
+        <v>4.767544310200019</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09204946466024447</v>
+        <v>0.09198498299883798</v>
       </c>
       <c r="C76">
-        <v>20.49522249019434</v>
+        <v>19.81884628585168</v>
       </c>
       <c r="D76">
-        <v>72.73422249019434</v>
+        <v>72.76884628585168</v>
       </c>
       <c r="E76">
-        <v>24.114</v>
+        <v>24.825</v>
       </c>
       <c r="F76">
-        <v>52.614</v>
+        <v>53.325</v>
       </c>
       <c r="G76">
         <v>0.375</v>
@@ -7519,28 +7519,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M76">
-        <v>2.9095542</v>
+        <v>2.9488725</v>
       </c>
       <c r="N76">
-        <v>10.96187437142857</v>
+        <v>10.92255607142857</v>
       </c>
       <c r="O76">
-        <v>1.644281155714285</v>
+        <v>1.638383410714285</v>
       </c>
       <c r="P76">
-        <v>9.317593215714284</v>
+        <v>9.284172660714285</v>
       </c>
       <c r="Q76">
-        <v>14.01759321571428</v>
+        <v>13.98417266071428</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2202529410009403</v>
+        <v>0.2269249319953519</v>
       </c>
       <c r="T76">
-        <v>3.195166879774531</v>
+        <v>3.317366737943636</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.767544310200019</v>
+        <v>4.703977052730686</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09198498299883798</v>
+        <v>0.0919205013374315</v>
       </c>
       <c r="C77">
-        <v>19.81884628585168</v>
+        <v>19.14250306125711</v>
       </c>
       <c r="D77">
-        <v>72.76884628585168</v>
+        <v>72.8035030612571</v>
       </c>
       <c r="E77">
-        <v>24.825</v>
+        <v>25.53599999999999</v>
       </c>
       <c r="F77">
-        <v>53.325</v>
+        <v>54.03599999999999</v>
       </c>
       <c r="G77">
         <v>0.375</v>
@@ -7601,28 +7601,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M77">
-        <v>2.9488725</v>
+        <v>2.9881908</v>
       </c>
       <c r="N77">
-        <v>10.92255607142857</v>
+        <v>10.88323777142857</v>
       </c>
       <c r="O77">
-        <v>1.638383410714285</v>
+        <v>1.632485665714285</v>
       </c>
       <c r="P77">
-        <v>9.284172660714285</v>
+        <v>9.250752105714284</v>
       </c>
       <c r="Q77">
-        <v>13.98417266071428</v>
+        <v>13.95075210571428</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2269249319953519</v>
+        <v>0.2341529222392979</v>
       </c>
       <c r="T77">
-        <v>3.317366737943636</v>
+        <v>3.449749917626833</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.703977052730686</v>
+        <v>4.642082617826335</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0919205013374315</v>
+        <v>0.09185601967602501</v>
       </c>
       <c r="C78">
-        <v>19.14250306125711</v>
+        <v>18.46619286355373</v>
       </c>
       <c r="D78">
-        <v>72.8035030612571</v>
+        <v>72.83819286355373</v>
       </c>
       <c r="E78">
-        <v>25.53599999999999</v>
+        <v>26.247</v>
       </c>
       <c r="F78">
-        <v>54.03599999999999</v>
+        <v>54.747</v>
       </c>
       <c r="G78">
         <v>0.375</v>
@@ -7683,28 +7683,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M78">
-        <v>2.9881908</v>
+        <v>3.0275091</v>
       </c>
       <c r="N78">
-        <v>10.88323777142857</v>
+        <v>10.84391947142857</v>
       </c>
       <c r="O78">
-        <v>1.632485665714285</v>
+        <v>1.626587920714285</v>
       </c>
       <c r="P78">
-        <v>9.250752105714284</v>
+        <v>9.217331550714285</v>
       </c>
       <c r="Q78">
-        <v>13.95075210571428</v>
+        <v>13.91733155071428</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2341529222392979</v>
+        <v>0.2420094333740218</v>
       </c>
       <c r="T78">
-        <v>3.449749917626833</v>
+        <v>3.593644678152047</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.642082617826335</v>
+        <v>4.581795830581838</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09185601967602501</v>
+        <v>0.09179153801461852</v>
       </c>
       <c r="C79">
-        <v>18.46619286355373</v>
+        <v>17.78991573997455</v>
       </c>
       <c r="D79">
-        <v>72.83819286355373</v>
+        <v>72.87291573997454</v>
       </c>
       <c r="E79">
-        <v>26.247</v>
+        <v>26.958</v>
       </c>
       <c r="F79">
-        <v>54.747</v>
+        <v>55.458</v>
       </c>
       <c r="G79">
         <v>0.375</v>
@@ -7765,28 +7765,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M79">
-        <v>3.0275091</v>
+        <v>3.0668274</v>
       </c>
       <c r="N79">
-        <v>10.84391947142857</v>
+        <v>10.80460117142857</v>
       </c>
       <c r="O79">
-        <v>1.626587920714285</v>
+        <v>1.620690175714285</v>
       </c>
       <c r="P79">
-        <v>9.217331550714285</v>
+        <v>9.183910995714283</v>
       </c>
       <c r="Q79">
-        <v>13.91733155071428</v>
+        <v>13.88391099571428</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2420094333740218</v>
+        <v>0.2505801727937206</v>
       </c>
       <c r="T79">
-        <v>3.593644678152047</v>
+        <v>3.750620780543189</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.581795830581838</v>
+        <v>4.52305485839489</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09179153801461852</v>
+        <v>0.09340580635321202</v>
       </c>
       <c r="C80">
-        <v>17.78991573997455</v>
+        <v>16.21948697985505</v>
       </c>
       <c r="D80">
-        <v>72.87291573997454</v>
+        <v>72.01348697985505</v>
       </c>
       <c r="E80">
-        <v>26.958</v>
+        <v>27.669</v>
       </c>
       <c r="F80">
-        <v>55.458</v>
+        <v>56.169</v>
       </c>
       <c r="G80">
         <v>0.375</v>
@@ -7847,45 +7847,45 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M80">
-        <v>3.0668274</v>
+        <v>3.2465682</v>
       </c>
       <c r="N80">
-        <v>10.80460117142857</v>
+        <v>10.62486037142857</v>
       </c>
       <c r="O80">
-        <v>1.620690175714285</v>
+        <v>1.593729055714285</v>
       </c>
       <c r="P80">
-        <v>9.183910995714283</v>
+        <v>9.031131315714283</v>
       </c>
       <c r="Q80">
-        <v>13.88391099571428</v>
+        <v>13.73113131571428</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2505801727937206</v>
+        <v>0.2599671731105335</v>
       </c>
       <c r="T80">
-        <v>3.750620780543189</v>
+        <v>3.922546987923965</v>
       </c>
       <c r="U80">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V80">
         <v>0.15</v>
       </c>
       <c r="W80">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.52305485839489</v>
+        <v>4.27264351675365</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09340580635321202</v>
+        <v>0.09336257469180553</v>
       </c>
       <c r="C81">
-        <v>16.21948697985505</v>
+        <v>15.53123905241458</v>
       </c>
       <c r="D81">
-        <v>72.01348697985505</v>
+        <v>72.03623905241457</v>
       </c>
       <c r="E81">
-        <v>27.669</v>
+        <v>28.38</v>
       </c>
       <c r="F81">
-        <v>56.169</v>
+        <v>56.88</v>
       </c>
       <c r="G81">
         <v>0.375</v>
@@ -7929,28 +7929,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M81">
-        <v>3.2465682</v>
+        <v>3.287664</v>
       </c>
       <c r="N81">
-        <v>10.62486037142857</v>
+        <v>10.58376457142857</v>
       </c>
       <c r="O81">
-        <v>1.593729055714285</v>
+        <v>1.587564685714286</v>
       </c>
       <c r="P81">
-        <v>9.031131315714283</v>
+        <v>8.996199885714285</v>
       </c>
       <c r="Q81">
-        <v>13.73113131571428</v>
+        <v>13.69619988571428</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2599671731105335</v>
+        <v>0.2702928734590277</v>
       </c>
       <c r="T81">
-        <v>3.922546987923965</v>
+        <v>4.111665816042817</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.27264351675365</v>
+        <v>4.21923547279423</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09336257469180553</v>
+        <v>0.09331934303039907</v>
       </c>
       <c r="C82">
-        <v>15.53123905241458</v>
+        <v>14.84300550618038</v>
       </c>
       <c r="D82">
-        <v>72.03623905241457</v>
+        <v>72.05900550618038</v>
       </c>
       <c r="E82">
-        <v>28.38</v>
+        <v>29.091</v>
       </c>
       <c r="F82">
-        <v>56.88</v>
+        <v>57.591</v>
       </c>
       <c r="G82">
         <v>0.375</v>
@@ -8011,28 +8011,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M82">
-        <v>3.287664</v>
+        <v>3.3287598</v>
       </c>
       <c r="N82">
-        <v>10.58376457142857</v>
+        <v>10.54266877142857</v>
       </c>
       <c r="O82">
-        <v>1.587564685714286</v>
+        <v>1.581400315714286</v>
       </c>
       <c r="P82">
-        <v>8.996199885714285</v>
+        <v>8.961268455714285</v>
       </c>
       <c r="Q82">
-        <v>13.69619988571428</v>
+        <v>13.66126845571428</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2702928734590277</v>
+        <v>0.2817054896336794</v>
       </c>
       <c r="T82">
-        <v>4.111665816042817</v>
+        <v>4.320691889226813</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.21923547279423</v>
+        <v>4.16714614596961</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09331934303039907</v>
+        <v>0.09327611136899258</v>
       </c>
       <c r="C83">
-        <v>14.84300550618038</v>
+        <v>14.154786354792</v>
       </c>
       <c r="D83">
-        <v>72.05900550618038</v>
+        <v>72.081786354792</v>
       </c>
       <c r="E83">
-        <v>29.091</v>
+        <v>29.802</v>
       </c>
       <c r="F83">
-        <v>57.591</v>
+        <v>58.302</v>
       </c>
       <c r="G83">
         <v>0.375</v>
@@ -8093,28 +8093,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M83">
-        <v>3.3287598</v>
+        <v>3.3698556</v>
       </c>
       <c r="N83">
-        <v>10.54266877142857</v>
+        <v>10.50157297142857</v>
       </c>
       <c r="O83">
-        <v>1.581400315714286</v>
+        <v>1.575235945714285</v>
       </c>
       <c r="P83">
-        <v>8.961268455714285</v>
+        <v>8.926337025714284</v>
       </c>
       <c r="Q83">
-        <v>13.66126845571428</v>
+        <v>13.62633702571428</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2817054896336794</v>
+        <v>0.2943861742721811</v>
       </c>
       <c r="T83">
-        <v>4.320691889226813</v>
+        <v>4.552943081653474</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.16714614596961</v>
+        <v>4.116327290530956</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09327611136899258</v>
+        <v>0.09323287970758609</v>
       </c>
       <c r="C84">
-        <v>14.154786354792</v>
+        <v>13.46658161190621</v>
       </c>
       <c r="D84">
-        <v>72.081786354792</v>
+        <v>72.10458161190621</v>
       </c>
       <c r="E84">
-        <v>29.802</v>
+        <v>30.513</v>
       </c>
       <c r="F84">
-        <v>58.302</v>
+        <v>59.013</v>
       </c>
       <c r="G84">
         <v>0.375</v>
@@ -8175,28 +8175,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M84">
-        <v>3.3698556</v>
+        <v>3.4109514</v>
       </c>
       <c r="N84">
-        <v>10.50157297142857</v>
+        <v>10.46047717142857</v>
       </c>
       <c r="O84">
-        <v>1.575235945714285</v>
+        <v>1.569071575714285</v>
       </c>
       <c r="P84">
-        <v>8.926337025714284</v>
+        <v>8.891405595714284</v>
       </c>
       <c r="Q84">
-        <v>13.62633702571428</v>
+        <v>13.59140559571428</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2943861742721811</v>
+        <v>0.3085587041622713</v>
       </c>
       <c r="T84">
-        <v>4.552943081653474</v>
+        <v>4.81251794377739</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.116327290530956</v>
+        <v>4.066732985825764</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09323287970758609</v>
+        <v>0.09318964804617962</v>
       </c>
       <c r="C85">
-        <v>13.46658161190621</v>
+        <v>12.77839129119697</v>
       </c>
       <c r="D85">
-        <v>72.10458161190621</v>
+        <v>72.12739129119697</v>
       </c>
       <c r="E85">
-        <v>30.513</v>
+        <v>31.224</v>
       </c>
       <c r="F85">
-        <v>59.013</v>
+        <v>59.724</v>
       </c>
       <c r="G85">
         <v>0.375</v>
@@ -8257,28 +8257,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M85">
-        <v>3.4109514</v>
+        <v>3.4520472</v>
       </c>
       <c r="N85">
-        <v>10.46047717142857</v>
+        <v>10.41938137142857</v>
       </c>
       <c r="O85">
-        <v>1.569071575714285</v>
+        <v>1.562907205714285</v>
       </c>
       <c r="P85">
-        <v>8.891405595714284</v>
+        <v>8.856474165714284</v>
       </c>
       <c r="Q85">
-        <v>13.59140559571428</v>
+        <v>13.55647416571428</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3085587041622713</v>
+        <v>0.3245028002886227</v>
       </c>
       <c r="T85">
-        <v>4.81251794377739</v>
+        <v>5.104539663666795</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.066732985825764</v>
+        <v>4.018319497899267</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0931896480461796</v>
+        <v>0.09567516638477312</v>
       </c>
       <c r="C86">
-        <v>12.77839129119698</v>
+        <v>10.77901164000661</v>
       </c>
       <c r="D86">
-        <v>72.12739129119697</v>
+        <v>70.8390116400066</v>
       </c>
       <c r="E86">
-        <v>31.22399999999999</v>
+        <v>31.935</v>
       </c>
       <c r="F86">
-        <v>59.72399999999999</v>
+        <v>60.435</v>
       </c>
       <c r="G86">
         <v>0.375</v>
@@ -8339,45 +8339,45 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M86">
-        <v>3.4520472</v>
+        <v>3.7046655</v>
       </c>
       <c r="N86">
-        <v>10.41938137142857</v>
+        <v>10.16676307142857</v>
       </c>
       <c r="O86">
-        <v>1.562907205714286</v>
+        <v>1.525014460714285</v>
       </c>
       <c r="P86">
-        <v>8.856474165714285</v>
+        <v>8.641748610714284</v>
       </c>
       <c r="Q86">
-        <v>13.55647416571428</v>
+        <v>13.34174861071428</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3245028002886225</v>
+        <v>0.3425727758984874</v>
       </c>
       <c r="T86">
-        <v>5.104539663666792</v>
+        <v>5.435497612874784</v>
       </c>
       <c r="U86">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V86">
         <v>0.15</v>
       </c>
       <c r="W86">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>4.018319497899268</v>
+        <v>3.744313372267636</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09567516638477312</v>
+        <v>0.09566168472336663</v>
       </c>
       <c r="C87">
-        <v>10.77901164000661</v>
+        <v>10.07487575655563</v>
       </c>
       <c r="D87">
-        <v>70.8390116400066</v>
+        <v>70.84587575655563</v>
       </c>
       <c r="E87">
-        <v>31.935</v>
+        <v>32.64599999999999</v>
       </c>
       <c r="F87">
-        <v>60.435</v>
+        <v>61.14599999999999</v>
       </c>
       <c r="G87">
         <v>0.375</v>
@@ -8421,28 +8421,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M87">
-        <v>3.7046655</v>
+        <v>3.7482498</v>
       </c>
       <c r="N87">
-        <v>10.16676307142857</v>
+        <v>10.12317877142857</v>
       </c>
       <c r="O87">
-        <v>1.525014460714285</v>
+        <v>1.518476815714285</v>
       </c>
       <c r="P87">
-        <v>8.641748610714284</v>
+        <v>8.604701955714285</v>
       </c>
       <c r="Q87">
-        <v>13.34174861071428</v>
+        <v>13.30470195571428</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3425727758984874</v>
+        <v>0.3632241765954759</v>
       </c>
       <c r="T87">
-        <v>5.435497612874784</v>
+        <v>5.813735269112488</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.744313372267636</v>
+        <v>3.70077484468313</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09566168472336663</v>
+        <v>0.09564820306196015</v>
       </c>
       <c r="C88">
-        <v>10.07487575655563</v>
+        <v>9.37074120346373</v>
       </c>
       <c r="D88">
-        <v>70.84587575655563</v>
+        <v>70.85274120346372</v>
       </c>
       <c r="E88">
-        <v>32.64599999999999</v>
+        <v>33.35699999999999</v>
       </c>
       <c r="F88">
-        <v>61.14599999999999</v>
+        <v>61.85699999999999</v>
       </c>
       <c r="G88">
         <v>0.375</v>
@@ -8503,28 +8503,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M88">
-        <v>3.7482498</v>
+        <v>3.7918341</v>
       </c>
       <c r="N88">
-        <v>10.12317877142857</v>
+        <v>10.07959447142857</v>
       </c>
       <c r="O88">
-        <v>1.518476815714285</v>
+        <v>1.511939170714286</v>
       </c>
       <c r="P88">
-        <v>8.604701955714285</v>
+        <v>8.567655300714286</v>
       </c>
       <c r="Q88">
-        <v>13.30470195571428</v>
+        <v>13.26765530071429</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3632241765954759</v>
+        <v>0.3870527158612319</v>
       </c>
       <c r="T88">
-        <v>5.813735269112488</v>
+        <v>6.250163334002148</v>
       </c>
       <c r="U88">
         <v>0.0613</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.70077484468313</v>
+        <v>3.65823720279022</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09564820306196015</v>
+        <v>0.09563472140055367</v>
       </c>
       <c r="C89">
-        <v>9.37074120346373</v>
+        <v>8.666607981117735</v>
       </c>
       <c r="D89">
-        <v>70.85274120346372</v>
+        <v>70.85960798111773</v>
       </c>
       <c r="E89">
-        <v>33.35699999999999</v>
+        <v>34.068</v>
       </c>
       <c r="F89">
-        <v>61.85699999999999</v>
+        <v>62.568</v>
       </c>
       <c r="G89">
         <v>0.375</v>
@@ -8585,28 +8585,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M89">
-        <v>3.7918341</v>
+        <v>3.8354184</v>
       </c>
       <c r="N89">
-        <v>10.07959447142857</v>
+        <v>10.03601017142857</v>
       </c>
       <c r="O89">
-        <v>1.511939170714286</v>
+        <v>1.505401525714285</v>
       </c>
       <c r="P89">
-        <v>8.567655300714286</v>
+        <v>8.530608645714285</v>
       </c>
       <c r="Q89">
-        <v>13.26765530071429</v>
+        <v>13.23060864571428</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3870527158612319</v>
+        <v>0.4148526783379472</v>
       </c>
       <c r="T89">
-        <v>6.250163334002148</v>
+        <v>6.759329409706752</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.65823720279022</v>
+        <v>3.616666325485785</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09563472140055367</v>
+        <v>0.09562123973914716</v>
       </c>
       <c r="C90">
-        <v>8.666607981117735</v>
+        <v>7.962476089904598</v>
       </c>
       <c r="D90">
-        <v>70.85960798111773</v>
+        <v>70.86647608990459</v>
       </c>
       <c r="E90">
-        <v>34.068</v>
+        <v>34.779</v>
       </c>
       <c r="F90">
-        <v>62.568</v>
+        <v>63.279</v>
       </c>
       <c r="G90">
         <v>0.375</v>
@@ -8667,28 +8667,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M90">
-        <v>3.8354184</v>
+        <v>3.8790027</v>
       </c>
       <c r="N90">
-        <v>10.03601017142857</v>
+        <v>9.992425871428571</v>
       </c>
       <c r="O90">
-        <v>1.505401525714285</v>
+        <v>1.498863880714286</v>
       </c>
       <c r="P90">
-        <v>8.530608645714285</v>
+        <v>8.493561990714285</v>
       </c>
       <c r="Q90">
-        <v>13.23060864571428</v>
+        <v>13.19356199071428</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4148526783379472</v>
+        <v>0.4477071794467925</v>
       </c>
       <c r="T90">
-        <v>6.759329409706752</v>
+        <v>7.361071135539465</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.616666325485785</v>
+        <v>3.576029625199429</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09562123973914716</v>
+        <v>0.09560775807774069</v>
       </c>
       <c r="C91">
-        <v>7.962476089904598</v>
+        <v>7.2583455302114</v>
       </c>
       <c r="D91">
-        <v>70.86647608990459</v>
+        <v>70.8733455302114</v>
       </c>
       <c r="E91">
-        <v>34.779</v>
+        <v>35.48999999999999</v>
       </c>
       <c r="F91">
-        <v>63.279</v>
+        <v>63.98999999999999</v>
       </c>
       <c r="G91">
         <v>0.375</v>
@@ -8749,28 +8749,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M91">
-        <v>3.8790027</v>
+        <v>3.922587</v>
       </c>
       <c r="N91">
-        <v>9.992425871428571</v>
+        <v>9.94884157142857</v>
       </c>
       <c r="O91">
-        <v>1.498863880714286</v>
+        <v>1.492326235714285</v>
       </c>
       <c r="P91">
-        <v>8.493561990714285</v>
+        <v>8.456515335714284</v>
       </c>
       <c r="Q91">
-        <v>13.19356199071428</v>
+        <v>13.15651533571428</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4477071794467925</v>
+        <v>0.487132580777407</v>
       </c>
       <c r="T91">
-        <v>7.361071135539465</v>
+        <v>8.083161206538721</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.576029625199429</v>
+        <v>3.536295962697213</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09560775807774069</v>
+        <v>0.09776007641633419</v>
       </c>
       <c r="C92">
-        <v>7.2583455302114</v>
+        <v>5.467262587598825</v>
       </c>
       <c r="D92">
-        <v>70.8733455302114</v>
+        <v>69.79326258759882</v>
       </c>
       <c r="E92">
-        <v>35.48999999999999</v>
+        <v>36.20099999999999</v>
       </c>
       <c r="F92">
-        <v>63.98999999999999</v>
+        <v>64.70099999999999</v>
       </c>
       <c r="G92">
         <v>0.375</v>
@@ -8831,45 +8831,45 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M92">
-        <v>3.922587</v>
+        <v>4.1473341</v>
       </c>
       <c r="N92">
-        <v>9.94884157142857</v>
+        <v>9.72409447142857</v>
       </c>
       <c r="O92">
-        <v>1.492326235714285</v>
+        <v>1.458614170714285</v>
       </c>
       <c r="P92">
-        <v>8.456515335714284</v>
+        <v>8.265480300714284</v>
       </c>
       <c r="Q92">
-        <v>13.15651533571428</v>
+        <v>12.96548030071428</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.487132580777407</v>
+        <v>0.5353191824037135</v>
       </c>
       <c r="T92">
-        <v>8.083161206538721</v>
+        <v>8.965715737760034</v>
       </c>
       <c r="U92">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V92">
         <v>0.15</v>
       </c>
       <c r="W92">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y92">
-        <v>3.536295962697213</v>
+        <v>3.344661470950356</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09776007641633419</v>
+        <v>0.09777039475492771</v>
       </c>
       <c r="C93">
-        <v>5.467262587598825</v>
+        <v>4.75116389047021</v>
       </c>
       <c r="D93">
-        <v>69.79326258759882</v>
+        <v>69.7881638904702</v>
       </c>
       <c r="E93">
-        <v>36.20099999999999</v>
+        <v>36.91199999999999</v>
       </c>
       <c r="F93">
-        <v>64.70099999999999</v>
+        <v>65.41199999999999</v>
       </c>
       <c r="G93">
         <v>0.375</v>
@@ -8913,28 +8913,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M93">
-        <v>4.1473341</v>
+        <v>4.1929092</v>
       </c>
       <c r="N93">
-        <v>9.72409447142857</v>
+        <v>9.678519371428571</v>
       </c>
       <c r="O93">
-        <v>1.458614170714285</v>
+        <v>1.451777905714286</v>
       </c>
       <c r="P93">
-        <v>8.265480300714284</v>
+        <v>8.226741465714285</v>
       </c>
       <c r="Q93">
-        <v>12.96548030071428</v>
+        <v>12.92674146571428</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5353191824037135</v>
+        <v>0.5955524344365967</v>
       </c>
       <c r="T93">
-        <v>8.965715737760034</v>
+        <v>10.06890890178668</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.344661470950356</v>
+        <v>3.308306454961765</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09777039475492771</v>
+        <v>0.09778071309352122</v>
       </c>
       <c r="C94">
-        <v>4.75116389047021</v>
+        <v>4.035065938250568</v>
       </c>
       <c r="D94">
-        <v>69.7881638904702</v>
+        <v>69.78306593825057</v>
       </c>
       <c r="E94">
-        <v>36.91199999999999</v>
+        <v>37.623</v>
       </c>
       <c r="F94">
-        <v>65.41199999999999</v>
+        <v>66.123</v>
       </c>
       <c r="G94">
         <v>0.375</v>
@@ -8995,28 +8995,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M94">
-        <v>4.1929092</v>
+        <v>4.238484300000001</v>
       </c>
       <c r="N94">
-        <v>9.678519371428571</v>
+        <v>9.63294427142857</v>
       </c>
       <c r="O94">
-        <v>1.451777905714286</v>
+        <v>1.444941640714285</v>
       </c>
       <c r="P94">
-        <v>8.226741465714285</v>
+        <v>8.188002630714285</v>
       </c>
       <c r="Q94">
-        <v>12.92674146571428</v>
+        <v>12.88800263071428</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5955524344365967</v>
+        <v>0.6729951870503036</v>
       </c>
       <c r="T94">
-        <v>10.06890890178668</v>
+        <v>11.48730011267807</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.308306454961765</v>
+        <v>3.272733267274004</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09778071309352122</v>
+        <v>0.09779103143211473</v>
       </c>
       <c r="C95">
-        <v>4.035065938250568</v>
+        <v>3.31896873077666</v>
       </c>
       <c r="D95">
-        <v>69.78306593825057</v>
+        <v>69.77796873077666</v>
       </c>
       <c r="E95">
-        <v>37.623</v>
+        <v>38.334</v>
       </c>
       <c r="F95">
-        <v>66.123</v>
+        <v>66.834</v>
       </c>
       <c r="G95">
         <v>0.375</v>
@@ -9077,28 +9077,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M95">
-        <v>4.238484300000001</v>
+        <v>4.2840594</v>
       </c>
       <c r="N95">
-        <v>9.63294427142857</v>
+        <v>9.58736917142857</v>
       </c>
       <c r="O95">
-        <v>1.444941640714285</v>
+        <v>1.438105375714285</v>
       </c>
       <c r="P95">
-        <v>8.188002630714285</v>
+        <v>8.149263795714285</v>
       </c>
       <c r="Q95">
-        <v>12.88800263071428</v>
+        <v>12.84926379571428</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6729951870503036</v>
+        <v>0.7762521905352462</v>
       </c>
       <c r="T95">
-        <v>11.48730011267807</v>
+        <v>13.3784883938666</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.272733267274004</v>
+        <v>3.237916955920025</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09779103143211473</v>
+        <v>0.09780134977070826</v>
       </c>
       <c r="C96">
-        <v>3.31896873077666</v>
+        <v>2.602872267885274</v>
       </c>
       <c r="D96">
-        <v>69.77796873077666</v>
+        <v>69.77287226788528</v>
       </c>
       <c r="E96">
-        <v>38.334</v>
+        <v>39.045</v>
       </c>
       <c r="F96">
-        <v>66.834</v>
+        <v>67.545</v>
       </c>
       <c r="G96">
         <v>0.375</v>
@@ -9159,28 +9159,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M96">
-        <v>4.2840594</v>
+        <v>4.3296345</v>
       </c>
       <c r="N96">
-        <v>9.58736917142857</v>
+        <v>9.541794071428569</v>
       </c>
       <c r="O96">
-        <v>1.438105375714285</v>
+        <v>1.431269110714285</v>
       </c>
       <c r="P96">
-        <v>8.149263795714285</v>
+        <v>8.110524960714283</v>
       </c>
       <c r="Q96">
-        <v>12.84926379571428</v>
+        <v>12.81052496071428</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7762521905352462</v>
+        <v>0.9208119954141661</v>
       </c>
       <c r="T96">
-        <v>13.3784883938666</v>
+        <v>16.02615198753055</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.237916955920025</v>
+        <v>3.203833619541919</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09780134977070826</v>
+        <v>0.09781166810930175</v>
       </c>
       <c r="C97">
-        <v>2.602872267885274</v>
+        <v>1.886776549413341</v>
       </c>
       <c r="D97">
-        <v>69.77287226788528</v>
+        <v>69.76777654941334</v>
       </c>
       <c r="E97">
-        <v>39.045</v>
+        <v>39.756</v>
       </c>
       <c r="F97">
-        <v>67.545</v>
+        <v>68.256</v>
       </c>
       <c r="G97">
         <v>0.375</v>
@@ -9241,28 +9241,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M97">
-        <v>4.3296345</v>
+        <v>4.375209600000001</v>
       </c>
       <c r="N97">
-        <v>9.541794071428569</v>
+        <v>9.496218971428569</v>
       </c>
       <c r="O97">
-        <v>1.431269110714285</v>
+        <v>1.424432845714285</v>
       </c>
       <c r="P97">
-        <v>8.110524960714283</v>
+        <v>8.071786125714283</v>
       </c>
       <c r="Q97">
-        <v>12.81052496071428</v>
+        <v>12.77178612571428</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9208119954141661</v>
+        <v>1.137651702732546</v>
       </c>
       <c r="T97">
-        <v>16.02615198753055</v>
+        <v>19.99764737802646</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.203833619541919</v>
+        <v>3.170460352671691</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09781166810930175</v>
+        <v>0.09782198644789528</v>
       </c>
       <c r="C98">
-        <v>1.886776549413355</v>
+        <v>1.17068157519769</v>
       </c>
       <c r="D98">
-        <v>69.76777654941334</v>
+        <v>69.76268157519769</v>
       </c>
       <c r="E98">
-        <v>39.75599999999999</v>
+        <v>40.467</v>
       </c>
       <c r="F98">
-        <v>68.25599999999999</v>
+        <v>68.967</v>
       </c>
       <c r="G98">
         <v>0.375</v>
@@ -9323,28 +9323,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M98">
-        <v>4.3752096</v>
+        <v>4.4207847</v>
       </c>
       <c r="N98">
-        <v>9.49621897142857</v>
+        <v>9.45064387142857</v>
       </c>
       <c r="O98">
-        <v>1.424432845714285</v>
+        <v>1.417596580714285</v>
       </c>
       <c r="P98">
-        <v>8.071786125714285</v>
+        <v>8.033047290714284</v>
       </c>
       <c r="Q98">
-        <v>12.77178612571428</v>
+        <v>12.73304729071428</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.137651702732543</v>
+        <v>1.499051214929841</v>
       </c>
       <c r="T98">
-        <v>19.99764737802641</v>
+        <v>26.61680636218624</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.170460352671692</v>
+        <v>3.137775194396725</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09782198644789528</v>
+        <v>0.09783230478648879</v>
       </c>
       <c r="C99">
-        <v>1.17068157519769</v>
+        <v>0.4545873450753248</v>
       </c>
       <c r="D99">
-        <v>69.76268157519769</v>
+        <v>69.75758734507532</v>
       </c>
       <c r="E99">
-        <v>40.467</v>
+        <v>41.178</v>
       </c>
       <c r="F99">
-        <v>68.967</v>
+        <v>69.678</v>
       </c>
       <c r="G99">
         <v>0.375</v>
@@ -9405,28 +9405,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M99">
-        <v>4.4207847</v>
+        <v>4.4663598</v>
       </c>
       <c r="N99">
-        <v>9.45064387142857</v>
+        <v>9.405068771428571</v>
       </c>
       <c r="O99">
-        <v>1.417596580714285</v>
+        <v>1.410760315714286</v>
       </c>
       <c r="P99">
-        <v>8.033047290714284</v>
+        <v>7.994308455714285</v>
       </c>
       <c r="Q99">
-        <v>12.73304729071428</v>
+        <v>12.69430845571429</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.499051214929841</v>
+        <v>2.221850239324437</v>
       </c>
       <c r="T99">
-        <v>26.61680636218624</v>
+        <v>39.8551243305059</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.137775194396725</v>
+        <v>3.105757080168188</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09783230478648879</v>
+        <v>0.0978426231250823</v>
       </c>
       <c r="C100">
-        <v>0.4545873450753248</v>
+        <v>-0.2615061411167545</v>
       </c>
       <c r="D100">
-        <v>69.75758734507532</v>
+        <v>69.75249385888324</v>
       </c>
       <c r="E100">
-        <v>41.178</v>
+        <v>41.889</v>
       </c>
       <c r="F100">
-        <v>69.678</v>
+        <v>70.389</v>
       </c>
       <c r="G100">
         <v>0.375</v>
@@ -9487,28 +9487,28 @@
         <v>13.87142857142857</v>
       </c>
       <c r="M100">
-        <v>4.4663598</v>
+        <v>4.5119349</v>
       </c>
       <c r="N100">
-        <v>9.405068771428571</v>
+        <v>9.35949367142857</v>
       </c>
       <c r="O100">
-        <v>1.410760315714286</v>
+        <v>1.403924050714285</v>
       </c>
       <c r="P100">
-        <v>7.994308455714285</v>
+        <v>7.955569620714285</v>
       </c>
       <c r="Q100">
-        <v>12.69430845571429</v>
+        <v>12.65556962071429</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.221850239324437</v>
+        <v>4.390247312508226</v>
       </c>
       <c r="T100">
-        <v>39.8551243305059</v>
+        <v>79.57007823546489</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.105757080168188</v>
+        <v>3.074385796530125</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0978426231250823</v>
-      </c>
-      <c r="C101">
-        <v>-0.2615061411167545</v>
-      </c>
-      <c r="D101">
-        <v>69.75249385888324</v>
-      </c>
-      <c r="E101">
-        <v>41.889</v>
-      </c>
-      <c r="F101">
-        <v>70.389</v>
-      </c>
-      <c r="G101">
-        <v>0.375</v>
-      </c>
-      <c r="H101">
-        <v>42.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>18.57142857142857</v>
-      </c>
-      <c r="K101">
-        <v>4.699999999999999</v>
-      </c>
-      <c r="L101">
-        <v>13.87142857142857</v>
-      </c>
-      <c r="M101">
-        <v>4.5119349</v>
-      </c>
-      <c r="N101">
-        <v>9.35949367142857</v>
-      </c>
-      <c r="O101">
-        <v>1.403924050714285</v>
-      </c>
-      <c r="P101">
-        <v>7.955569620714285</v>
-      </c>
-      <c r="Q101">
-        <v>12.65556962071429</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.390247312508226</v>
-      </c>
-      <c r="T101">
-        <v>79.57007823546489</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.054485</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.074385796530125</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
